--- a/workspaces/nasdaq_hourly_24hrs/rsi/rsi_14.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/rsi/rsi_14.xlsx
@@ -618,2133 +618,2133 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 17.57</t>
+          <t>X ≈ 17.54</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7.436829119005253</v>
+        <v>8.411528515251533</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.095372756007514</v>
+        <v>5.647973032541294</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.820246358535115</v>
+        <v>-0.6600588553198818</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-10.00383225496902</v>
+        <v>-8.660228553893937</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-7.892303764131242</v>
+        <v>-9.003904396645254</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-12.67858149550221</v>
+        <v>-13.66951335861948</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-20.93425034378058</v>
+        <v>-21.74207234914614</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-13.75881612102128</v>
+        <v>-14.74840340248955</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-13.71987373032916</v>
+        <v>-14.70982325339585</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-19.49475367443649</v>
+        <v>-20.36212033648123</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-16.7280077444216</v>
+        <v>-17.6568826269961</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-7.051476183087814</v>
+        <v>-8.223145663210119</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.259626791243988</v>
+        <v>2.785743342502471</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.9504318546619359</v>
+        <v>-2.302768538104047</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-1.624731150590947</v>
+        <v>-2.976251376417544</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>1.47926539984865</v>
+        <v>0.06542125755269268</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>1.343266813677474</v>
+        <v>2.36317241258017</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>7.706915810952495</v>
+        <v>7.128086337540225</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>10.42135490984047</v>
+        <v>9.788167316739155</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>3.120534354596884</v>
+        <v>2.67289758227389</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>5.076709770642942</v>
+        <v>4.554955237595472</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>2.504049315029775</v>
+        <v>3.48814173367964</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>2.779645474491609</v>
+        <v>3.76373127337181</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>2.70467836257253</v>
+        <v>3.689166856621284</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 20.17</t>
+          <t>X ≈ 20.14</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>39</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.716278514656757</v>
+        <v>1.389384130075385</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1626827966437219</v>
+        <v>-0.1292330781416595</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.9542457335300867</v>
+        <v>0.9893865975897995</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.892801845911627</v>
+        <v>7.928836532568695</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.431712775717443</v>
+        <v>2.497031105157802</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.06835246235427661</v>
+        <v>0.1334769357683143</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.700241471910438</v>
+        <v>-0.634189370069933</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.9780899636902021</v>
+        <v>-0.9116758129229865</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.615980348205561</v>
+        <v>1.682400997404947</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.953938722517215</v>
+        <v>6.021315921075782</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>8.783452247906865</v>
+        <v>8.850563668334608</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.06313571128668</v>
+        <v>11.13061860056152</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>12.50138327233227</v>
+        <v>12.57021457774915</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.727571621278024</v>
+        <v>9.796687477202468</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>9.073415838120106</v>
+        <v>9.143333501625456</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>4.552705915302134</v>
+        <v>4.621958996306404</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>6.979736708295576</v>
+        <v>7.049191527851647</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>6.874753292200296</v>
+        <v>6.946684827649676</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>4.532553911951233</v>
+        <v>4.603567926912838</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>4.721025176227386</v>
+        <v>4.791897762824917</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>4.17997617675875</v>
+        <v>4.251344971139751</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>9.230645735718035</v>
+        <v>9.300654611223983</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>9.508325802779716</v>
+        <v>9.578052823627132</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>6.871345029240352</v>
+        <v>6.94119937694763</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 22.77</t>
+          <t>X ≈ 22.75</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-5.454332709774931</v>
+        <v>-7.422176648181157</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-11.82703627475227</v>
+        <v>-13.20476963589475</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-16.74911832242551</v>
+        <v>-17.32518815640186</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-20.95223774672319</v>
+        <v>-22.47223413903992</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-12.59891364974037</v>
+        <v>-15.58505117774772</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-8.925746902239219</v>
+        <v>-10.76450467294467</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-9.697009151202082</v>
+        <v>-11.53542739767101</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-13.47004045525827</v>
+        <v>-15.43571063433785</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-11.68639111473358</v>
+        <v>-13.589157600149</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-8.9659447281064</v>
+        <v>-10.74128194002208</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-6.948034612246282</v>
+        <v>-8.6606419557883</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-5.480351628258084</v>
+        <v>-7.12955441674378</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-11.85018103370466</v>
+        <v>-13.68939603785039</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-8.575382755702854</v>
+        <v>-10.28763364764842</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-9.235099308761789</v>
+        <v>-10.94709466050674</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-10.39468691190813</v>
+        <v>-12.17154196141619</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-10.53171149649777</v>
+        <v>-10.49415035900801</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-10.63669491259305</v>
+        <v>-10.60205056653935</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-10.42407965107689</v>
+        <v>-10.3895751127959</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-11.99242868953198</v>
+        <v>-12.02235516333586</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-12.53862966108273</v>
+        <v>-12.56808928115377</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-10.86493964531792</v>
+        <v>-10.82682931721643</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-5.331934248422478</v>
+        <v>-5.102774434678778</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-7.163742690058484</v>
+        <v>-6.99819456244731</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 25.38</t>
+          <t>X ≈ 25.36</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.043960570546353</v>
+        <v>-3.067847558691106</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-8.612992145793321</v>
+        <v>-9.875334426137492</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-8.757578867522639</v>
+        <v>-8.758122813076589</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.9864625555322348</v>
+        <v>0.8502474322992555</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.6196681265730888</v>
+        <v>1.239398231520873</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>6.044486237405032</v>
+        <v>6.595964878474724</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.647142474985387</v>
+        <v>3.233854802896502</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.562680862555958</v>
+        <v>-0.9243909330047373</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.141148723170851</v>
+        <v>-3.468697620975021</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.3196117275497912</v>
+        <v>0.925270684252034</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.023974165398094</v>
+        <v>-1.384468633927376</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.9931797638605175</v>
+        <v>-0.3701386001049443</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4.431130887006631</v>
+        <v>4.970726097406661</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.584275038227446</v>
+        <v>2.158427695109857</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>2.231150337031274</v>
+        <v>2.78935258641765</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.2072771899790595</v>
+        <v>0.7989657487864861</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-6.496011097930293</v>
+        <v>-5.818307030385796</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-5.287306940459267</v>
+        <v>-5.925090028688984</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-2.979206010699997</v>
+        <v>-3.11287041608206</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-1.478967894901849</v>
+        <v>-1.627663347929953</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>4.550702269189109</v>
+        <v>3.015227614180745</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>4.476391854110254</v>
+        <v>2.938592405135402</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>8.698726696583684</v>
+        <v>7.880149950116063</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>5.994152046783633</v>
+        <v>5.209597645345603</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 28</t>
+          <t>X ≈ 27.96</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.222742454719793</v>
+        <v>-2.7004334475372</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-3.568730780671693</v>
+        <v>-3.0468889267812</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-4.468634308367527</v>
+        <v>-5.501233067516601</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.172830034908415</v>
+        <v>-2.240369720476806</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-2.53999589302456</v>
+        <v>-2.57956647495179</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.347161711579837</v>
+        <v>-1.392819995082519</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.901509723213913</v>
+        <v>3.366114106236672</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.62175146191791</v>
+        <v>3.086886547178366</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.359899137515313</v>
+        <v>-0.8544277118130168</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.13201079765723</v>
+        <v>-0.6354451549313325</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.875670329458437</v>
+        <v>-3.349094745373364</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.156591966335625</v>
+        <v>-3.629490346238029</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.274499150672106</v>
+        <v>-2.765934508874508</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-4.506677100925835</v>
+        <v>-3.987563295842264</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-1.14013078022348</v>
+        <v>-0.6602956243575875</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.5406280881461427</v>
+        <v>-0.06137190161368267</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.3318584952931545</v>
+        <v>-0.1970164715789195</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-2.799147437856831</v>
+        <v>-2.30002412746061</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-2.580223142841305</v>
+        <v>-3.081012882876045</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.7886837141690393</v>
+        <v>-1.893995495768245</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-4.358869892613278</v>
+        <v>-4.441684419955216</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-1.407726143349684</v>
+        <v>-1.5181691549191</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-3.152923115747512</v>
+        <v>-3.2389036407764</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-2.219564061669324</v>
+        <v>-1.725467289719631</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 30.6</t>
+          <t>X ≈ 30.57</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-7.549401178427971</v>
+        <v>-7.005214789508571</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-8.85288805726951</v>
+        <v>-8.302490555917508</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-7.402403218957922</v>
+        <v>-6.834872321940509</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-4.258258221659574</v>
+        <v>-3.680941150924262</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-16.21716881562383</v>
+        <v>-15.61066274407376</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-6.371564363481163</v>
+        <v>-6.728991034761592</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-6.18440410394544</v>
+        <v>-6.530778004362389</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.533379175291842</v>
+        <v>-4.876362080785526</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-3.526513378297537</v>
+        <v>-3.869441999776456</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.370526628576094</v>
+        <v>-2.706847738714025</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.030732466124057</v>
+        <v>-3.402349428791375</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.4389044451831197</v>
+        <v>0.189588600521958</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-5.444336467728029</v>
+        <v>-4.803882674424173</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.794295269464321</v>
+        <v>-1.151480803949354</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-2.458371936961782</v>
+        <v>-1.808728577718639</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.07985118303041361</v>
+        <v>0.7226295682045532</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.025860674540006</v>
+        <v>-0.3801707689190437</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.1615382396906426</v>
+        <v>0.4849202343944583</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>3.936960897169428</v>
+        <v>4.581709568234992</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>4.125722216173969</v>
+        <v>4.770192302938398</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>7.064402497141138</v>
+        <v>7.142027474566625</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>5.050579445018293</v>
+        <v>5.124433940341994</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>4.356576442864728</v>
+        <v>4.428034866416283</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>7.194969624709024</v>
+        <v>7.264823972416302</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 33.2</t>
+          <t>X ≈ 33.19</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.294203203061421</v>
+        <v>-5.176025286600073</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.46648690393878</v>
+        <v>1.489684749050276</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.777209592393028</v>
+        <v>-1.496119699543044</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.494693372279549</v>
+        <v>-2.207719922863291</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.658028224009961</v>
+        <v>-3.317656931964841</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-4.835182123426762</v>
+        <v>-4.688629616351783</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.8765223516996059</v>
+        <v>-0.792346097795857</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.213009495478978</v>
+        <v>1.263505266164422</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.4635132634072576</v>
+        <v>1.305433278238169</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.3180462275757705</v>
+        <v>-0.2429817933972984</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.8321470476068527</v>
+        <v>-1.527018452853781</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.070692677017696</v>
+        <v>-5.700244210335526</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.627620517214602</v>
+        <v>-5.264254661846344</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.268272557979309</v>
+        <v>-3.928046344724777</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-3.144367919564338</v>
+        <v>-3.806631355407561</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-6.505702964027989</v>
+        <v>-7.11394883204823</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.679179474146288</v>
+        <v>-3.349216980380788</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-3.578060107873796</v>
+        <v>-4.23551111078617</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-3.354515918747659</v>
+        <v>-4.021343446163982</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-1.577557394665604</v>
+        <v>-2.273856219818072</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-2.921015900889877</v>
+        <v>-3.598263787569302</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>1.439344770861084</v>
+        <v>0.2321402510217752</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.1957966073219239</v>
+        <v>-1.837135036496349</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>1.315789473684212</v>
+        <v>-0.3504672897196244</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 35.81</t>
+          <t>X ≈ 35.79</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>115</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.218418224441066</v>
+        <v>-4.0516988662214</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-8.738802722259479</v>
+        <v>-9.57384231841656</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.711280481449748</v>
+        <v>-6.678664237248391</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-7.426281744445284</v>
+        <v>-7.390142528597217</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-6.060184113803004</v>
+        <v>-5.992137644232379</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-5.878158737392638</v>
+        <v>-5.808307380334512</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-6.650644029182963</v>
+        <v>-6.576935676013662</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-8.663565168508903</v>
+        <v>-8.587302207497814</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5.158532222753905</v>
+        <v>-5.951904074990608</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-6.799516651006208</v>
+        <v>-6.724432297084398</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-4.793739687402514</v>
+        <v>-4.72110268513854</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-5.942034052322533</v>
+        <v>-5.867915940480806</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-7.934740948180995</v>
+        <v>-7.857128610669236</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-8.158856975537716</v>
+        <v>-8.080790076494814</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-14.03168798044441</v>
+        <v>-13.94633311352918</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-12.57325865928036</v>
+        <v>-12.4900756839355</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-14.4504530137056</v>
+        <v>-14.36501059549992</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-11.07844532588646</v>
+        <v>-11.00066760359839</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-12.60099088583401</v>
+        <v>-12.52701003075332</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-10.67557142581771</v>
+        <v>-10.60629420680836</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-12.95706757417071</v>
+        <v>-12.89174204843886</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-13.03307591317373</v>
+        <v>-12.96758800984816</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-14.49690286537015</v>
+        <v>-14.43224373214852</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-11.09966946351386</v>
+        <v>-11.02981511580658</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 38.42</t>
+          <t>X ≈ 38.4</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.04233853646658</v>
+        <v>-1.58222308200645</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>6.661698882353193</v>
+        <v>7.200776990345958</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6.040030739433043</v>
+        <v>6.587314646440177</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.251042319020513</v>
+        <v>-0.7596378919570057</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.316012481263236</v>
+        <v>3.877182457177561</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.683552034209924</v>
+        <v>3.237064879056504</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.854135417006702</v>
+        <v>-4.170085685261178</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.488809283233955</v>
+        <v>-2.792383324645542</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.02358559420365935</v>
+        <v>-0.2625280432479187</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.578456492159816</v>
+        <v>-1.86889641564278</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3459853723648294</v>
+        <v>0.06659675406933729</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.583884854074803</v>
+        <v>-1.874657115697111</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.241261397606749</v>
+        <v>-0.5118248020719136</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.289268500074591</v>
+        <v>-0.734028021960917</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.3034876469071364</v>
+        <v>0.2655218402222985</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>1.121926414930179</v>
+        <v>1.695756048966082</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>3.135698146962284</v>
+        <v>3.225822372663288</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1.378438230218883</v>
+        <v>1.457077820032218</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.594386818392984</v>
+        <v>1.676781916087975</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.1290377301929837</v>
+        <v>1.033823038373072</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.4139299124610858</v>
+        <v>0.1517362124306985</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-2.968314266972968</v>
+        <v>-2.42410974897841</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-2.693640935766055</v>
+        <v>-2.149635036496356</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-2.770528248997152</v>
+        <v>-2.225467289719631</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 41.02</t>
+          <t>X ≈ 41.01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-4.555827051172663</v>
+        <v>-4.928619321180875</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.5789709342504</v>
+        <v>-1.977539539163914</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-5.523243304871841</v>
+        <v>-5.900973498308332</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.929066835892016</v>
+        <v>-3.330393862780383</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-6.621719624603095</v>
+        <v>-6.139984618459458</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.769346954635601</v>
+        <v>-4.30010156297309</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-8.880098256282032</v>
+        <v>-7.552354721104699</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-7.017993556074188</v>
+        <v>-7.014045133721368</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-7.809447483327453</v>
+        <v>-6.973030561271763</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-7.759886030037009</v>
+        <v>-6.935327757339167</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-7.486383520067065</v>
+        <v>-6.658816281426439</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-7.770428966037791</v>
+        <v>-7.283246377746721</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.912033881263355</v>
+        <v>-3.469239261179887</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.471181446646376</v>
+        <v>-2.867993813156062</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-2.304626558749526</v>
+        <v>-2.707633988194722</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-2.038085277631303</v>
+        <v>-2.935474159772696</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-2.172147004534921</v>
+        <v>-3.071501376921475</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.6111462546461084</v>
+        <v>-1.525709092792766</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-2.894191144161397</v>
+        <v>-3.78621767537863</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.04129105153693</v>
+        <v>-2.280924231173522</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-2.417227805566512</v>
+        <v>-2.823470399139552</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-4.992175093807624</v>
+        <v>-5.378655203523863</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-5.55050389567581</v>
+        <v>-5.930626772033541</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-11.46198830409357</v>
+        <v>-11.79158299219896</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 43.63</t>
+          <t>X ≈ 43.62</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.070354469482616</v>
+        <v>1.434896461675251</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.005340651671069452</v>
+        <v>0.3646128543463902</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.7245114700668296</v>
+        <v>-0.3585125912725218</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.182574824569208</v>
+        <v>-1.809166313903788</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-5.50959032065456</v>
+        <v>-5.813719254510062</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-6.794028268349322</v>
+        <v>-7.083732163432238</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-7.150157967787955</v>
+        <v>-7.868399633736175</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-5.213927565234314</v>
+        <v>-5.222057506808412</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.696650469037067</v>
+        <v>-4.447677101587189</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.998204601793816</v>
+        <v>-3.765308425416848</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-6.420442818547492</v>
+        <v>-6.723497283243766</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-5.964535721546376</v>
+        <v>-5.536827445065022</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.917041298898113</v>
+        <v>-1.531362119002729</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-4.361474790578988</v>
+        <v>-3.956002738341546</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-2.355092912110358</v>
+        <v>-2.417872288151678</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-3.981575838258244</v>
+        <v>-4.024677731748611</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-3.375214374960393</v>
+        <v>-3.426335524403477</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.739813634980194</v>
+        <v>-2.79717147555769</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.3025912548502347</v>
+        <v>0.06626009984046277</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-3.077403589703252</v>
+        <v>-2.688070560779742</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-2.879882586111044</v>
+        <v>-2.495322611098551</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-2.95580214106851</v>
+        <v>-2.571168572507815</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-2.681133476643161</v>
+        <v>-2.296693860025762</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-2.758284600389864</v>
+        <v>-2.372526113249037</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 46.24</t>
+          <t>X ≈ 46.22</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>126</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-4.24721379480458</v>
+        <v>-4.572254065251578</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.011605450098202</v>
+        <v>-2.541675045633653</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-4.514122526188316</v>
+        <v>-4.029178522067447</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-5.252732890053991</v>
+        <v>-4.75862735064446</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-7.240091027141894</v>
+        <v>-6.703465432457364</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-7.031220087675813</v>
+        <v>-6.496197942809928</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-9.438491385444649</v>
+        <v>-8.888613719212749</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-6.547027097255821</v>
+        <v>-6.004935428850246</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-4.444213979663303</v>
+        <v>-4.373363513778777</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-6.355599998410632</v>
+        <v>-6.756798795683089</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.112807714699173</v>
+        <v>-3.30305463109417</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.98650661210209</v>
+        <v>-5.174309570858618</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.1117677084130122</v>
+        <v>-1.084712924836204</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.3643998933400425</v>
+        <v>-0.8347549830718606</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.4936151511620253</v>
+        <v>-0.7113863367686477</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.2994966482757349</v>
+        <v>-0.9028055097783749</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-1.422242651724176</v>
+        <v>-2.146116376213115</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.52619401217089</v>
+        <v>-1.77194687398768</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-3.68689500759772</v>
+        <v>-3.937007874015741</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-5.878739481632898</v>
+        <v>-6.131114445000094</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-5.633793393771931</v>
+        <v>-5.880009819315511</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-5.710436486513167</v>
+        <v>-5.955855780724434</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-8.60820038333744</v>
+        <v>-8.855984242845558</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-5.033416875522136</v>
+        <v>-5.757213321465656</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 48.85</t>
+          <t>X ≈ 48.83</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>157</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4.855032964974761</v>
+        <v>4.888078710403718</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>7.696768770795451</v>
+        <v>7.09473096058435</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4.329008853911098</v>
+        <v>3.728658919956693</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.972921903006281</v>
+        <v>2.37302056998179</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.959057169798839</v>
+        <v>1.389918144755512</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.568493191441704</v>
+        <v>-3.502888684777098</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.4700658229039831</v>
+        <v>-0.4747770314779132</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.8289465189573519</v>
+        <v>-0.1167664382742828</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.509512648371484</v>
+        <v>0.5650434382512799</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.5424228911812463</v>
+        <v>-1.1112646912513</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.176931068407775</v>
+        <v>-2.107771235845568</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.078415215357744</v>
+        <v>-1.751775562790925</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.292078408367473</v>
+        <v>-0.9672052904489234</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.3973928060760272</v>
+        <v>0.720255197615792</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-3.44625180875731</v>
+        <v>-3.127188505533724</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-3.488134434295453</v>
+        <v>-2.781798880525137</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-2.985285453284995</v>
+        <v>-2.278773342343378</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-4.364154219698747</v>
+        <v>-3.657499396482883</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-3.511088381607692</v>
+        <v>-2.804665340399325</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-5.871815286624063</v>
+        <v>-5.165590231068094</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-7.05195837078125</v>
+        <v>-6.345079074193507</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-9.038741451901707</v>
+        <v>-8.331753061080171</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-7.490080935101112</v>
+        <v>-6.783392998279645</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-7.566022274369431</v>
+        <v>-6.859225251503062</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 51.45</t>
+          <t>X ≈ 51.44</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.534956982732972</v>
+        <v>-0.643329994621709</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2894666270486752</v>
+        <v>0.6682397910225291</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.080543959944833</v>
+        <v>2.514223337779704</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.8233451935186267</v>
+        <v>1.798227618066932</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.47128397972844</v>
+        <v>3.652858530903288</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>4.198480271145485</v>
+        <v>4.939272063640374</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>4.506779013965414</v>
+        <v>4.710746388224486</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.9866372506980809</v>
+        <v>1.139625369258177</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.5928551735053773</v>
+        <v>0.4089029282880077</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.8259066496332537</v>
+        <v>0.1856755682626599</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.715141590760588</v>
+        <v>-1.73708883194108</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.8320733320733282</v>
+        <v>-0.3682202036146691</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.956564550560351</v>
+        <v>-1.491248296743088</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.259002442675786</v>
+        <v>-3.359730846999732</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.6746904384700869</v>
+        <v>-0.1739740015301905</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-3.322873632091579</v>
+        <v>-2.876290376290378</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-2.375886245159549</v>
+        <v>-1.911306414366756</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-4.10249128287645</v>
+        <v>-3.664498766539701</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-5.507989741566497</v>
+        <v>-5.096959033967032</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-5.320945945945944</v>
+        <v>-4.910113223999126</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-4.783065273862938</v>
+        <v>-4.353758293063926</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-2.156317626802725</v>
+        <v>-1.68235150722041</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.341001919780055</v>
+        <v>-0.8584262452878093</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.957483799589191</v>
+        <v>-1.483709047961511</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 54.06</t>
+          <t>X ≈ 54.05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3.30031774868911</v>
+        <v>2.105371571943856</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.803550274043488</v>
+        <v>1.196440516471569</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5.011781616180684</v>
+        <v>4.352954445018952</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6.624849809050978</v>
+        <v>5.362982765182856</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>8.584353507814384</v>
+        <v>7.898548092517643</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>6.447038216164678</v>
+        <v>5.214742993001614</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>7.41806208603348</v>
+        <v>6.740450474079573</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.49120002927053</v>
+        <v>1.870016898310347</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.694580917732026</v>
+        <v>2.485612297586954</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>4.083458447890678</v>
+        <v>2.862050909834252</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.2892581578252091</v>
+        <v>-0.3102292774646784</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.478207838673086</v>
+        <v>-4.035090939661558</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-8.091071150183346</v>
+        <v>-8.604300245063079</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-6.568241914706206</v>
+        <v>-5.953375080122768</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-6.064382456068962</v>
+        <v>-6.615808029570864</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-6.050717755284914</v>
+        <v>-6.596133751306162</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-4.440625402922223</v>
+        <v>-5.580625600927313</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-5.708399516691784</v>
+        <v>-6.834891592104682</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-3.166694958411</v>
+        <v>-3.745436992789564</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-2.979651162790695</v>
+        <v>-4.133303826499557</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-3.522851571788649</v>
+        <v>-4.675849994465857</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-3.017411278594054</v>
+        <v>-4.176983312196668</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-3.905426809786206</v>
+        <v>-5.05193388707093</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-5.144158846729233</v>
+        <v>-6.277191427650529</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 56.67</t>
+          <t>X ≈ 56.65</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.893877207406881</v>
+        <v>3.875393133347217</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.752195090815178</v>
+        <v>1.117099731839915</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.304318035472036</v>
+        <v>2.083000116668508</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4.336193842766932</v>
+        <v>4.392365095592815</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>4.568274467179009</v>
+        <v>4.652473733914718</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.06203116070579284</v>
+        <v>-0.6114764291078387</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.3626945141800277</v>
+        <v>-0.1858203225789978</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.08052613357711635</v>
+        <v>-0.1107730361426746</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.330113837284124</v>
+        <v>1.146103509753409</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.257093838791285</v>
+        <v>-1.451167160200704</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.5834582138633166</v>
+        <v>0.03428743811364399</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2980453281658129</v>
+        <v>-1.459851329315732</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.434584739423961</v>
+        <v>-5.01125022824337</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.451122273349959</v>
+        <v>-5.23232910468996</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-2.302824596724612</v>
+        <v>-3.094386921942991</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.105354908549003</v>
+        <v>-1.893939393939192</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.6370389641437129</v>
+        <v>-0.8157353187955181</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.1396127416849779</v>
+        <v>-0.3145154165563042</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-4.140357048632481</v>
+        <v>-4.94710888411668</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-3.953313253012048</v>
+        <v>-4.154202468088251</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-4.496513662010003</v>
+        <v>-4.696748636054018</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-5.174878356206825</v>
+        <v>-5.378655203523863</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-3.695283912616404</v>
+        <v>-3.892059278920584</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-4.373634890439014</v>
+        <v>-3.967891532143859</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 59.27</t>
+          <t>X ≈ 59.26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.8130580814286859</v>
+        <v>1.136222950262301</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.759933848835651</v>
+        <v>2.71227417739027</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.9618178973017777</v>
+        <v>0.637312453200046</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.31663685152057</v>
+        <v>-1.986469591720486</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.681906636544618</v>
+        <v>-2.322260064267823</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.351411822616008</v>
+        <v>2.323304847944208</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>5.065725177741477</v>
+        <v>6.009954890168572</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.864093609146067</v>
+        <v>3.820915419937791</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.222595454036501</v>
+        <v>-0.596196124262157</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.073353941728932</v>
+        <v>-0.09522644998024532</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.765107889488888</v>
+        <v>2.089661217659383</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.078088578088575</v>
+        <v>-0.0999162112662475</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.2795028734988705</v>
+        <v>0.6877497473553404</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.345294161620693</v>
+        <v>4.925269597023402</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>2.045337281557678</v>
+        <v>2.99324094912437</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.7173204081022106</v>
+        <v>1.676799845589585</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.980875850149282</v>
+        <v>-1.004887992024763</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.760294579909363</v>
+        <v>2.711927355109545</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.6943664607898228</v>
+        <v>1.016990710556023</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.400641025641022</v>
+        <v>0.5668938453648806</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.9438414346389763</v>
+        <v>0.02434767739885046</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.3787708492559503</v>
+        <v>0.5854443911489824</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.1039956827738209</v>
+        <v>0.8599191036310359</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.102114260009067</v>
+        <v>1.421029525567</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 61.88</t>
+          <t>X ≈ 61.87</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-4.283877503311771</v>
+        <v>-4.845666390540401</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-7.667833505760974</v>
+        <v>-8.192491381661299</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.619729091798334</v>
+        <v>-4.208823683704338</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.284741917186608</v>
+        <v>-1.307319871821775</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.4304995070887045</v>
+        <v>-0.4382910672605576</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.3664212034790495</v>
+        <v>0.3510847573910496</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.2033111689859979</v>
+        <v>0.1815457120548487</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.5345126210284121</v>
+        <v>0.5057439058559794</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.253239606631873</v>
+        <v>-1.862407466446179</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.850973763086429</v>
+        <v>2.786363604505283</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.5332035551640217</v>
+        <v>-0.5540345846580905</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.23648302916596</v>
+        <v>2.179264204664996</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.941260103361742</v>
+        <v>2.260921414917306</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.329659389888363</v>
+        <v>2.642252177024943</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>3.280484248412108</v>
+        <v>3.188928156552812</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>3.875544298033418</v>
+        <v>3.783315078495804</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.521938408762544</v>
+        <v>2.444578664409903</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.416954992667264</v>
+        <v>2.339737960588721</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.8038098629161539</v>
+        <v>1.350810064404605</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.9908536585365866</v>
+        <v>0.9352462358184184</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.667165444660647</v>
+        <v>1.597519344960887</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>3.420478681700899</v>
+        <v>3.32890229921437</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.03671726281717014</v>
+        <v>-0.01108081962888008</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.18028811867066</v>
+        <v>1.117906204256279</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 64.49</t>
+          <t>X ≈ 64.47</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.871333139703836</v>
+        <v>0.5845049992440963</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.634059722961602</v>
+        <v>3.066629609345057</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.194359258875309</v>
+        <v>0.9243852082013149</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.31663685152057</v>
+        <v>-1.90124486757945</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.8145968599588826</v>
+        <v>1.284091420436653</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-6.690546219342025</v>
+        <v>-6.27542126670533</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.966908854892559</v>
+        <v>-3.526243190032382</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-5.644064899012442</v>
+        <v>-5.21290533901081</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.406744638185771</v>
+        <v>-0.9460660444199647</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.0826779510529434</v>
+        <v>0.3936943358814915</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.890982015363015</v>
+        <v>1.371979330156016</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.409090909090835</v>
+        <v>3.91013133515888</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.8859982920023626</v>
+        <v>1.378518564077403</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.433260616934007</v>
+        <v>-0.9552363687072898</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.7050109412314214</v>
+        <v>1.203521742162941</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.6007702915520881</v>
+        <v>1.09368331199309</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.165977296703879</v>
+        <v>1.663991527128459</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.337607517992808</v>
+        <v>0.1507001190817618</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.5778163442397002</v>
+        <v>1.07081685211876</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.6337412587412601</v>
+        <v>-0.1507880421384868</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.9209604301628005</v>
+        <v>1.419341846233436</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.8450053745203618</v>
+        <v>1.343495884824414</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.518381939603806</v>
+        <v>3.026421301531826</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>1.743139901034638</v>
+        <v>2.246363696195864</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 67.09</t>
+          <t>X ≈ 67.08</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>139</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.160410968349801</v>
+        <v>3.193685260668751</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.386386532842209</v>
+        <v>0.7006350810239326</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.211587312538732</v>
+        <v>-2.176232888870324</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.04768278400526782</v>
+        <v>-0.7309135270181031</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.4129525690294074</v>
+        <v>-1.066703999565377</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>5.52960772743063</v>
+        <v>5.595082330416808</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.879043753649981</v>
+        <v>1.945435804799928</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.917035870721264</v>
+        <v>5.983771122636696</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>7.397400856607376</v>
+        <v>7.464107225414708</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>8.062414366701169</v>
+        <v>8.13004047024161</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>11.21447147554312</v>
+        <v>11.2817979541303</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>9.496528651204997</v>
+        <v>9.564199629818773</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>9.810886353581076</v>
+        <v>9.879886483825878</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.431256161251603</v>
+        <v>7.500534226084397</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>8.93059830350942</v>
+        <v>9.000664309798729</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>8.086809432267493</v>
+        <v>8.156202310878655</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>8.672140198550224</v>
+        <v>8.741709634332665</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>5.689458940728329</v>
+        <v>5.759171088785038</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.747308722365261</v>
+        <v>3.816789088414396</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.214928057553955</v>
+        <v>3.284210437950684</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>4.830001029851054</v>
+        <v>4.899937651279622</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>7.631743815934904</v>
+        <v>7.701789531597136</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>7.187094521985451</v>
+        <v>7.256839783647536</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.514030880558707</v>
+        <v>3.583885228265906</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 69.71</t>
+          <t>X ≈ 69.69</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.842218463530287</v>
+        <v>4.151360678775831</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.414525678565056</v>
+        <v>-0.07952001567791456</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.5470366001675302</v>
+        <v>-0.2188377660075744</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.353549171606559</v>
+        <v>1.665610811952284</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.9725049271429071</v>
+        <v>-0.6182316086469442</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-3.399719399103439</v>
+        <v>-3.678018669302809</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.211801217432019</v>
+        <v>-2.501915405141247</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-3.143950634192329</v>
+        <v>-3.429477499244825</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-5.716813654137049</v>
+        <v>-5.985392914732834</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-5.183459522422901</v>
+        <v>-5.459607292068021</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.641126399098376</v>
+        <v>-1.938794403152968</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.04056401115225583</v>
+        <v>-0.2694918585488963</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.8768571063905952</v>
+        <v>0.5553980226470046</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.923474151565465</v>
+        <v>3.581072392953658</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>3.264542912528086</v>
+        <v>2.9229290953731</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>6.473982047116785</v>
+        <v>6.114718614718626</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>7.647077895451531</v>
+        <v>7.279502776442442</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>5.581310165630754</v>
+        <v>5.226610124569305</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>7.104622871046168</v>
+        <v>6.741202804194934</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>8.598856209150327</v>
+        <v>8.226749912864264</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>7.402061028910474</v>
+        <v>7.034853095547582</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>5.36532165954241</v>
+        <v>5.010955186086498</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>3.025717741057285</v>
+        <v>2.688027301166024</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>3.603371173030609</v>
+        <v>3.261545697293435</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 72.31</t>
+          <t>X ≈ 72.29</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>135</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.822269553898948</v>
+        <v>-1.788995261580119</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5.990703079604877</v>
+        <v>6.024376088218219</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.588039652555779</v>
+        <v>1.623394076224265</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.096468561584835</v>
+        <v>3.132662279003739</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.953420998783017</v>
+        <v>5.019094028678694</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.362807834012031</v>
+        <v>7.428282436998302</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.849200961217306</v>
+        <v>5.915593012367253</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.829905574957913</v>
+        <v>4.896640826873345</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.649199417758368</v>
+        <v>2.71590578656587</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.134623266248191</v>
+        <v>1.202249369788632</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-4.516943392562347</v>
+        <v>-4.449616913975319</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.351592851592855</v>
+        <v>-0.2839218729789224</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.005397411401482088</v>
+        <v>0.07439754164644086</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-3.178922362595827</v>
+        <v>-3.109644297763104</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-3.837853601633128</v>
+        <v>-3.767787595343663</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.201650892432696</v>
+        <v>1.271043771043772</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>2.549038679765253</v>
+        <v>2.618608115547779</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>3.184796004410714</v>
+        <v>3.254508152467338</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.141659908083277</v>
+        <v>4.211140274132411</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>5.81018518518519</v>
+        <v>5.879467565581919</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>6.00772551692797</v>
+        <v>6.077662138356622</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>2.228066757581708</v>
+        <v>2.298112473243869</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>2.502841924063745</v>
+        <v>2.57258718572583</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.686159844054579</v>
+        <v>1.756014191761857</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 74.92</t>
+          <t>X ≈ 74.91</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-10.81697854860799</v>
+        <v>-11.29850477108963</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4378683489665534</v>
+        <v>-0.8224707586286257</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.37243118694731</v>
+        <v>4.045816498646637</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.980066445182679</v>
+        <v>0.6301597765012446</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.6147966601586745</v>
+        <v>0.2943693039539212</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.694818416022656</v>
+        <v>2.283137291853095</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.814809426825725</v>
+        <v>2.412089508863652</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.536254781307107</v>
+        <v>2.133878064110675</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.577770846329798</v>
+        <v>2.175365246025379</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.8039354355604118</v>
+        <v>1.402449569988889</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.7074195830386287</v>
+        <v>-0.1252925896510391</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.772227772227822</v>
+        <v>-2.205843794900844</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.3252904192862971</v>
+        <v>0.2745977418466978</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.3462099125365015</v>
+        <v>0.9544197663010081</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>3.25870724492767</v>
+        <v>3.899880072324052</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.2823387231205245</v>
+        <v>0.8906633906633985</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>1.933959314685936</v>
+        <v>2.558548055487677</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>4.507547327162044</v>
+        <v>5.156410054369189</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>4.723670490093859</v>
+        <v>5.372301435293515</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>2.232142857142861</v>
+        <v>2.856444542558947</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>5.260371019573476</v>
+        <v>5.917501978196476</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2.505844535359437</v>
+        <v>3.138953314084659</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>6.352048273270135</v>
+        <v>7.017031630170308</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>4.49039264828739</v>
+        <v>5.139397575145288</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 77.53</t>
+          <t>X ≈ 77.51</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>8.230640499011166</v>
+        <v>8.623303829964257</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.628344539442736</v>
+        <v>-1.145435232536499</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.503383567899697</v>
+        <v>5.907111756168412</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.9800664451827785</v>
+        <v>1.420572831065243</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.471939517301536</v>
+        <v>3.914971037763301</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.706723177927316</v>
+        <v>2.215144771030495</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.886237998254295</v>
+        <v>2.386592313555241</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.512445257497696</v>
+        <v>3.995173321632237</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.506342274901257</v>
+        <v>4.980056729962072</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.542030673655539</v>
+        <v>7.980725959585925</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.816389940770989</v>
+        <v>8.254785601747905</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.537296037296088</v>
+        <v>7.976036198299909</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.317566723570728</v>
+        <v>8.739666584273898</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.239067055393569</v>
+        <v>5.688399028582083</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>4.62775486397539</v>
+        <v>4.086859504586393</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>6.175195865977663</v>
+        <v>5.624642652944544</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>7.945864076590595</v>
+        <v>7.377517968797306</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>10.69802351763823</v>
+        <v>10.10286594422141</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>7.10462287104621</v>
+        <v>6.545172419485333</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>11.10119047619048</v>
+        <v>10.50560313511366</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>9.605609114811564</v>
+        <v>9.019660740732583</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>11.43441596393087</v>
+        <v>10.83060723215367</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>10.75681017803205</v>
+        <v>10.16168571822062</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>8.776106934001668</v>
+        <v>8.199061012167114</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 80.13</t>
+          <t>X ≈ 80.12</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>92</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6.108487289901412</v>
+        <v>6.141761582220241</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>7.947224818735307</v>
+        <v>7.980897827348649</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.101171297524743</v>
+        <v>-1.065816873856257</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-3.988877654196159</v>
+        <v>-3.952683936777255</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.093277874002808</v>
+        <v>-1.027604844107131</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.267799782482236</v>
+        <v>1.333274385468506</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-3.852892436528307</v>
+        <v>-3.786500385378361</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.2163790049096477</v>
+        <v>0.2831142568250797</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.344851591671386</v>
+        <v>1.411557960478888</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.74492922438025</v>
+        <v>2.812555327920691</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.193201534973845</v>
+        <v>5.260528013560872</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8.174977196716327</v>
+        <v>8.24264817533026</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.31135554344664</v>
+        <v>10.3803556736916</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.916085688933926</v>
+        <v>7.985363753766649</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>9.431067493374918</v>
+        <v>9.501133499664384</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>7.852214499518006</v>
+        <v>7.921607378129082</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>1.196381674934344</v>
+        <v>1.26595111071687</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.004441737099924126</v>
+        <v>0.07415388515654797</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>4.568390986988298</v>
+        <v>4.637871353037433</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>5.842391304347828</v>
+        <v>5.911673684744557</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>6.386147417088971</v>
+        <v>6.456084038517623</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>7.397148883185487</v>
+        <v>7.467194598847648</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>9.84583709314591</v>
+        <v>9.915582354807995</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>13.03076531909483</v>
+        <v>13.10061966680211</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 82.74</t>
+          <t>X ≈ 82.72</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>89</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.752844886383997</v>
+        <v>4.786119178702826</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-5.694690178822107</v>
+        <v>-5.661017170208765</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-3.76360412605429</v>
+        <v>-3.728249702385803</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.140580088842434</v>
+        <v>1.176773806261338</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-4.842667224271494</v>
+        <v>-4.776994194375817</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-3.531907105646738</v>
+        <v>-3.466432502660467</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.560395301625121</v>
+        <v>3.626787352775068</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.529031667342473</v>
+        <v>5.595766919257905</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.446952226747158</v>
+        <v>4.513658595554659</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.3023302991238026</v>
+        <v>0.3699564026642435</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.700285071857117</v>
+        <v>1.767611550444144</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.915573190854062</v>
+        <v>5.983244169467994</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.667486466748933</v>
+        <v>3.736486596993892</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>2.322534150096637</v>
+        <v>2.391812214929359</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>0.5400074054413651</v>
+        <v>0.6100734117308306</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-2.235719061791166</v>
+        <v>-2.16632618318009</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>1.000973760913823</v>
+        <v>1.070543196696349</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.8959903448185429</v>
+        <v>0.9657024928751667</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>1.112113507750358</v>
+        <v>1.181593873799493</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>1.299157303370791</v>
+        <v>1.368439683767519</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>1.879552399990828</v>
+        <v>1.949489021419481</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>1.803597344348219</v>
+        <v>1.87364306001038</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>0.9547770052123354</v>
+        <v>1.02452226687442</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>4.249622182797815</v>
+        <v>4.319476530505092</v>
       </c>
     </row>
     <row r="32">
@@ -2754,243 +2754,243 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-7.007454739084132</v>
+        <v>-5.91357438615924</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-5.120408031506201</v>
+        <v>-3.975623911781717</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-2.115664051147895</v>
+        <v>-3.140915688085499</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-13.9405684754522</v>
+        <v>-12.94477879843736</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-12.08361603825399</v>
+        <v>-11.00784199825733</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-11.89645142524726</v>
+        <v>-13.09360308488723</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-8.224873112856912</v>
+        <v>-7.047369950595822</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-8.503427758375381</v>
+        <v>-7.325581395348834</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-6.239689471130582</v>
+        <v>-5.011366940706957</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-7.013524881900011</v>
+        <v>-5.784282616743447</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-2.294721170340232</v>
+        <v>-0.9647684291269414</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-7.018259518259455</v>
+        <v>-5.788972378029356</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-8.142750736746663</v>
+        <v>-6.912134444885538</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-8.364107547781018</v>
+        <v>-7.133213321332128</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-13.46748323126276</v>
+        <v>-12.33681116436723</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-15.0946454038636</v>
+        <v>-14.01515151515152</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-17.45096132023475</v>
+        <v>-16.42179592485623</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-15.33372251410777</v>
+        <v>-14.25390935595017</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-17.33982157339821</v>
+        <v>-16.31074524775308</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-10.48611111111111</v>
+        <v>-9.305717619603271</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-11.02931152010903</v>
+        <v>-9.848263787569266</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-6.660822131307228</v>
+        <v>-5.378655203523827</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-6.386046964825098</v>
+        <v>-5.104180491041774</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-8.684210526315795</v>
+        <v>-7.452740016992323</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 87.96</t>
+          <t>X ≈ 87.94</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>49</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.427919410575761</v>
+        <v>-0.5796226236360482</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.174376548992633</v>
+        <v>5.208049557605939</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.73467608490644</v>
+        <v>5.810846835105615</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.020882771713339</v>
+        <v>3.057076489132271</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.696429313219873</v>
+        <v>4.762102343115579</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.238855053365121</v>
+        <v>0.8674358761517311</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.02909514111146905</v>
+        <v>0.09548719226138047</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.8321731486541</v>
+        <v>3.898908400569532</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-2.248759765915111</v>
+        <v>-2.182053397107573</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.9817788501539226</v>
+        <v>-0.9141527466134463</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>1.333396743492031</v>
+        <v>1.400723222079058</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.095119166547761</v>
+        <v>3.162790145161694</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.111004705000632</v>
+        <v>-2.042004574755673</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2915451895043404</v>
+        <v>-0.2222671246716175</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.9504764285416414</v>
+        <v>-0.8804104222521758</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-2.396232705450927</v>
+        <v>-2.32683982683983</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-2.530326399599829</v>
+        <v>-2.460756963817325</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-6.716942468756358</v>
+        <v>-6.647230320699705</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-12.62326828541638</v>
+        <v>-12.55378791936722</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-10.39540816326531</v>
+        <v>-10.32612578286858</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-8.897792245732646</v>
+        <v>-8.827855624303993</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-6.932930974844588</v>
+        <v>-6.862885259182484</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-2.57652315530126</v>
+        <v>-2.506777893639232</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>1.429168158491485</v>
+        <v>1.499022506198713</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 90.56</t>
+          <t>X ≈ 90.55</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>9.591184716698152</v>
+        <v>10.35915288656803</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.133560222462037</v>
+        <v>2.024376088218233</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.775492411437128</v>
+        <v>4.586357039187206</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.061699098243949</v>
+        <v>3.873403019744487</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>4.696429313219902</v>
+        <v>3.537612547197213</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.883593926226688</v>
+        <v>3.724578733294592</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.110727794172661</v>
+        <v>2.952630049404242</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>5.872989475184717</v>
+        <v>4.674418604651166</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>7.955321866737961</v>
+        <v>6.71590578656587</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>7.181486455968532</v>
+        <v>5.942990110529379</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>1.333396743492031</v>
+        <v>0.2170497526912953</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-7.108962466105332</v>
+        <v>-8.061699650756708</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-8.233453684592462</v>
+        <v>-9.184861717612812</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-10.49562682215748</v>
+        <v>-11.40594059405944</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-9.113741734664131</v>
+        <v>-10.06408389163997</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-2.396232705450871</v>
+        <v>-3.469696969696962</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-8.65277537919166</v>
+        <v>-9.603614106674442</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-10.79857512181756</v>
+        <v>-11.70845481049562</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-12.62326828541632</v>
+        <v>-13.49256342957133</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-14.47704081632655</v>
+        <v>-15.30571761960329</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-19.10187387838571</v>
+        <v>-19.8482637875693</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-19.17782893402833</v>
+        <v>-19.92410974897839</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-22.9846864206074</v>
+        <v>-23.64963503649631</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-16.93817878028408</v>
+        <v>-17.72546728971962</v>
       </c>
     </row>
   </sheetData>
@@ -3180,2461 +3180,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 16.26</t>
+          <t>X &gt; 16.23</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3337</v>
+        <v>3342</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1324547390841317</v>
+        <v>-0.1193017939668835</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.005129013279912442</v>
+        <v>-0.02199727682339869</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2077823755473744</v>
+        <v>-0.1950880990821773</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2795616240968144</v>
+        <v>-0.2669896036939434</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3004085160715277</v>
+        <v>-0.3183826923148345</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2753220991998759</v>
+        <v>-0.2932784095625465</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2860935461702709</v>
+        <v>-0.3042916534835243</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2792835425818936</v>
+        <v>-0.2975885424602112</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.3102277898788657</v>
+        <v>-0.3284790808752973</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.2911534504864477</v>
+        <v>-0.3096916534753831</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.357739412462891</v>
+        <v>-0.3760948076663766</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.3509293036017453</v>
+        <v>-0.3693919584490075</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.3530255276666097</v>
+        <v>-0.3718584369686155</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.4073967288054732</v>
+        <v>-0.4262269902407851</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.3911732093460429</v>
+        <v>-0.410249215423903</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.4359508348551344</v>
+        <v>-0.4547715965626367</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.4626572266675026</v>
+        <v>-0.451628439311051</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.4901023459288538</v>
+        <v>-0.4790641294920448</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.5255387088460495</v>
+        <v>-0.5143740062070989</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.5602738700987686</v>
+        <v>-0.5489931725022572</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.5170028042075288</v>
+        <v>-0.5059618443704963</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.4553713975546074</v>
+        <v>-0.444444677208061</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.4323820956419624</v>
+        <v>-0.4213969270138449</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.4306228061413151</v>
+        <v>-0.4196623824784496</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 18.87</t>
+          <t>X &gt; 18.84</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3297</v>
+        <v>3301</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2242871183148267</v>
+        <v>-0.2252587896281781</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.09127401503044297</v>
+        <v>-0.09242102195636903</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1882195732060055</v>
+        <v>-0.1893129397347906</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1615844250568088</v>
+        <v>-0.1627415585687686</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2083018099986162</v>
+        <v>-0.2105043554843178</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1248427616651213</v>
+        <v>-0.1271391690562282</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.0355851227840418</v>
+        <v>-0.0380241562032424</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1157465989550843</v>
+        <v>-0.1181025051196443</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1475387278169862</v>
+        <v>-0.1498559027252355</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.05817073621347646</v>
+        <v>-0.06063089128112154</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1591313647594248</v>
+        <v>-0.1614591516250243</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.2696366511360395</v>
+        <v>-0.271844578292928</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.4089873392396868</v>
+        <v>-0.4110773624331117</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.400808495552738</v>
+        <v>-0.4029194460231551</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.3762073865829834</v>
+        <v>-0.3783782403858069</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.4591867006082921</v>
+        <v>-0.4612326407973342</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.48456713313211</v>
+        <v>-0.4865896131758021</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.5895505492273898</v>
+        <v>-0.5735485794006507</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.6583490651540487</v>
+        <v>-0.6423365006756896</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.6049303241442061</v>
+        <v>-0.5890105978115017</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.5848670756646186</v>
+        <v>-0.56882085690021</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.4912758041373806</v>
+        <v>-0.4932892827355957</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.4713511896077947</v>
+        <v>-0.4733782224442606</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.4686610368809454</v>
+        <v>-0.4706960082897496</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 21.47</t>
+          <t>X &gt; 21.45</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3258</v>
+        <v>3262</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.259487259409326</v>
+        <v>-0.2445632267429687</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.09041921377724549</v>
+        <v>-0.09198090233919487</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2018954930840593</v>
+        <v>-0.2034053008493402</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2579997303262331</v>
+        <v>-0.259483295403335</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2399041945421772</v>
+        <v>-0.2428752576808293</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1271554116764051</v>
+        <v>-0.1302550574952761</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02762883131198635</v>
+        <v>-0.03089649116927973</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1054238883275076</v>
+        <v>-0.1086146574788316</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1686489929995716</v>
+        <v>-0.1717621011020185</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.1301388973216717</v>
+        <v>-0.1333457673332106</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.2661788665685023</v>
+        <v>-0.2692055924522521</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.4052959888077652</v>
+        <v>-0.4081707781627415</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.5635313705015932</v>
+        <v>-0.566279810522353</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.5220506148149937</v>
+        <v>-0.5248644705497654</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.4893244233427794</v>
+        <v>-0.492218448214885</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.5191817319221315</v>
+        <v>-0.5220065444904805</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.5739188365746202</v>
+        <v>-0.5766863220967196</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.6789022526699</v>
+        <v>-0.6634594018638538</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.7204869460954555</v>
+        <v>-0.7050557749479012</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.6686848559166094</v>
+        <v>-0.6533439595726378</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.6419047941558773</v>
+        <v>-0.6264500620791082</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.6076523971559027</v>
+        <v>-0.6103842587823252</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.5908132530525734</v>
+        <v>-0.5935516776241485</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.5565248295693195</v>
+        <v>-0.5593115570402887</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 24.08</t>
+          <t>X &gt; 24.06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3201</v>
+        <v>3207</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1669829824112554</v>
+        <v>-0.1214672684707239</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1185739672523027</v>
+        <v>0.1329032200011682</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.09275983377394681</v>
+        <v>0.09023300817947444</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1105012277914241</v>
+        <v>0.1214650352483631</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01982811239712845</v>
+        <v>0.02024282015005952</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.02952053801497101</v>
+        <v>0.05212215761221017</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1445531987516517</v>
+        <v>0.166406034511283</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.1325589746262779</v>
+        <v>0.1542447995611553</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.03644669614094909</v>
+        <v>0.05834602251743348</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.02719972571949114</v>
+        <v>0.04858017264118075</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1471954934027337</v>
+        <v>-0.1252925896510391</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3149248012261694</v>
+        <v>-0.2928991535534635</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.3625507298260047</v>
+        <v>-0.341218571824804</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.3786454501693797</v>
+        <v>-0.3574331313728294</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.3335889755236963</v>
+        <v>-0.3129174841749531</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.3433292498042988</v>
+        <v>-0.3222171937168881</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.3966010666228499</v>
+        <v>-0.4066019684858304</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.5015844827181297</v>
+        <v>-0.4930127183411983</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.5476956983029098</v>
+        <v>-0.5389664192941268</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.4670436817472705</v>
+        <v>-0.4583655946811547</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.4300605837794791</v>
+        <v>-0.4216511356528159</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.425001546438871</v>
+        <v>-0.4351723853137059</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.5063884180834819</v>
+        <v>-0.5162185776434782</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.4388705283984748</v>
+        <v>-0.4488848138855062</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 26.69</t>
+          <t>X &gt; 26.66</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3125</v>
+        <v>3130</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.0970148874678074</v>
+        <v>-0.04898443066019098</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.3309256551215682</v>
+        <v>0.3791122611362141</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.308000070989479</v>
+        <v>0.3079082152838524</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.08919784830077049</v>
+        <v>0.1035365226052676</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.0353806609288867</v>
+        <v>-0.009749181982698474</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.11676342779419</v>
+        <v>-0.1088605546901533</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.08369022755365307</v>
+        <v>0.09094483477785076</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.1737872074665461</v>
+        <v>0.180779927806384</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1380458167386109</v>
+        <v>0.1451135498493556</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.02008826583497836</v>
+        <v>0.02701302586992682</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.1015522360998062</v>
+        <v>-0.09431605437651314</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2984296405349056</v>
+        <v>-0.290999013814023</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.479133066747373</v>
+        <v>-0.4718958049017559</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.4263836764471804</v>
+        <v>-0.4193249152831129</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.395963435605033</v>
+        <v>-0.3892353101927242</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.3567199984198268</v>
+        <v>-0.3497990105132942</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.2482634146614444</v>
+        <v>-0.2734705660045904</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.3851957125458583</v>
+        <v>-0.3593801455307286</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.4885613675054117</v>
+        <v>-0.4756467363060537</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.4424336848833477</v>
+        <v>-0.429600122796117</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.5511927363636815</v>
+        <v>-0.5062005489873798</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.5442034339402184</v>
+        <v>-0.5181691549190006</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.7302568176721849</v>
+        <v>-0.7227746085180726</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.5953216374269061</v>
+        <v>-0.5880870980263353</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 29.3</t>
+          <t>X &gt; 29.27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3026</v>
+        <v>3030</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.005247845234748638</v>
+        <v>0.03852213755357781</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.45850859865876</v>
+        <v>0.4921816072721015</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4642746260312265</v>
+        <v>0.4996290496997133</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.1632033871103289</v>
+        <v>0.1808931642911347</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.04656147653888354</v>
+        <v>0.07506326993046741</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.07650915479526077</v>
+        <v>-0.06648565566730724</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.008498843850965443</v>
+        <v>-0.01714656031980155</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.09369848929381419</v>
+        <v>0.08486881825615455</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1870532689762712</v>
+        <v>0.178101710300254</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.05778086573111807</v>
+        <v>0.04887633216699783</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.02192353760889176</v>
+        <v>0.01310238427024757</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1722042372783719</v>
+        <v>-0.180817781720819</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.3876785914306069</v>
+        <v>-0.3961849565858202</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.29289093057033</v>
+        <v>-0.3015612723603596</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.371616916399077</v>
+        <v>-0.3802894252367963</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.3507031772423943</v>
+        <v>-0.3593180570116346</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.2672429483975662</v>
+        <v>-0.2759938034443863</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.3062197638327717</v>
+        <v>-0.295332489361428</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.4201296042012928</v>
+        <v>-0.3896610549011115</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.4311056105610547</v>
+        <v>-0.3812702425000083</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.4266190290045557</v>
+        <v>-0.3763165928498253</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.5159520300302631</v>
+        <v>-0.4851658545889634</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.6509957590107689</v>
+        <v>-0.6397340463973435</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.542182179396498</v>
+        <v>-0.5505497979704472</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 31.9</t>
+          <t>X &gt; 31.88</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2923</v>
+        <v>2927</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2714568255417191</v>
+        <v>0.2863885207060832</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.7866214469518198</v>
+        <v>0.801662725416449</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.7414788059949302</v>
+        <v>0.7577273214041611</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3190058317573659</v>
+        <v>0.316789622940675</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.619659054401609</v>
+        <v>0.627037912719139</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1453145491030128</v>
+        <v>0.1679653364907807</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.2091262816330399</v>
+        <v>0.2120656155382079</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2567463851037104</v>
+        <v>0.2594526182566028</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.317911074200083</v>
+        <v>0.3205332108598427</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1433490052842004</v>
+        <v>0.1458491983442229</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1647300953866733</v>
+        <v>0.133290814999782</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1628063168492986</v>
+        <v>-0.1938522393125552</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2094932471751747</v>
+        <v>-0.2410797755344447</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2399847906777168</v>
+        <v>-0.271652932164379</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.2980843241589355</v>
+        <v>-0.3300232029253323</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.3658749525103033</v>
+        <v>-0.3973913762454018</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.2405109518896396</v>
+        <v>-0.2723278562479692</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.3113180180191009</v>
+        <v>-0.3227892814853917</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.573663754608809</v>
+        <v>-0.5646016678778807</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.5916780587833159</v>
+        <v>-0.5625482206961721</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.6905859182255725</v>
+        <v>-0.6408842180441923</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.7121041825892789</v>
+        <v>-0.6825655057259254</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.8274514335893457</v>
+        <v>-0.8180668779722637</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.8148221505983031</v>
+        <v>-0.8255697837408107</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 34.51</t>
+          <t>X &gt; 34.49</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2797</v>
+        <v>2799</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.5221801589718211</v>
+        <v>0.5361880803113692</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.7559946870017455</v>
+        <v>0.7701990530244771</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.8098930849355312</v>
+        <v>0.8607971387250828</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.4007098359435091</v>
+        <v>0.4322370048138069</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.7673131827819688</v>
+        <v>0.8074312460951916</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.3696772880156871</v>
+        <v>0.3900604254382074</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2580328700491634</v>
+        <v>0.2579979839936399</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2136683901422174</v>
+        <v>0.213536670085027</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3113519480506</v>
+        <v>0.27549312203368</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1641340604648747</v>
+        <v>0.1636306799244025</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2096376820928612</v>
+        <v>0.2092177840191738</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.0582854533978292</v>
+        <v>0.05795846890143252</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.0104642746957424</v>
+        <v>-0.01136688327009949</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1035656778139398</v>
+        <v>-0.1044438014720868</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.1698641836437105</v>
+        <v>-0.1710357632977164</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.08928634705760174</v>
+        <v>-0.09023905243591201</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1306531636149373</v>
+        <v>-0.1316198148442638</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.16415695140428</v>
+        <v>-0.1438580938646439</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.4483911866140033</v>
+        <v>-0.4065227298212122</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.5472659042172978</v>
+        <v>-0.484289048174702</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.5901089150737278</v>
+        <v>-0.5056414224388988</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.809023227328197</v>
+        <v>-0.7243955653413963</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.8559063882227633</v>
+        <v>-0.7714642612194638</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.9108025097901447</v>
+        <v>-0.8472965144427391</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 37.12</t>
+          <t>X &gt; 37.09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2682</v>
+        <v>2684</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.6825712156804258</v>
+        <v>0.7327629681099097</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.163116872708322</v>
+        <v>1.213404998522144</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.132389341510589</v>
+        <v>1.183836653716504</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.7363190946104439</v>
+        <v>0.7673985720054191</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.060065676856269</v>
+        <v>1.098768959354366</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.6375748058836734</v>
+        <v>0.6556387777719834</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.5542662195688095</v>
+        <v>0.5508509537778536</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.5943103958263762</v>
+        <v>0.590621793379384</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.5458920970597418</v>
+        <v>0.5423152821148278</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.4627246017844726</v>
+        <v>0.4587600548707584</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4241747430518359</v>
+        <v>0.4204647489793487</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.315569846819848</v>
+        <v>0.3118614335359169</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.3293164178660888</v>
+        <v>0.324796529043951</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.2418327186209055</v>
+        <v>0.2373147013698045</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.4245093199476742</v>
+        <v>0.4191874838247287</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.4460070220347276</v>
+        <v>0.4410505200761818</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.4833576427834316</v>
+        <v>0.4782311314207917</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.3038308051451111</v>
+        <v>0.3213181705241013</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.07269343881862511</v>
+        <v>0.1127977022231903</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.1129798732761884</v>
+        <v>-0.05059657677273321</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.05983290992974588</v>
+        <v>0.02505961034425752</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.2848748086584507</v>
+        <v>-0.1998176476371185</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.2710016175769994</v>
+        <v>-0.1861477041565536</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.4739196985753011</v>
+        <v>-0.4110112539521111</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 39.72</t>
+          <t>X &gt; 39.7</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2561</v>
+        <v>2564</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.8113154874530935</v>
+        <v>0.8411086490825923</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.9033244388281787</v>
+        <v>0.9331847804960631</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9005171786255346</v>
+        <v>0.9309437679415922</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.8302162953325691</v>
+        <v>0.8388667372454606</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.9534785767651925</v>
+        <v>0.9687340062581313</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.5409081738542056</v>
+        <v>0.5348232036089087</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.7625507170407531</v>
+        <v>0.7717996264317932</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.7399790725800983</v>
+        <v>0.7489527661418549</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.5705696007089287</v>
+        <v>0.5799834564687814</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.5591646300418986</v>
+        <v>0.5676987352380038</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.4278689694685127</v>
+        <v>0.4370264336085228</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.4053137042225217</v>
+        <v>0.4141945949664745</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.3562746043839411</v>
+        <v>0.3639519735579455</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.3141729167709073</v>
+        <v>0.2827753592479922</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.458905115726445</v>
+        <v>0.4263793236189031</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.4140717441978126</v>
+        <v>0.38232795242142</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.358042062539127</v>
+        <v>0.3496387176340932</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.2530586464438471</v>
+        <v>0.2681624927000072</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.0007977344342080528</v>
+        <v>0.03960031311876122</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.124414519906324</v>
+        <v>-0.1013494448762842</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.04310282898234163</v>
+        <v>0.01913090821853558</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.1580898908700732</v>
+        <v>-0.09571661325296787</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.1565387681037933</v>
+        <v>-0.09425282120773915</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.3654114460953863</v>
+        <v>-0.3260913146806175</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 42.33</t>
+          <t>X &gt; 42.31</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2441</v>
+        <v>2443</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.075165182100811</v>
+        <v>1.126879047937223</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.025354526812386</v>
+        <v>1.077350823344545</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.21631040190276</v>
+        <v>1.2693236243543</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.015023331689363</v>
+        <v>1.045367159923785</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.325876685804189</v>
+        <v>1.320823631141799</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.8019612731654604</v>
+        <v>0.7742934847208289</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.236585078695292</v>
+        <v>1.184088892110026</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.121362405410295</v>
+        <v>1.13344836412935</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.9825327510917035</v>
+        <v>0.9540787066311225</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.9681306600334878</v>
+        <v>0.9393181399051471</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.8169350484297127</v>
+        <v>0.7884783241198789</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.8072346876027865</v>
+        <v>0.7954432063861603</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.5661054189180064</v>
+        <v>0.5538071268134885</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.4511014393477453</v>
+        <v>0.4388306477706649</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.5947608309813077</v>
+        <v>0.5816047066436525</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.5346202254020298</v>
+        <v>0.5466562600659088</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.48242661315318</v>
+        <v>0.519085279828623</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.2955431151578267</v>
+        <v>0.3570116379495474</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.1431159095392687</v>
+        <v>0.2290902748904315</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.07934070434070151</v>
+        <v>0.00660329730217768</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.07360958281203978</v>
+        <v>0.1599228681818232</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.07955460906951117</v>
+        <v>0.1659434642839841</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.1086295298513988</v>
+        <v>0.1948185042322663</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.1800982724461022</v>
+        <v>0.2417860872758766</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 44.94</t>
+          <t>X &gt; 44.92</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.075446815320014</v>
+        <v>1.108721107638843</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.085694444026295</v>
+        <v>1.119367452639636</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.32993180377435</v>
+        <v>1.365286227442837</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.202220101461656</v>
+        <v>1.213644815944832</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.726044962418214</v>
+        <v>1.741412201774075</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.246652768440612</v>
+        <v>1.237532101170245</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.727569602231817</v>
+        <v>1.717742311925832</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.492248852087229</v>
+        <v>1.508111909186802</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.25646585374453</v>
+        <v>1.272517713964319</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.200331553505599</v>
+        <v>1.216660668246632</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.240632365013369</v>
+        <v>1.231316938164717</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.203673978684812</v>
+        <v>1.168737011586586</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.7114761070815732</v>
+        <v>0.6767299778889111</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.7328437598334929</v>
+        <v>0.6979105526303471</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.7674539165482557</v>
+        <v>0.7584269308708613</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.7990115821210821</v>
+        <v>0.8161410554221291</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.708264225206662</v>
+        <v>0.7516718551973085</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.4732417974078729</v>
+        <v>0.5429539454644967</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.1692089135256438</v>
+        <v>0.2386892795747784</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.09617468573905796</v>
+        <v>0.1654570661357866</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.2465156724931532</v>
+        <v>0.316452293921806</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.2572532913195573</v>
+        <v>0.3272990069817183</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.271950434394661</v>
+        <v>0.3416956960567461</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.3521198196416151</v>
+        <v>0.3959024545369871</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 47.55</t>
+          <t>X &gt; 47.52</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.38308683223547</v>
+        <v>1.436920498644888</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.322510859925238</v>
+        <v>1.330871971109346</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.667707421010732</v>
+        <v>1.676933434429678</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.575304540420817</v>
+        <v>1.558672919104048</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.244271170989116</v>
+        <v>2.229286838139579</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.725098630766617</v>
+        <v>1.684322557631276</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.372947439134222</v>
+        <v>2.330489152789418</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.956904250994214</v>
+        <v>1.942153158426905</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.585954688152505</v>
+        <v>1.598689669349753</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.637050533111761</v>
+        <v>1.677300692297592</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.434455048519688</v>
+        <v>1.493275130611593</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.50365689356515</v>
+        <v>1.535185369857139</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.7461381521422297</v>
+        <v>0.7784914660793589</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.7541391392730148</v>
+        <v>0.7864551915567262</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.7832812947311254</v>
+        <v>0.8433404896615926</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.8278826287561714</v>
+        <v>0.9154474594639623</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.831403613506339</v>
+        <v>0.9190819043296869</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.5888055185119683</v>
+        <v>0.6766896186653071</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.3920846447465394</v>
+        <v>0.4799262540600608</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.4415137614678954</v>
+        <v>0.5292204821848969</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.5863867469653528</v>
+        <v>0.6744322234348274</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.6021748105887994</v>
+        <v>0.6902873165878489</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.785206857804873</v>
+        <v>0.87306097450778</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.6633939589033702</v>
+        <v>0.7513781940034363</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 50.15</t>
+          <t>X &gt; 50.13</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.113637725542397</v>
+        <v>1.169217020756484</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.8278205524577942</v>
+        <v>0.8837742135265501</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.461170433880042</v>
+        <v>1.517782791530593</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.466838931955216</v>
+        <v>1.49550464776619</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.266405920463598</v>
+        <v>2.29439597097619</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.058313616474322</v>
+        <v>2.086690228114527</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.520625350032958</v>
+        <v>2.548091322221218</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.044442246016359</v>
+        <v>2.101861842558371</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.591887164793938</v>
+        <v>1.678868749528831</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.806194046514634</v>
+        <v>1.893607394479993</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.714725745681143</v>
+        <v>1.772605308246852</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.78165260345191</v>
+        <v>1.790152201095161</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.9043190715688283</v>
+        <v>0.9139037144859543</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.7818253351760873</v>
+        <v>0.7915902701381299</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.111524842554999</v>
+        <v>1.151331128122884</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.162837981647471</v>
+        <v>1.202239789196319</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>1.127607362140168</v>
+        <v>1.167136881467854</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.9731924087240742</v>
+        <v>1.012889063022165</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.6950001984477794</v>
+        <v>0.7347092977014285</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.9314755313890259</v>
+        <v>0.9709622222939558</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.179179719524036</v>
+        <v>1.218929888320027</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.350382350485489</v>
+        <v>1.39011950003345</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.42743136768437</v>
+        <v>1.46696575401748</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.302058491095089</v>
+        <v>1.341726386169704</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 52.76</t>
+          <t>X &gt; 52.74</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1838</v>
+        <v>1842</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.380226420336164</v>
+        <v>1.348306899583214</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.8820074274309633</v>
+        <v>0.9050702313852526</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.398828702475264</v>
+        <v>1.419328839621066</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.53160843228752</v>
+        <v>1.46559390911542</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.145131469449446</v>
+        <v>2.160172200125629</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.842899671363242</v>
+        <v>1.80483903698223</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.320713256546846</v>
+        <v>2.334408791269752</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.150913369048943</v>
+        <v>2.196936238943081</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.811787780999254</v>
+        <v>1.804348542941341</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.071122571426137</v>
+        <v>2.062360701956401</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.160604666922559</v>
+        <v>2.119382905160101</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.044731655721861</v>
+        <v>2.003411580930766</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.19227525769174</v>
+        <v>1.151546312772432</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.188546303022996</v>
+        <v>1.201764235023617</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.29131256126535</v>
+        <v>1.282278757654289</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.614337790429708</v>
+        <v>1.605221597078284</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.480244096280785</v>
+        <v>1.471304460100811</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.48407460836831</v>
+        <v>1.475041389287227</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.319349022660312</v>
+        <v>1.310911054684951</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.560799782372143</v>
+        <v>1.552045681156777</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.779296870653837</v>
+        <v>1.769542944243952</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.703341815011228</v>
+        <v>1.693696982834851</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.706082161036342</v>
+        <v>1.696727612797901</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>1.630140821767874</v>
+        <v>1.620895359574625</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 55.37</t>
+          <t>X &gt; 55.35</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.181993702162877</v>
+        <v>1.269332527286593</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.7868661491492475</v>
+        <v>0.8746754894158215</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.025822759403638</v>
+        <v>1.113303146971653</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.005775589068236</v>
+        <v>1.059031762259458</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.480337837637464</v>
+        <v>1.561564643005596</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.367562438646651</v>
+        <v>1.449129631498188</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.794456354583026</v>
+        <v>1.874785738027001</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.11578173305967</v>
+        <v>2.231039335627791</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.617405776486628</v>
+        <v>1.733281460622187</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.86336640650903</v>
+        <v>1.978939780990729</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.35380490675734</v>
+        <v>2.372831658023841</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.614927089717007</v>
+        <v>2.63332731149616</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.150699976872126</v>
+        <v>2.169242536431526</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.989367175441608</v>
+        <v>1.948163659984935</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>2.050724051650405</v>
+        <v>2.106179897328865</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>2.40568806285642</v>
+        <v>2.460758665794643</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>2.091522339895974</v>
+        <v>2.206937452078563</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>2.226634962216053</v>
+        <v>2.341904901734594</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.78249401950562</v>
+        <v>1.838371822227259</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>2.029561824729896</v>
+        <v>2.145121708933893</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>2.32669755018572</v>
+        <v>2.441904078138137</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>2.190718484939268</v>
+        <v>2.306106078359726</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>2.285421622609867</v>
+        <v>2.400724675733869</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>2.329528302549086</v>
+        <v>2.4447964992492</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 57.97</t>
+          <t>X &gt; 57.95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1500</v>
+        <v>1503</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.9925452609158683</v>
+        <v>0.9832380495753554</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.7907030796048815</v>
+        <v>0.8480620496287372</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.8843359488520761</v>
+        <v>1.006849387823294</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.63720930232558</v>
+        <v>0.693096965186939</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.1386061839682</v>
+        <v>1.222243285720168</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.525770796974989</v>
+        <v>1.675343869688469</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.952904664920965</v>
+        <v>2.100999976217281</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.341016686069075</v>
+        <v>2.488124526141519</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.649199417758368</v>
+        <v>1.797742113911177</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.208697340322274</v>
+        <v>2.355498427229307</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.549723274104274</v>
+        <v>2.62955806939123</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.937296037296043</v>
+        <v>3.082678260088279</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.879471485475555</v>
+        <v>2.957520185248136</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.591448007774545</v>
+        <v>2.736441308801545</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>2.532516768737246</v>
+        <v>2.677100406430569</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>2.794243485025284</v>
+        <v>2.938819331034892</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>2.393483124209702</v>
+        <v>2.538767796186505</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>2.488499708114425</v>
+        <v>2.633527890768519</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.437956204379567</v>
+        <v>2.58328487382191</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>2.69166666666667</v>
+        <v>2.836664283257676</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>3.081799591002046</v>
+        <v>3.22558850783988</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>3.005844535359437</v>
+        <v>3.14974254643078</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>2.947286368508237</v>
+        <v>3.09154926157418</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>3.071345029239772</v>
+        <v>3.148784207286361</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 60.58</t>
+          <t>X &gt; 60.56</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.013378594249204</v>
+        <v>0.9653935997923995</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.6782030796048772</v>
+        <v>0.630616801442585</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.098621663137784</v>
+        <v>1.049952878711743</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.9800664451827217</v>
+        <v>1.005646704737053</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.58205856492058</v>
+        <v>1.635680897865868</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.546008892213088</v>
+        <v>1.59976446880723</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.591595141111434</v>
+        <v>1.645052040488942</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.280302400354778</v>
+        <v>2.33266526141194</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.098604179663134</v>
+        <v>2.076975623118621</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.589649721274647</v>
+        <v>2.641355638018233</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.640794702675706</v>
+        <v>2.692532665024139</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.403367465867468</v>
+        <v>3.453902132304229</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.24613815214223</v>
+        <v>3.22227052607218</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.50394800777454</v>
+        <v>2.48113221426155</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.589064387784866</v>
+        <v>2.640225172253054</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>3.035314913596721</v>
+        <v>3.086023684092034</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.901221219447798</v>
+        <v>2.95210654711456</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.573023517638227</v>
+        <v>2.624383228137361</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.640337156760523</v>
+        <v>2.765980404009682</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>3.050595238095234</v>
+        <v>3.10141462408172</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>3.549061495763951</v>
+        <v>3.598987326843769</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>3.398701678216575</v>
+        <v>3.448847160382662</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>3.301453035174902</v>
+        <v>3.351850847604688</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>3.299916457811193</v>
+        <v>3.350312799433418</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 63.19</t>
+          <t>X &gt; 63.17</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1180</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.749607407808526</v>
+        <v>1.782881700127355</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.838160706723521</v>
+        <v>1.871833715336862</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.754392446027218</v>
+        <v>1.789746869695705</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.294836420969652</v>
+        <v>1.331030138388556</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.86177002577611</v>
+        <v>1.927443055671787</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.709951587935443</v>
+        <v>1.775426190921713</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.784543083000052</v>
+        <v>1.850935134149999</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.522937590023872</v>
+        <v>2.589672841939304</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.564453655046506</v>
+        <v>2.631160023854008</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.553330108683852</v>
+        <v>2.620956212224293</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.08192666393478</v>
+        <v>3.149253142521808</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.565544624866668</v>
+        <v>3.6332156034806</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.28851103349816</v>
+        <v>3.357511163743119</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.389188120768893</v>
+        <v>2.458466185601615</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2.492968746138366</v>
+        <v>2.563034752427832</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.918537270336024</v>
+        <v>2.9879301489471</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.953935101610824</v>
+        <v>3.02350453739335</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.59471439737996</v>
+        <v>2.664426545436584</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.895583323023637</v>
+        <v>2.965063689072771</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.336864406779661</v>
+        <v>3.40614678717639</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.810613150324073</v>
+        <v>3.880549771752726</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.395675043834011</v>
+        <v>3.465720759496172</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.755195973028009</v>
+        <v>3.824941234690094</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.594508871047672</v>
+        <v>3.66436321875495</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 65.79</t>
+          <t>X &gt; 65.78</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.870719481423741</v>
+        <v>1.946821480016972</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.72840799763766</v>
+        <v>1.708383795347309</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.831619780417491</v>
+        <v>1.908129678878943</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.792850575228186</v>
+        <v>1.773210341517128</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.006172882778877</v>
+        <v>2.01545455105078</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.868361603789516</v>
+        <v>2.87679453290923</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.577655548881104</v>
+        <v>2.586541417419653</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.64914911937025</v>
+        <v>3.657077564188739</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.112073091818161</v>
+        <v>3.12053006402251</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.916829773623455</v>
+        <v>2.925649070066953</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.384053071597044</v>
+        <v>3.392386939589187</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.587119245267758</v>
+        <v>3.59533310454195</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.619812211930082</v>
+        <v>3.628240401847684</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.916295323750106</v>
+        <v>2.925465957000327</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.739524161858427</v>
+        <v>2.749018227820535</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>3.238152196050684</v>
+        <v>3.247066036083382</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.200490517330884</v>
+        <v>3.209488012786053</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.999075085806481</v>
+        <v>3.008308195284727</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.215198248738297</v>
+        <v>3.224199576209053</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.884402121504337</v>
+        <v>3.892740954577846</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>4.209089851368482</v>
+        <v>4.217246809733204</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.747406734009381</v>
+        <v>3.756044393603489</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>3.925749885062402</v>
+        <v>3.93417999240539</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.849808545793934</v>
+        <v>3.858347739182115</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 68.4</t>
+          <t>X &gt; 68.38</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.671090175540968</v>
+        <v>1.754036090127542</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.781348959337613</v>
+        <v>1.864198112689849</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.457461412846136</v>
+        <v>2.539638462991455</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.077743823483708</v>
+        <v>2.160388559232807</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.380625486121133</v>
+        <v>2.492006318053718</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.456431524517676</v>
+        <v>2.456503093695034</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.685792563955857</v>
+        <v>2.685666756856968</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.298106515319255</v>
+        <v>3.297332953928148</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.44875398345993</v>
+        <v>2.448942494018596</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.120352871131473</v>
+        <v>2.120965638894226</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.171994989026324</v>
+        <v>2.172555870600085</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.672411107823137</v>
+        <v>2.67244940374831</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.661505635438445</v>
+        <v>2.661634389172512</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.217431675183605</v>
+        <v>2.218086102269858</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1.78121758536679</v>
+        <v>1.782412215145364</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>2.487636209598413</v>
+        <v>2.488033842316376</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>2.35354251544949</v>
+        <v>2.354116705338903</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.582634823184947</v>
+        <v>2.582980117201821</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.132833709947491</v>
+        <v>3.132575613810239</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.988028953229396</v>
+        <v>3.986829655146451</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>4.112979991892907</v>
+        <v>4.111691718548606</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>3.146156339368346</v>
+        <v>3.145968115315256</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>3.420931505850476</v>
+        <v>3.420442827797309</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>3.90178303963323</v>
+        <v>3.900784100714198</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 71.01</t>
+          <t>X &gt; 70.99</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>745</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.225207453309608</v>
+        <v>1.258481745628437</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.232313817859911</v>
+        <v>2.265986826473252</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.074492548404649</v>
+        <v>3.109846972073136</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.22647104729203</v>
+        <v>2.262664764710934</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.069254953543151</v>
+        <v>3.134927983438828</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.659104130308322</v>
+        <v>3.724578733294592</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.691607125771078</v>
+        <v>3.757999176921025</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.621106171527671</v>
+        <v>4.687841423443103</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.125709484872466</v>
+        <v>4.192415853679968</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.62033044994196</v>
+        <v>3.687956553482401</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.955092401621059</v>
+        <v>3.022418880208086</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.212911249824003</v>
+        <v>3.280582228437936</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.028017346773105</v>
+        <v>3.097017477018063</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.867063220302505</v>
+        <v>1.936341285135228</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>1.476588357104134</v>
+        <v>1.5466543633936</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.668963842967123</v>
+        <v>1.738356721578199</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>1.266413772979277</v>
+        <v>1.335983208761803</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>1.966799484400774</v>
+        <v>2.036511632457398</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2.31715083525205</v>
+        <v>2.386631201301185</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>3.041107382550337</v>
+        <v>3.110389762947065</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>3.437504288988627</v>
+        <v>3.50744091041728</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>2.690408293748703</v>
+        <v>2.760454009410864</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>3.502096211908672</v>
+        <v>3.571841473570757</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>3.963067624318064</v>
+        <v>4.032921972025342</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 73.62</t>
+          <t>X &gt; 73.6</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>610</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.899649086052477</v>
+        <v>1.932923378371306</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.400539145178648</v>
+        <v>1.434212153791989</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.403461631912187</v>
+        <v>3.438816055580673</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.03393061380099</v>
+        <v>2.070124331219894</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.652267386153994</v>
+        <v>2.717940416049672</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.83943199916078</v>
+        <v>2.904906602147051</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.214106850713314</v>
+        <v>3.280498901863261</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.574896467489829</v>
+        <v>4.641631719405261</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.452478106282953</v>
+        <v>4.519184475090455</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.170445974202053</v>
+        <v>4.238072077742494</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.608739667546899</v>
+        <v>4.676066146133927</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.001776911612986</v>
+        <v>4.069447890226918</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.696957824273383</v>
+        <v>3.765957954518342</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.9837977345505</v>
+        <v>3.053075799383222</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>2.652735347972211</v>
+        <v>2.722801354261676</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>1.772385561528026</v>
+        <v>1.841778440139102</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.9825541624610636</v>
+        <v>1.05212359824359</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>1.697242877513325</v>
+        <v>1.766955025569949</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>1.91336604044514</v>
+        <v>1.982846406494275</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>2.428278688524586</v>
+        <v>2.497561068921314</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>2.868684836903682</v>
+        <v>2.938621458332335</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2.792729781261073</v>
+        <v>2.862775496923234</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>3.723242652661234</v>
+        <v>3.792987914323319</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>4.466973444540308</v>
+        <v>4.536827792247585</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 76.22</t>
+          <t>X &gt; 76.21</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.759613534008245</v>
+        <v>4.876186954704309</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.813996252295638</v>
+        <v>1.936199735512808</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.185540768129179</v>
+        <v>3.303791908926712</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.270944242084624</v>
+        <v>2.390437087880763</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.110493734169005</v>
+        <v>3.257051424952728</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.096855134324379</v>
+        <v>3.043216007843697</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.528808279378794</v>
+        <v>3.473672133572585</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.258285762374292</v>
+        <v>5.199468704851562</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.098998614545515</v>
+        <v>5.040555085163057</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>4.927572842330299</v>
+        <v>4.868841813936186</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.804341747999864</v>
+        <v>5.744103860907735</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.525247844524962</v>
+        <v>5.465354457459739</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.601559838889209</v>
+        <v>4.542593192206823</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.576990176449236</v>
+        <v>3.519911109347404</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>2.516452511709133</v>
+        <v>2.460966208560436</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.107496497073484</v>
+        <v>2.053349122487397</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.7685835258161191</v>
+        <v>0.7170271758906921</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>1.065206535423656</v>
+        <v>1.012988075275928</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1.281329698355471</v>
+        <v>1.228879456200254</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>2.472389558232933</v>
+        <v>2.417729274184296</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>2.330795574937788</v>
+        <v>2.275984709424684</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>2.8572501578494</v>
+        <v>2.801341152825202</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>3.132025324331529</v>
+        <v>3.075815865307256</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>4.461706475022901</v>
+        <v>4.402789223306421</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 78.83</t>
+          <t>X &gt; 78.81</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>393</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.832239917404422</v>
+        <v>3.865514209723251</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.733705624134139</v>
+        <v>2.76737863274748</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.566269791091258</v>
+        <v>2.601624214759745</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.615835256524058</v>
+        <v>2.652028973942961</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.01392425012596</v>
+        <v>3.079597280021638</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.201088863132746</v>
+        <v>3.266563466119017</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.700487362121983</v>
+        <v>3.76687941327193</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.457556126272628</v>
+        <v>5.52429137818806</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.990166338877955</v>
+        <v>5.056872707685457</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>3.961878001899883</v>
+        <v>4.029504105440324</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>4.99959604764117</v>
+        <v>5.066922526228197</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.720502144166268</v>
+        <v>4.788173122780201</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.341557999470481</v>
+        <v>3.41055812971544</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.865748262227463</v>
+        <v>2.935026327060186</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1.952364096981519</v>
+        <v>2.022430103270985</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>1.020706589350986</v>
+        <v>1.090099467962062</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-1.149010514467143</v>
+        <v>-1.079441078684617</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-1.508446856771073</v>
+        <v>-1.438734708714449</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.274511989004651</v>
+        <v>-0.2050316229555165</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.1669847328244245</v>
+        <v>0.2362671132211531</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.387143102452427</v>
+        <v>0.4570797238810798</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>0.5656409730184677</v>
+        <v>0.6356866886806287</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>1.094869065709254</v>
+        <v>1.164614327371339</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>3.309004062318643</v>
+        <v>3.37885841002592</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 81.44</t>
+          <t>X &gt; 81.42</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>301</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.136509823485078</v>
+        <v>3.169784115803907</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.14020474073444</v>
+        <v>1.173877749347781</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.687215240103455</v>
+        <v>3.722569663771942</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.634551495016609</v>
+        <v>4.670745212435513</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.269281709992562</v>
+        <v>4.334954739888239</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.791994495756832</v>
+        <v>3.857469098743103</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.009161586294162</v>
+        <v>6.075553637444109</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.059510595260647</v>
+        <v>7.126245847176079</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.1043489194195</v>
+        <v>6.171055288227002</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.333835767786276</v>
+        <v>4.401461871326717</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.940420948522878</v>
+        <v>5.007747427109905</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.664649304184195</v>
+        <v>3.732320282798128</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>1.211254431211991</v>
+        <v>1.28025456145695</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.322123533798901</v>
+        <v>1.391401598631624</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.3334854461021806</v>
+        <v>-0.263419439812715</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-1.067329050965846</v>
+        <v>-0.9979361723547697</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-1.865874572357299</v>
+        <v>-1.796305136574773</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-1.970857988452579</v>
+        <v>-1.901145840395955</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-1.754734825520764</v>
+        <v>-1.685254459471629</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-1.567691029900331</v>
+        <v>-1.498408649503602</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-1.446439611655755</v>
+        <v>-1.376502990227102</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-1.522394667298364</v>
+        <v>-1.452348951636203</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-1.5798454144375</v>
+        <v>-1.510100152775415</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.3375687280216084</v>
+        <v>0.4074230757288859</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 84.04</t>
+          <t>X &gt; 84.03</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>212</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.45795406594732</v>
+        <v>2.491228358266149</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.009571004133186</v>
+        <v>4.043244012746527</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.815153558914965</v>
+        <v>6.850507982583451</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6.101360245721807</v>
+        <v>6.137553963140711</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.094581026735497</v>
+        <v>8.160254056631175</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.866651300119642</v>
+        <v>6.932125903105913</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.037181394480704</v>
+        <v>7.103573445630651</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>7.702022975377247</v>
+        <v>7.768758227292679</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.800142813984777</v>
+        <v>6.866849182792279</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.026307403215348</v>
+        <v>6.093933506755789</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.300666670330685</v>
+        <v>6.367993148917712</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.719685974402964</v>
+        <v>2.787356953016896</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.1801004162931719</v>
+        <v>0.2491005465381306</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.9021398316739138</v>
+        <v>0.9714178965066367</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.7001876337784836</v>
+        <v>-0.630121627489018</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.5768256973646473</v>
+        <v>-0.5074328187535713</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-3.069409957551308</v>
+        <v>-2.999840521768782</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-3.174393373646588</v>
+        <v>-3.104681225589964</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-2.958270210714772</v>
+        <v>-2.888789844665638</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-2.77122641509434</v>
+        <v>-2.701944034697611</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-2.842728710884742</v>
+        <v>-2.77279208945609</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-2.918683766527352</v>
+        <v>-2.848638050865191</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-2.643908600045222</v>
+        <v>-2.574163338383137</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-1.304755599691056</v>
+        <v>-1.234901251983779</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 86.65</t>
+          <t>X &gt; 86.64</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>5.008513324788126</v>
+        <v>4.692486219901369</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>6.469744995772544</v>
+        <v>6.143423707265832</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>9.221661298153464</v>
+        <v>9.467309420139607</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>11.50187996100822</v>
+        <v>11.13530778164926</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>13.53181975682249</v>
+        <v>13.18046969005435</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>11.92257718420055</v>
+        <v>12.17695968567554</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11.14971105214652</v>
+        <v>10.8097729065471</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>12.06876119704711</v>
+        <v>11.72203765227022</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>10.31387007644101</v>
+        <v>9.977810548470643</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>9.540034665671577</v>
+        <v>9.204894872434153</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>8.61678914236775</v>
+        <v>8.288478324119872</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>5.343683262844941</v>
+        <v>5.033538444481401</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.422784858729052</v>
+        <v>2.124662091910999</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>3.399032838113861</v>
+        <v>3.094059405940598</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>2.74010159907656</v>
+        <v>2.43591610836004</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>3.335161648697941</v>
+        <v>3.030303030303031</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.8058583737106986</v>
+        <v>0.5154335123731713</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>0.1020725624058301</v>
+        <v>-0.1846452866860986</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>0.916998120547234</v>
+        <v>0.6264841894763151</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.692365269461078</v>
+        <v>-0.9723842862699357</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.6367632832494508</v>
+        <v>-0.9196923589978709</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-1.910323129311216</v>
+        <v>-2.186014510883169</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-1.635547962829087</v>
+        <v>-1.911539798401115</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.6837202787407648</v>
+        <v>0.3935803293279889</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 89.26</t>
+          <t>X &gt; 89.25</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>6.495370119672927</v>
+        <v>6.8633545672403</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>7.007652232147251</v>
+        <v>6.528577768890486</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>11.50015515789163</v>
+        <v>10.97291166103596</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>15.02364998029169</v>
+        <v>14.46163831386214</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>17.20075307662357</v>
+        <v>16.6468562446762</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>17.38791768963036</v>
+        <v>16.83382243077358</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>15.76759393045769</v>
+        <v>15.22153761242945</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>15.48903928493912</v>
+        <v>14.94332616767637</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>15.53055534996176</v>
+        <v>14.98481334959108</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.90926231207369</v>
+        <v>13.37156153910081</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>11.64124869783309</v>
+        <v>11.12461277790138</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.277409031646314</v>
+        <v>5.803846567730695</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>4.305460186040534</v>
+        <v>3.840348366420798</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>4.931561002124816</v>
+        <v>4.459605624427986</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>4.272629763087515</v>
+        <v>3.801462326847428</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>5.715147439827554</v>
+        <v>5.236185383244205</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>2.191223237204049</v>
+        <v>1.740923708451611</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>2.933697448227413</v>
+        <v>2.476419139084207</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>6.53965111963381</v>
+        <v>6.053655057823654</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>3.336864406779661</v>
+        <v>2.87915632997656</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>2.793663997781707</v>
+        <v>2.33661016201053</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>0.1753360607831596</v>
+        <v>-0.2602442027599139</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-1.244804026971991</v>
+        <v>-1.666441759185417</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>0.3741698879968212</v>
+        <v>-0.06160174350113579</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 91.87</t>
+          <t>X &gt; 91.85</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>4.296893087002829</v>
+        <v>4.330167379321658</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>9.758819021633855</v>
+        <v>9.792492030247196</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>15.56549536914193</v>
+        <v>15.60084979281041</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>22.09807886754297</v>
+        <v>22.13427258496188</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>26.08063516947544</v>
+        <v>26.14630819937112</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>26.26779978248223</v>
+        <v>26.3332743854685</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>24.04565828810937</v>
+        <v>24.11205033925932</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>22.31782828027197</v>
+        <v>22.3845635321874</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>20.91006898297576</v>
+        <v>20.97677535178326</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>18.68695820988749</v>
+        <v>18.75458431342793</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>18.96131747700282</v>
+        <v>19.02864395558985</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>15.78367284889023</v>
+        <v>15.85134382750417</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>13.20990626808426</v>
+        <v>13.27890639832922</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>15.88710018168759</v>
+        <v>15.95637824652032</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>13.77889358033143</v>
+        <v>13.8489595866209</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>11.47540290531514</v>
+        <v>11.54479578392622</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>9.892033848847376</v>
+        <v>9.961603284629902</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>12.68560115738978</v>
+        <v>12.75531330544641</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>20.1481011319158</v>
+        <v>20.21758149796494</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>15.98731884057972</v>
+        <v>16.05660122097645</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>18.34266915621944</v>
+        <v>18.41260577764809</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>13.9188880136203</v>
+        <v>13.98893372928246</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>14.19366318010243</v>
+        <v>14.26340844176451</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>12.66844647851513</v>
+        <v>12.73830082622241</v>
       </c>
     </row>
   </sheetData>
@@ -5824,2461 +5824,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 16.26</t>
+          <t>X &lt; 16.23</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2.847617724683985</v>
+        <v>2.241505827744504</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.183209963873381</v>
+        <v>-5.446212147075897</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.522017108272365</v>
+        <v>1.939298215657814</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4.706774519716895</v>
+        <v>4.167520666803306</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>5.790780097011677</v>
+        <v>6.772906664844271</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.528669347699633</v>
+        <v>5.489284615647534</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>5.205078577964436</v>
+        <v>6.1879241670513</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.926523932445875</v>
+        <v>5.909712722298224</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>6.417315359787345</v>
+        <v>7.421788139507044</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.643479949017916</v>
+        <v>6.648872463470553</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.816389940770932</v>
+        <v>9.864108576220723</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>8.537296037296031</v>
+        <v>9.585359172772726</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>8.862080181127745</v>
+        <v>9.93278534121071</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>11.53927409473106</v>
+        <v>12.65288293535237</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>10.88034285569376</v>
+        <v>11.99473963777181</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>12.92467826763399</v>
+        <v>14.05971479500892</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>14.23985993580389</v>
+        <v>13.92579765803144</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>15.58415188202747</v>
+        <v>15.29154518950438</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>17.24955040727811</v>
+        <v>16.97802480572282</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>18.88586956521739</v>
+        <v>18.63545885098496</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>16.89339379390059</v>
+        <v>16.62232444772481</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>13.9188880136203</v>
+        <v>13.60530201572748</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>12.7443878177836</v>
+        <v>12.40918849291542</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>12.66844647851513</v>
+        <v>12.33335623969214</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 18.87</t>
+          <t>X &lt; 18.84</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>109</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.507696776067384</v>
+        <v>4.540971068386213</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.282024193122403</v>
+        <v>-1.248351184509062</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.9146389791551002</v>
+        <v>0.949993402823587</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.7082452431289639</v>
+        <v>-0.6720515257100601</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.7446667900288091</v>
+        <v>0.8103398199244864</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.795441324237139</v>
+        <v>-1.729966721250868</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.386489274472986</v>
+        <v>-4.320097223323039</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.937771192718813</v>
+        <v>-1.871035940803381</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.9871642186052725</v>
+        <v>-0.9204578497977707</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.579181447556522</v>
+        <v>-3.511555344016081</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.5775494531684515</v>
+        <v>-0.5102229745814242</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.779720279720287</v>
+        <v>2.84739125833422</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>7.109774515778604</v>
+        <v>7.178774646023562</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.888417704744249</v>
+        <v>6.957695769576972</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>6.229486465706948</v>
+        <v>6.299552471996414</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>8.642728333510128</v>
+        <v>8.712121212121204</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>9.417725548452125</v>
+        <v>9.487294984234651</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>12.69889726163123</v>
+        <v>12.10972700768619</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>14.74988280988415</v>
+        <v>14.14380020679233</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>13.10206422018348</v>
+        <v>12.51246419857854</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>12.55886381118552</v>
+        <v>11.96991803061251</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>9.730615177561269</v>
+        <v>9.80066089322343</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>9.087959151382854</v>
+        <v>9.157704413044939</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>9.012017812114387</v>
+        <v>9.081872159821664</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 21.47</t>
+          <t>X &lt; 21.45</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>148</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.043999399618336</v>
+        <v>3.692486219901369</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.9891626922072021</v>
+        <v>-0.9554896835938607</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.9268415416932356</v>
+        <v>0.9621959653617225</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.555330107694715</v>
+        <v>1.591523825113619</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.190060322670668</v>
+        <v>1.255733352566345</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.307338822711813</v>
+        <v>-1.241864219725542</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.42248683396047</v>
+        <v>-3.356094782810523</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.687618660687086</v>
+        <v>-1.620883408771654</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.3038207164698221</v>
+        <v>-0.2371143476623203</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.077656127239251</v>
+        <v>-1.01003002369881</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.881266898265352</v>
+        <v>1.948593376852379</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.957877692777025</v>
+        <v>5.025548671390958</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8.531373051471085</v>
+        <v>8.600373181716044</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>7.638875300839423</v>
+        <v>7.708153365672146</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>6.979944061802122</v>
+        <v>7.050010068091588</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>7.575004111423503</v>
+        <v>7.644396990034579</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>8.78319229646921</v>
+        <v>8.852761732251736</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>11.16777898739369</v>
+        <v>10.76134384722249</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>12.0595778260012</v>
+        <v>11.64837616774414</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>10.89527027027027</v>
+        <v>10.49294009851754</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>10.35206986127232</v>
+        <v>9.950393930551506</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>9.600439129954033</v>
+        <v>9.670484845616194</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>9.199538620760485</v>
+        <v>9.26928388242257</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>8.44792160581634</v>
+        <v>8.517775953523618</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 24.08</t>
+          <t>X &lt; 24.06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.398342362365149</v>
+        <v>0.6860759634911062</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.009296920395123</v>
+        <v>-4.217169805501591</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.992686704869612</v>
+        <v>-3.957332281201126</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.70648001806277</v>
+        <v>-4.907084785133563</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.644565337067398</v>
+        <v>-3.291655745485713</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-3.428274510468377</v>
+        <v>-3.824440874548543</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.172014428930176</v>
+        <v>-5.576781715301642</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.965132181244847</v>
+        <v>-5.364797081623337</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.467305436610566</v>
+        <v>-3.852721664414524</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.27026706097223</v>
+        <v>-3.645245183588273</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.5687233278374748</v>
+        <v>-0.9202051492694849</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.064804127910925</v>
+        <v>1.742221917870758</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.882060482239311</v>
+        <v>2.57984416474013</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.146140564408853</v>
+        <v>2.848961366724915</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>2.487209325371552</v>
+        <v>2.190818069144356</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>2.596832481789036</v>
+        <v>2.295008912655973</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>3.433612574047892</v>
+        <v>3.631680010972616</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>5.099881821935554</v>
+        <v>4.99742754244555</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>5.803809862916161</v>
+        <v>5.703515001801257</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>4.527439024390247</v>
+        <v>4.419772576475154</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>3.984238615392293</v>
+        <v>3.877226408509124</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>3.908283559749684</v>
+        <v>4.115299118016672</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>5.158668482329368</v>
+        <v>5.374995505375566</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>4.107117386963345</v>
+        <v>4.31394157727545</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 26.69</t>
+          <t>X &lt; 26.66</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1991180308689167</v>
+        <v>-0.330742583815244</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-5.246046037002891</v>
+        <v>-5.723875660033528</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-5.272318939251576</v>
+        <v>-5.238204364321547</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.159257128769823</v>
+        <v>-3.309695571804809</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.757742461497052</v>
+        <v>-2.045426322060742</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.8638640675715408</v>
+        <v>-0.9562723305351923</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.050157761463026</v>
+        <v>-3.146660730737601</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-4.035426187900306</v>
+        <v>-4.134092033646709</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.640553232418306</v>
+        <v>-3.737994922653982</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.294247300431557</v>
+        <v>-2.383251024222396</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.9598173619381214</v>
+        <v>-1.045361594826424</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.234586967802521</v>
+        <v>1.158158505271679</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.290307763449654</v>
+        <v>3.226485800117686</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.715594061955933</v>
+        <v>2.650796994593072</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>2.410019713377999</v>
+        <v>2.347263626090538</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1.945009091621287</v>
+        <v>1.877820760799487</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.7508447260942646</v>
+        <v>1.034683765665989</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>2.278570630100226</v>
+        <v>1.993672849078841</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>3.427280047795932</v>
+        <v>3.273394017237209</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>2.902580071174377</v>
+        <v>2.751019969049203</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>4.138739092781414</v>
+        <v>3.626913517395238</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>4.062784037138805</v>
+        <v>3.776957866679957</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>6.116918634225904</v>
+        <v>6.064650677789359</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>4.61748975047346</v>
+        <v>4.560246995994667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 29.3</t>
+          <t>X &lt; 29.27</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>380</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.6871084187378145</v>
+        <v>-0.9416183216581899</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.790546920395123</v>
+        <v>-5.006551746833331</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.057352475865073</v>
+        <v>-5.284443994404498</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.899083125872849</v>
+        <v>-3.017788690100076</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.958869882176273</v>
+        <v>-2.176673167088502</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.988415451937108</v>
+        <v>-1.067087933372072</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.500184978247013</v>
+        <v>-1.433792927097066</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.300932835253825</v>
+        <v>-2.234197583338393</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-3.042706587463556</v>
+        <v>-2.976000218656054</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.988865758024112</v>
+        <v>-1.921239654483671</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.714506490908775</v>
+        <v>-1.647180012321748</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1659241541748031</v>
+        <v>-0.09825317556087043</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.581647290523435</v>
+        <v>1.650647420768394</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.8380972680008298</v>
+        <v>0.9073753328335528</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>1.484649057684145</v>
+        <v>1.55471506397361</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>1.29641929007316</v>
+        <v>1.365812168684236</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.6401323844359865</v>
+        <v>0.7097018202185126</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.9548173346414686</v>
+        <v>0.8659577221414523</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1.855279039025241</v>
+        <v>1.604042314554036</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.940789473684212</v>
+        <v>1.529791518777934</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>1.923904854159943</v>
+        <v>1.509438562300147</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>2.637423482727854</v>
+        <v>2.379555172487571</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>3.701672333420511</v>
+        <v>3.604958139356661</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>2.836257309941516</v>
+        <v>2.906111657648793</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 31.9</t>
+          <t>X &lt; 31.88</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>483</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.140379074462452</v>
+        <v>-2.218082885789684</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.648641182690206</v>
+        <v>-5.706784807912129</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-5.551666788998709</v>
+        <v>-5.617724593465837</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.185377966668263</v>
+        <v>-3.16136180643138</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.988019414936652</v>
+        <v>-5.027961223294582</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.131450284476067</v>
+        <v>-2.271314490524716</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.493638798460289</v>
+        <v>-2.520620979402338</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.77219344397885</v>
+        <v>-2.798832424155414</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.141354997026021</v>
+        <v>-3.168867875985569</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.067141126481282</v>
+        <v>-2.089931700170212</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.203459477435771</v>
+        <v>-2.021633374880714</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2238264815266788</v>
+        <v>-0.03700829273199702</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.08905396323051917</v>
+        <v>0.2801588585188739</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.2783747702659909</v>
+        <v>0.4706026158171426</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.6461375764032269</v>
+        <v>0.841265902598721</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>1.035858816989702</v>
+        <v>1.229891507669279</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.2857486957360535</v>
+        <v>0.4786904200745354</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.7156602019415814</v>
+        <v>0.7853723499982053</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.293626307472351</v>
+        <v>2.235831632157094</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>2.401859504132233</v>
+        <v>2.216916125252702</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>3.021758183134551</v>
+        <v>2.703176541648808</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>3.152842464966064</v>
+        <v>2.962488189165924</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>3.841696306396436</v>
+        <v>3.780117029619362</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>3.765754967127968</v>
+        <v>3.835609314835246</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 34.51</t>
+          <t>X &lt; 34.49</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.782711357128434</v>
+        <v>-2.834395500528743</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.171634582732786</v>
+        <v>-4.217950244576613</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.554688441391832</v>
+        <v>-4.766393769874256</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.829457364341081</v>
+        <v>-2.966143171503482</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.495540157495206</v>
+        <v>-4.676673167088495</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.68235928432582</v>
+        <v>-2.779486307355818</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.154412408249776</v>
+        <v>-2.161376465253738</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.945162175719553</v>
+        <v>-1.950988561472613</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.391450988745703</v>
+        <v>-2.235234278580705</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.701871765368786</v>
+        <v>-1.70521835852599</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.915317376302234</v>
+        <v>-1.919758064898268</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.218801523679574</v>
+        <v>-1.221308771277862</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.879878108020371</v>
+        <v>-0.8786727925313755</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.4508284149896866</v>
+        <v>-0.4482858709323594</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.1341498979294258</v>
+        <v>-0.1292304714445152</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.5146996044056067</v>
+        <v>-0.5120422465699264</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.323590046522007</v>
+        <v>-0.3202264845246034</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.1690464373796061</v>
+        <v>-0.2622007388343803</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.123111179909742</v>
+        <v>0.9308893391583482</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>1.572712418300661</v>
+        <v>1.280601598637773</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>1.783927250576511</v>
+        <v>1.389521228717349</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>2.792729781261073</v>
+        <v>2.392366596861727</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>3.006399669000842</v>
+        <v>2.605266924287967</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>3.258865554691326</v>
+        <v>2.958657096532427</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 37.12</t>
+          <t>X &lt; 37.09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.854449274603255</v>
+        <v>-3.028602215472787</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-4.898489806852034</v>
+        <v>-5.065542167912568</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.901052179001809</v>
+        <v>-5.072578840758204</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.560050971647023</v>
+        <v>-3.667580586812889</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.747238564890246</v>
+        <v>-4.8892000383021</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-3.190210938184826</v>
+        <v>-3.261722636568422</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.867186659279952</v>
+        <v>-2.863556507523057</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.008755003428647</v>
+        <v>-3.004593741027847</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.830252637036153</v>
+        <v>-2.825932347864857</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.508197636846674</v>
+        <v>-2.501454333915063</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.370824671101204</v>
+        <v>-2.364568903001434</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.964987067726788</v>
+        <v>-1.957447250207998</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.993587875255031</v>
+        <v>-1.98321562707784</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.666999480809935</v>
+        <v>-1.655597658531278</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-2.325930719847236</v>
+        <v>-2.313740956111836</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-2.415802177075165</v>
+        <v>-2.405225090410276</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-2.549895871224088</v>
+        <v>-2.53914222738775</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.890649811775845</v>
+        <v>-1.9581118749675</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.045560279136915</v>
+        <v>-1.193523649050029</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.365371389270976</v>
+        <v>-0.5951552053371501</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.5518092244249573</v>
+        <v>-0.8633529508066076</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.2817066043249525</v>
+        <v>-0.03399985886851198</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.2253710830570341</v>
+        <v>-0.08980009839456216</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.978159025556522</v>
+        <v>0.7428522695090223</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 39.72</t>
+          <t>X &lt; 39.7</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.737353255867887</v>
+        <v>-2.82309010408617</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.247280507733933</v>
+        <v>-3.332349057980615</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.336321328143235</v>
+        <v>-3.423010642311603</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.22851839720493</v>
+        <v>-3.254381270994088</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-3.593788182228977</v>
+        <v>-3.645486044352083</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.350285541053182</v>
+        <v>-2.338876025812347</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.005780781088433</v>
+        <v>-3.047369950595758</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.93222275055065</v>
+        <v>-2.97264021887824</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.421223117452897</v>
+        <v>-2.460564801669427</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.373462284090877</v>
+        <v>-2.409951065941208</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.981732124956764</v>
+        <v>-2.018244364955756</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.908713352375329</v>
+        <v>-1.944052591933165</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.742124758655898</v>
+        <v>-1.773097011730464</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.611368893633909</v>
+        <v>-1.523587652882931</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-2.03555834863365</v>
+        <v>-1.946436832816431</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.909981867087382</v>
+        <v>-1.822638146167563</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.741338654090342</v>
+        <v>-1.721261165497971</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.425225782081661</v>
+        <v>-1.473160692848559</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.6692287190597739</v>
+        <v>-0.7866810766301242</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.2948113207547181</v>
+        <v>-0.3645411490150394</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.5321319320203841</v>
+        <v>-0.7198774507023984</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.1832807601488398</v>
+        <v>-0.3722229565255688</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.1927530792235217</v>
+        <v>-0.3816303139461752</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.4413647531056455</v>
+        <v>0.3218140341574411</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 42.33</t>
+          <t>X &lt; 42.31</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.956908290996694</v>
+        <v>-3.079049360622975</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.034937946036145</v>
+        <v>-3.157628001761331</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.600948103167092</v>
+        <v>-3.72479956265515</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.185377966668263</v>
+        <v>-3.257744521239125</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-3.961325369762115</v>
+        <v>-3.949566939982276</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.644797307063342</v>
+        <v>-2.579322704077072</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.725671652669725</v>
+        <v>-3.604410032815693</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.435482114890171</v>
+        <v>-3.471521785893536</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.085641281111101</v>
+        <v>-3.0189349123036</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.037277308530072</v>
+        <v>-2.969651204989631</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.660143118495931</v>
+        <v>-2.592816639908904</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.630912253214404</v>
+        <v>-2.609024753637357</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.00822978208182</v>
+        <v>-1.98321562707784</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.715711978522137</v>
+        <v>-1.689891211343351</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-2.06631844880301</v>
+        <v>-2.039392533615263</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.925921124028207</v>
+        <v>-1.959408903853351</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-1.79470774431072</v>
+        <v>-1.887564723958391</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.324558711129562</v>
+        <v>-1.478002135598508</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.9449127326689322</v>
+        <v>-1.159230096237962</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.3873966942148783</v>
+        <v>-0.60334892753324</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.7661838629793394</v>
+        <v>-0.9822844061259985</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.7809049470422167</v>
+        <v>-0.9973811628070948</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.8592766712154258</v>
+        <v>-1.075254871207093</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.038844953489082</v>
+        <v>-1.193926441736167</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 44.94</t>
+          <t>X &lt; 44.92</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.461183400359957</v>
+        <v>-2.521778178785596</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.66037605708577</v>
+        <v>-2.721143625043432</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.243776862429051</v>
+        <v>-3.306019642427117</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.057480166621311</v>
+        <v>-3.074532348298604</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.142821958846078</v>
+        <v>-4.171282331508984</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-3.145576337738476</v>
+        <v>-3.127939252316914</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.14078902877273</v>
+        <v>-4.122077421342837</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.650206638247134</v>
+        <v>-3.680216858895193</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.157833945632071</v>
+        <v>-3.188684672480029</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.029956101216655</v>
+        <v>-3.061510339515621</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.116282136175258</v>
+        <v>-3.098265562624015</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.03469073757622</v>
+        <v>-2.967019758962287</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.995070143619714</v>
+        <v>-1.926070013374755</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.036084303617102</v>
+        <v>-1.966806238784379</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-2.101658923200183</v>
+        <v>-2.083921583254032</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-2.176849559238491</v>
+        <v>-2.210905265458912</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-1.987830920395488</v>
+        <v>-2.074308425880936</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.497623972126902</v>
+        <v>-1.638121176591213</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.8663916217073862</v>
+        <v>-1.008808916935919</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.7167951042611023</v>
+        <v>-0.8594664904253122</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-1.025278448925356</v>
+        <v>-1.168336120299863</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-1.047743112233654</v>
+        <v>-1.191078074770253</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-1.083016661794801</v>
+        <v>-1.225721993018091</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.249867091972355</v>
+        <v>-1.339247888087712</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 47.55</t>
+          <t>X &lt; 47.52</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.62910532858038</v>
+        <v>-2.718633801483293</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.681863292076535</v>
+        <v>-2.691514762504092</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.355599638909602</v>
+        <v>-3.365450189728442</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.264239973036737</v>
+        <v>-3.232706305014354</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-4.434662737126807</v>
+        <v>-4.410899118128611</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.522860442960599</v>
+        <v>-3.457385839974329</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-4.656066594815812</v>
+        <v>-4.589674543665865</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.924574711780394</v>
+        <v>-3.900923861102257</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.274932947051965</v>
+        <v>-3.295375438252819</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.358884781379395</v>
+        <v>-3.423649696078201</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.003750069999114</v>
+        <v>-3.105530892469993</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.121293084944135</v>
+        <v>-3.178729513549271</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.776093052384851</v>
+        <v>-1.834296289502952</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.789134516497306</v>
+        <v>-1.847331054851644</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.834554756229025</v>
+        <v>-1.939589146288299</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.921585796444191</v>
+        <v>-2.072768917958896</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-1.927846965003603</v>
+        <v>-2.079342262014251</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.498946179331476</v>
+        <v>-1.651774648552305</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.154245257846263</v>
+        <v>-1.307798437675025</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.244918699186989</v>
+        <v>-1.398175040527846</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.496719530234735</v>
+        <v>-1.650211839517361</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.525100090047722</v>
+        <v>-1.678780748166048</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.854669621711814</v>
+        <v>-2.007358613732123</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.638714785877148</v>
+        <v>-1.792188201029632</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 50.15</t>
+          <t>X &lt; 50.13</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.78531171223689</v>
+        <v>-1.862753230074922</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.512863254203964</v>
+        <v>-1.591282274771103</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.486827505823157</v>
+        <v>-2.564640111809929</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.558222532078418</v>
+        <v>-2.598443024446539</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.708645778915454</v>
+        <v>-3.751973758080965</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.412324441120255</v>
+        <v>-3.456006562922397</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-4.075877798743569</v>
+        <v>-4.118798522024335</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.386594186606189</v>
+        <v>-3.468438538205973</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.733764075441343</v>
+        <v>-2.855522784862707</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.038676107624248</v>
+        <v>-3.160655350514226</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.907583316153605</v>
+        <v>-2.990389446164201</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.003922600696789</v>
+        <v>-3.015171375881962</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.721580642692778</v>
+        <v>-1.735004984088462</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.542698917327158</v>
+        <v>-1.556478228468002</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-2.016333805975407</v>
+        <v>-2.071252350421325</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-2.098399697337513</v>
+        <v>-2.152623798965266</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-2.047284261881423</v>
+        <v>-2.1018194189501</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.822803387637919</v>
+        <v>-1.877995040380682</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.420833420980657</v>
+        <v>-1.476747469830109</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.768655371304973</v>
+        <v>-1.82370323111406</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-2.125992616790157</v>
+        <v>-2.180877178498029</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-2.376826944784973</v>
+        <v>-2.431314359929409</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-2.493946772146877</v>
+        <v>-2.547976781269242</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-2.311590617904123</v>
+        <v>-2.366159930412273</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 52.76</t>
+          <t>X &lt; 52.74</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1568</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.754675213176846</v>
+        <v>-1.721400920858017</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.301488356163382</v>
+        <v>-1.330787639741473</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.951832923233624</v>
+        <v>-1.979490471839867</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.161530458228924</v>
+        <v>-2.091288026913773</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.871061743732511</v>
+        <v>-2.897718683086701</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.523861169376218</v>
+        <v>-2.487542478826626</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.073357961341664</v>
+        <v>-3.099170329622922</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.875576280871343</v>
+        <v>-2.935183416827037</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.483543945073492</v>
+        <v>-2.480048701424018</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.779917460436742</v>
+        <v>-2.775542463790664</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.885064834687626</v>
+        <v>-2.846241386549202</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.74962379392759</v>
+        <v>-2.710211367032827</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.749112006185825</v>
+        <v>-1.707041692264262</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.74391320895549</v>
+        <v>-1.764849915555907</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.858943810421501</v>
+        <v>-1.852289345032474</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-2.242135533587231</v>
+        <v>-2.236194431625904</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-2.085881955155379</v>
+        <v>-2.079804582864924</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-2.090746374054156</v>
+        <v>-2.084566627522307</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-1.901522498735496</v>
+        <v>-1.895614923531888</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-2.1867048346056</v>
+        <v>-2.181035685761032</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-2.438887869214376</v>
+        <v>-2.432604971528562</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-2.350843362729741</v>
+        <v>-2.3444919145835</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-2.358003625118279</v>
+        <v>-2.351993226426238</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-2.269811433345268</v>
+        <v>-2.263732595842072</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 55.37</t>
+          <t>X &lt; 55.35</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.260719929316956</v>
+        <v>-1.343626466806889</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.9979332840314825</v>
+        <v>-1.081185773302778</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.270486867141862</v>
+        <v>-1.353449888694662</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.302074381585733</v>
+        <v>-1.35386970752824</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.749903486111428</v>
+        <v>-1.829073069630525</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.645392170203912</v>
+        <v>-1.724795555670134</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.045424871905155</v>
+        <v>-2.12420546567828</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.34958160452922</v>
+        <v>-2.459332106788793</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.877596477338557</v>
+        <v>-1.987966650791762</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.106381572018478</v>
+        <v>-2.216554049014782</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.573608157726873</v>
+        <v>-2.594808856202661</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.821151451288429</v>
+        <v>-2.842076148189669</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.372080008908597</v>
+        <v>-2.392624274690434</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.218075801749265</v>
+        <v>-2.181497418731013</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-2.272514677803642</v>
+        <v>-2.325648711742765</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-2.61689305196937</v>
+        <v>-2.669696969696972</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.317717028432924</v>
+        <v>-2.428085233032363</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-2.447124575963478</v>
+        <v>-2.55742506221187</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-2.026227176709263</v>
+        <v>-2.079855931002328</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-2.264908256880737</v>
+        <v>-2.375591617312324</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.545853880024914</v>
+        <v>-2.6562867102054</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.416658334904632</v>
+        <v>-2.527320758152719</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-2.510879436584624</v>
+        <v>-2.621522586697154</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-2.553942327082069</v>
+        <v>-2.664617691556593</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 57.97</t>
+          <t>X &lt; 57.95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.9006636556211944</v>
+        <v>-0.8947331237946585</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.8453965054573658</v>
+        <v>-0.8911241709834385</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.9601546237132297</v>
+        <v>-1.056796487783728</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.8149194619527123</v>
+        <v>-0.8593421800479391</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.203385158023146</v>
+        <v>-1.270279456956466</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.50721603601184</v>
+        <v>-1.626070617354763</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.835550873300562</v>
+        <v>-1.953814857040669</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.137373879314211</v>
+        <v>-2.255378587236514</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.598588192861101</v>
+        <v>-1.71697662758605</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.030885993011061</v>
+        <v>-2.148628837934957</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.300511223029645</v>
+        <v>-2.366283580642026</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.602780431247581</v>
+        <v>-2.720376044711884</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.550679792563038</v>
+        <v>-2.61551865191938</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.324905506491291</v>
+        <v>-2.441934334278493</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2.275142065031254</v>
+        <v>-2.391850071180663</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-2.485798312257891</v>
+        <v>-2.602856238626465</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-2.171876694574067</v>
+        <v>-2.289089550770576</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-2.246786205414175</v>
+        <v>-2.363969708561484</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-2.209872157734516</v>
+        <v>-2.327291463044098</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-2.411649214659683</v>
+        <v>-2.529160843046498</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-2.715476469762756</v>
+        <v>-2.832556981286587</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-2.656629259189835</v>
+        <v>-2.773769256573999</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.613979144513969</v>
+        <v>-2.731396042785661</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-2.712425519903292</v>
+        <v>-2.777381290768389</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 60.58</t>
+          <t>X &lt; 60.56</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7724427486764611</v>
+        <v>-0.7419491738057147</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.6503717764411832</v>
+        <v>-0.6199192137952068</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.9602791895700733</v>
+        <v>-0.9292304907887896</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.927440073274802</v>
+        <v>-0.9442553295837257</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.314220982458195</v>
+        <v>-1.349569401914643</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.292818946614751</v>
+        <v>-1.328255080346132</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.317706205689909</v>
+        <v>-1.352992247568373</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.761902787784003</v>
+        <v>-1.796735241502681</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.645456335732241</v>
+        <v>-1.63233856167848</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.958932717481197</v>
+        <v>-1.993487271568789</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.994855039148739</v>
+        <v>-2.029459635849861</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.488097726766959</v>
+        <v>-2.522200614147827</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.379766334109583</v>
+        <v>-2.365584609179081</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.897998581672041</v>
+        <v>-1.884243390587848</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.949697942352408</v>
+        <v>-1.984006708813141</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-2.244403857969878</v>
+        <v>-2.278577278577274</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-2.157475470924823</v>
+        <v>-2.191735787022097</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.944511252556111</v>
+        <v>-1.978986211461809</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.990684337468515</v>
+        <v>-2.073520413621566</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.259801548886742</v>
+        <v>-2.294112203742536</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.581638665656548</v>
+        <v>-2.615559385053579</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-2.484465542159938</v>
+        <v>-2.518495034554398</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-2.424179134804099</v>
+        <v>-2.458351743518136</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-2.423837641306626</v>
+        <v>-2.458025429254505</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 63.19</t>
+          <t>X &lt; 63.17</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2226</v>
+        <v>2230</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.028501130072712</v>
+        <v>-1.044309164031169</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.16232183142715</v>
+        <v>-1.178110590289776</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.154382342202666</v>
+        <v>-1.171084098085096</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.9535297893930306</v>
+        <v>-0.9710414246999548</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.249664046172853</v>
+        <v>-1.282307417231422</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.171555406233573</v>
+        <v>-1.204246889481212</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.206494948691763</v>
+        <v>-1.239626292384806</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.593922356452495</v>
+        <v>-1.626560914493979</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.61675328192927</v>
+        <v>-1.649350338155742</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.606778850153923</v>
+        <v>-1.639897590005376</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.88779347444418</v>
+        <v>-1.920266341824977</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.141881800058741</v>
+        <v>-2.174099293932429</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.98966873207771</v>
+        <v>-2.022880459246011</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.514574651736488</v>
+        <v>-1.548797736916541</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.565917235737025</v>
+        <v>-1.600484070291138</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.795132820555132</v>
+        <v>-1.82894629945568</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.813801545143939</v>
+        <v>-1.847690995364651</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.624045094752965</v>
+        <v>-1.658365365057342</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.785262083383763</v>
+        <v>-1.819185353508658</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-2.020739910313907</v>
+        <v>-2.054150923094767</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-2.269030377593737</v>
+        <v>-2.302361414080721</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-2.049810760870365</v>
+        <v>-2.083607956863709</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-2.242954613380704</v>
+        <v>-2.276259868410285</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-2.158304566447569</v>
+        <v>-2.191835002724105</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 65.79</t>
+          <t>X &lt; 65.78</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2369</v>
+        <v>2372</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.9149240813360748</v>
+        <v>-0.9477364662503405</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9352693168819499</v>
+        <v>-0.9263340203866264</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.013850940966613</v>
+        <v>-1.04673949236313</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.035122217138628</v>
+        <v>-1.026262532094975</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.126050432447201</v>
+        <v>-1.129890589565655</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.502186192272326</v>
+        <v>-1.505546789717961</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.371934675676968</v>
+        <v>-1.37554073335005</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.836761091708709</v>
+        <v>-1.839819251295239</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.604156286939613</v>
+        <v>-1.607512730401034</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.515320004760952</v>
+        <v>-1.518870744458042</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.720973619262651</v>
+        <v>-1.724250037665087</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.808497046842277</v>
+        <v>-1.811699650756694</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.816887057941805</v>
+        <v>-1.820195330705552</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.509686922868589</v>
+        <v>-1.513413306066127</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.429355953438254</v>
+        <v>-1.433256508187625</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.650995611875572</v>
+        <v>-1.654570919276793</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.634463003736435</v>
+        <v>-1.638082370650906</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.546588011183822</v>
+        <v>-1.550338746576358</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.642919954002906</v>
+        <v>-1.64653902906646</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.937157606405393</v>
+        <v>-1.94039775428341</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-2.076716429234047</v>
+        <v>-2.079842734937721</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.875218307322982</v>
+        <v>-1.878616909888265</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.955667217989657</v>
+        <v>-1.958948142269634</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.922801586772614</v>
+        <v>-1.926141825975947</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 68.4</t>
+          <t>X &lt; 68.38</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2508</v>
+        <v>2511</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.691110738030531</v>
+        <v>-0.7205629776782203</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.8077158927271384</v>
+        <v>-0.8370530471943383</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.07968144932903</v>
+        <v>-1.108745646436788</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.9808286723579585</v>
+        <v>-1.010042258801541</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.086825817087067</v>
+        <v>-1.126419073356146</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.115242663040853</v>
+        <v>-1.11527891795096</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.192969922537777</v>
+        <v>-1.192939570848928</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.409749293856983</v>
+        <v>-1.409475340738616</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.108232211254709</v>
+        <v>-1.108322241937692</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.987443288808052</v>
+        <v>-0.9877029587775539</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.007753917486369</v>
+        <v>-1.007989866960045</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.184926184926184</v>
+        <v>-1.184965603986974</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.175259227770432</v>
+        <v>-1.175345460673867</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.016124139432236</v>
+        <v>-1.016412628966187</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.8572329332889765</v>
+        <v>-0.857734685290751</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.113016716352561</v>
+        <v>-1.113206298795816</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.064833641860545</v>
+        <v>-1.065091469660942</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.146504269610325</v>
+        <v>-1.146674913793198</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.344773600634362</v>
+        <v>-1.344709693482272</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.652070063694268</v>
+        <v>-1.65164207288359</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.694385195935432</v>
+        <v>-1.693928067601128</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.348737137947339</v>
+        <v>-1.348701869949352</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.449153116014152</v>
+        <v>-1.448998093821196</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.621477937267414</v>
+        <v>-1.621126389679794</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 71.01</t>
+          <t>X &lt; 70.99</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2661</v>
+        <v>2665</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.4326907053037061</v>
+        <v>-0.4414423515272006</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.7852939386582634</v>
+        <v>-0.7936365652987192</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.049295669343302</v>
+        <v>-1.057723377789692</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.8476097950261519</v>
+        <v>-0.8565783582815882</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.080299288668613</v>
+        <v>-1.097260776200706</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.245711099254947</v>
+        <v>-1.262376167935379</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.251177983821883</v>
+        <v>-1.26810074850777</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.508865022310957</v>
+        <v>-1.525506796318624</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.371727338594397</v>
+        <v>-1.388571825374427</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.227439731328815</v>
+        <v>-1.244766515077188</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.043994003382636</v>
+        <v>-1.061516341408776</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.114780281446947</v>
+        <v>-1.13230107025614</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.057754063426628</v>
+        <v>-1.075743630916243</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.7331744806817184</v>
+        <v>-0.7517349865827612</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.6210412836972097</v>
+        <v>-0.6400001220064553</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.6780932203574963</v>
+        <v>-0.6967826412270881</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.5652375154704643</v>
+        <v>-0.58415302883013</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.7605441614018886</v>
+        <v>-0.7792148254712856</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.8598682517344614</v>
+        <v>-0.8783312198334698</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.063555347091935</v>
+        <v>-1.081663666811963</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.17195416275171</v>
+        <v>-1.190092873026572</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.9629876088388372</v>
+        <v>-0.981477577999776</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.191957307925534</v>
+        <v>-1.210025134020732</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.321063839606531</v>
+        <v>-1.338975732496358</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 73.62</t>
+          <t>X &lt; 73.6</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2796</v>
+        <v>2800</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.4992366948604072</v>
+        <v>-0.5058843079059372</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4606808806506208</v>
+        <v>-0.4674736637307575</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.9229057976867949</v>
+        <v>-0.9294175088453898</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.6585293340380503</v>
+        <v>-0.6656040724540944</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.7909379249719919</v>
+        <v>-0.8043526887020391</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.8327224510705022</v>
+        <v>-0.846038725896328</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.9104203735907177</v>
+        <v>-0.9238342743444221</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.204549933181767</v>
+        <v>-1.217626849894295</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.17861986363615</v>
+        <v>-1.191731868851541</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.113959836427433</v>
+        <v>-1.127372362818164</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.210903283389499</v>
+        <v>-1.224116262239377</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.078088578088575</v>
+        <v>-1.091571627997091</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.006622802613734</v>
+        <v>-1.020507395307575</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.8508423224701644</v>
+        <v>-0.8650153271554899</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.7758611278759489</v>
+        <v>-0.790320986691583</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.587591988108322</v>
+        <v>-0.6021756021755991</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.4152456188037448</v>
+        <v>-0.43011927233173</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.5704581791089893</v>
+        <v>-0.5851476116360388</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.6188092365343891</v>
+        <v>-0.6333833939206741</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.7321428571428612</v>
+        <v>-0.7465164783764493</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.8256673614809813</v>
+        <v>-0.8400582934558471</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.809023227328197</v>
+        <v>-0.823467350691466</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-1.013624130836305</v>
+        <v>-1.027714293904424</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.175865271189423</v>
+        <v>-1.189753004005333</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 76.22</t>
+          <t>X &lt; 76.21</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2908</v>
+        <v>2911</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.8935004572690488</v>
+        <v>-0.9141940800304624</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.4598088657876147</v>
+        <v>-0.4809086032239875</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7204210785748089</v>
+        <v>-0.7410645160651654</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.5958508069640303</v>
+        <v>-0.616532155963462</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.7371482859099387</v>
+        <v>-0.7627287497311102</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.7359744752966009</v>
+        <v>-0.7274526767429563</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.8060696940533987</v>
+        <v>-0.7973699505957583</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.099566989261525</v>
+        <v>-1.090528440104556</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.073003798115735</v>
+        <v>-1.063998519654227</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.040447081306745</v>
+        <v>-1.031368863829591</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.191598191147349</v>
+        <v>-1.182403051686265</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.143069259507612</v>
+        <v>-1.133885760917487</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.9804805528937379</v>
+        <v>-0.9713093562165085</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.8048965204411331</v>
+        <v>-0.7958755478423498</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.6209514063284658</v>
+        <v>-0.6120290971194109</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.5541790115453509</v>
+        <v>-0.5454078295804905</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.3249845716164828</v>
+        <v>-0.3164311046182462</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.3752843229997467</v>
+        <v>-0.3666653007253089</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.4133997860083483</v>
+        <v>-0.4047719343723912</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.6181318681318686</v>
+        <v>-0.6093196779223149</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.5915085505300723</v>
+        <v>-0.5826495116598949</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.6814406880082586</v>
+        <v>-0.6724791276258415</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.7300368811766589</v>
+        <v>-0.7210636079249184</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.9576325040018716</v>
+        <v>-0.9484147304616357</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 78.83</t>
+          <t>X &lt; 78.81</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3013</v>
+        <v>3017</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.5779422226150928</v>
+        <v>-0.5816365871161722</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.5002359648761754</v>
+        <v>-0.5040872220812176</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5050290258787555</v>
+        <v>-0.5091004986666263</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5412938298867473</v>
+        <v>-0.5454313562844817</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.5913850209570413</v>
+        <v>-0.5994098506947552</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.6167124318823767</v>
+        <v>-0.6246799157993124</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.6781184373892728</v>
+        <v>-0.686130662527205</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.9050271127644294</v>
+        <v>-0.9127887807758057</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.8448560644080843</v>
+        <v>-0.8526957965475859</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.7080519163675234</v>
+        <v>-0.7161982761416823</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.8443282791012763</v>
+        <v>-0.8522571780017714</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.807056579783854</v>
+        <v>-0.8150836058573816</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.6229094669053836</v>
+        <v>-0.6313610571108299</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.5602335447670868</v>
+        <v>-0.5688081196623074</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.4385840474992477</v>
+        <v>-0.4474282406155083</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.3202881270237015</v>
+        <v>-0.3292011019283763</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.03742195305299845</v>
+        <v>-0.04673579979613862</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.009842316041982713</v>
+        <v>0.0004436347574312549</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.1518383615581413</v>
+        <v>-0.1609949318876502</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.2102668213457051</v>
+        <v>-0.2193223862368328</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.236502796265853</v>
+        <v>-0.2456147809467808</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.2594954314730629</v>
+        <v>-0.2685946777627635</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.3298647042632723</v>
+        <v>-0.3388331809628795</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.6184215378583602</v>
+        <v>-0.6270251286324537</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 81.44</t>
+          <t>X &lt; 81.42</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3105</v>
+        <v>3109</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.3812825310704895</v>
+        <v>-0.3841421325890479</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2517017812841544</v>
+        <v>-0.2547679552183837</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5225738400154825</v>
+        <v>-0.525464047074756</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.642790697674414</v>
+        <v>-0.6456126402107643</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6061654762964181</v>
+        <v>-0.6120038210892318</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.5611968623269661</v>
+        <v>-0.5670746085666138</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.7716735968770294</v>
+        <v>-0.7773763485484153</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.8719706043293129</v>
+        <v>-0.8775813953488338</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.7802877617288146</v>
+        <v>-0.786014828030801</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.6062005970508153</v>
+        <v>-0.6122452400950209</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.6661843589938599</v>
+        <v>-0.672123853971101</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.5419468244299779</v>
+        <v>-0.5480822204458988</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.3000749415676509</v>
+        <v>-0.3066565894076803</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.3098896059226206</v>
+        <v>-0.3164888467044733</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1469951130867813</v>
+        <v>-0.1538850462262289</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.07876219010053376</v>
+        <v>-0.0856738705631841</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.0009470386009198251</v>
+        <v>-0.00797867663593621</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.009682607503677332</v>
+        <v>0.002620630916894129</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.01220456732460917</v>
+        <v>-0.01921725102280902</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.03115953682856087</v>
+        <v>-0.03813008346449465</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.04046553126307373</v>
+        <v>-0.04749257934307849</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.03277793004127005</v>
+        <v>-0.03982816749334717</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.02845949970382833</v>
+        <v>-0.03548712652850838</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.2140011865412319</v>
+        <v>-0.2208034106588315</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 84.04</t>
+          <t>X &lt; 84.03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3194</v>
+        <v>3198</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.2392441909544019</v>
+        <v>-0.241281761056932</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.4023317462657729</v>
+        <v>-0.4041953403532119</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.6122944295823487</v>
+        <v>-0.6140157473924504</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.5934067524348379</v>
+        <v>-0.5952110262468082</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.7235164428603085</v>
+        <v>-0.7272304742513427</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.6435110627178275</v>
+        <v>-0.6473118139690897</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.6516006812847905</v>
+        <v>-0.6554570423531416</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.6944973326225252</v>
+        <v>-0.6983256392816273</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.6353128913722088</v>
+        <v>-0.6392140391421961</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.580995095255453</v>
+        <v>-0.5850298147508255</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.6005105893194838</v>
+        <v>-0.6045011660256066</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.3626831683600216</v>
+        <v>-0.3669956009124604</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.1898992893554308</v>
+        <v>-0.1945220479337877</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.2367667238109732</v>
+        <v>-0.2413520653810934</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.1279057518164066</v>
+        <v>-0.132683829276381</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.1387150825366561</v>
+        <v>-0.1434337133027057</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.0269101782553065</v>
+        <v>0.0219709167264952</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.03433304144775207</v>
+        <v>0.02937290486018185</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>0.01907530409823011</v>
+        <v>0.01414902750020275</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.005863039399621073</v>
+        <v>0.0009657033198990916</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>0.01298507739553401</v>
+        <v>0.008031120272001147</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>0.01836017991513472</v>
+        <v>0.01339025102159752</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.001070439003505896</v>
+        <v>-0.005996399422265597</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.0896234533317255</v>
+        <v>-0.09444790260268121</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 86.65</t>
+          <t>X &lt; 86.64</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3239</v>
+        <v>3242</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.3326131286202099</v>
+        <v>-0.3177230705529439</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4674385947281507</v>
+        <v>-0.4523395980562839</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.6330464642358535</v>
+        <v>-0.6480897888851018</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.777703247536337</v>
+        <v>-0.7617901133027232</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.8804238958353636</v>
+        <v>-0.8659446438484792</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.7989861368086579</v>
+        <v>-0.815298567318905</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.7562681442518482</v>
+        <v>-0.741754731203315</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.8024548961121951</v>
+        <v>-0.7878281725127394</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.7128165625735363</v>
+        <v>-0.698279046102229</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.6699787535398087</v>
+        <v>-0.655289987750713</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.6239544626730975</v>
+        <v>-0.6093711382457201</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.4548089560393436</v>
+        <v>-0.4403105911377594</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.3000156940116128</v>
+        <v>-0.2853843121409412</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.3493337712343845</v>
+        <v>-0.334599880652263</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.3127213265008564</v>
+        <v>-0.2978581149558579</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.3459885240086891</v>
+        <v>-0.3312354312354273</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.2153893342006512</v>
+        <v>-0.2007209087673942</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.1787832913719782</v>
+        <v>-0.164119835126165</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.2217232037585362</v>
+        <v>-0.2070691271382827</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.139724020968238</v>
+        <v>-0.1251877366704264</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.1402855416321316</v>
+        <v>-0.1256135564444918</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.07437761829683609</v>
+        <v>-0.0597447674740863</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.08975066852880076</v>
+        <v>-0.0751669513899671</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.2090295719746038</v>
+        <v>-0.194313680836224</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 89.26</t>
+          <t>X &lt; 89.25</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3288</v>
+        <v>3291</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.3065587358625521</v>
+        <v>-0.3215954538061325</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.3839192768905875</v>
+        <v>-0.3686211952107001</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.5683687957837691</v>
+        <v>-0.5525318497016585</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.7214364050504685</v>
+        <v>-0.7052741170721788</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.7977913566023105</v>
+        <v>-0.7826291446456821</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.8055056700546572</v>
+        <v>-0.7903804688812954</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.7446243315490406</v>
+        <v>-0.7293530219379605</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.7337210056177739</v>
+        <v>-0.7183845401931066</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.7356022776700328</v>
+        <v>-0.720270861951974</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.6746057083351076</v>
+        <v>-0.6591278924963433</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.5948995674588886</v>
+        <v>-0.57956041680022</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4020979020978999</v>
+        <v>-0.3868585971690521</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3269142879911442</v>
+        <v>-0.3114516631003923</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.348475177994608</v>
+        <v>-0.3329324147198065</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.3221996401192939</v>
+        <v>-0.3065081340642095</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.3764684890847434</v>
+        <v>-0.3608761148924771</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.2498148019410351</v>
+        <v>-0.2342993704706799</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.2760418826566848</v>
+        <v>-0.2604717956336273</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.4062587971388041</v>
+        <v>-0.390621681998482</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.2923754556500597</v>
+        <v>-0.276886056629067</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.2706768599247198</v>
+        <v>-0.2550640304351148</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.1765262853092509</v>
+        <v>-0.1609758285411047</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.126798966446664</v>
+        <v>-0.1113604313930665</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.1846160413198419</v>
+        <v>-0.169101443472286</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 91.87</t>
+          <t>X &lt; 91.85</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3337</v>
+        <v>3341</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1622166438460368</v>
+        <v>-0.162844735310685</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.3326074294752104</v>
+        <v>-0.3330428829384857</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.4757990521405802</v>
+        <v>-0.476105780562925</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.6370236437572316</v>
+        <v>-0.6371593128946031</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.7175718057020362</v>
+        <v>-0.7183398337551665</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.7224159889167154</v>
+        <v>-0.7231735739397109</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.6736904453950814</v>
+        <v>-0.6745289738238682</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.6371720006791222</v>
+        <v>-0.6380627775353105</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.6085571454874525</v>
+        <v>-0.6094815793459389</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.5597299948015717</v>
+        <v>-0.5607356718849275</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.5666946363434846</v>
+        <v>-0.5676848925084599</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.5002276016011464</v>
+        <v>-0.5013059734527801</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.4426312624336362</v>
+        <v>-0.4438115982810729</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.4970292355279256</v>
+        <v>-0.4981518742742637</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.4509460724661878</v>
+        <v>-0.4521435931324973</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.4060554686369002</v>
+        <v>-0.4072902811332142</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.3729443080072059</v>
+        <v>-0.3742234256708628</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.4302758427879638</v>
+        <v>-0.4314903647232953</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.5853831133942222</v>
+        <v>-0.586406824669929</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.5004115534271136</v>
+        <v>-0.501532268332717</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.5469429239680181</v>
+        <v>-0.5480245531195393</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.4553713975546074</v>
+        <v>-0.4565656269323384</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.4623401543597581</v>
+        <v>-0.4635189383515268</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.4306228061413151</v>
+        <v>-0.4318426264451531</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/rsi/rsi_14.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/rsi/rsi_14.xlsx
@@ -618,2379 +618,2379 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 17.54</t>
+          <t>X ≈ 17.55</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>41</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8.411528515251533</v>
+        <v>7.380885816520845</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.647973032541294</v>
+        <v>7.140438836259577</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.6600588553198818</v>
+        <v>-1.376695782938796</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-8.660228553893937</v>
+        <v>-9.239333090029554</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.003904396645254</v>
+        <v>-7.091186265667439</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-13.66951335861948</v>
+        <v>-11.78912248940805</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-21.74207234914614</v>
+        <v>-19.8638170271977</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-14.74840340248955</v>
+        <v>-12.89108271991496</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-14.70982325339585</v>
+        <v>-12.7673891406838</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-20.36212033648123</v>
+        <v>-18.42135967386618</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-17.6568826269961</v>
+        <v>-15.72625673682225</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-8.223145663210119</v>
+        <v>-6.285344163130212</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.785743342502471</v>
+        <v>4.756613969710287</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-2.302768538104047</v>
+        <v>-0.3528770268207992</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-2.976251376417544</v>
+        <v>-1.033102606863224</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.06542125755269268</v>
+        <v>1.959660218766246</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>2.36317241258017</v>
+        <v>1.856533215892718</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>7.128086337540225</v>
+        <v>6.593741143161949</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>9.788167316739155</v>
+        <v>9.2453060613513</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>2.67289758227389</v>
+        <v>2.154184637606704</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>4.554955237595472</v>
+        <v>4.02492079658299</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>3.48814173367964</v>
+        <v>1.513529396095237</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>3.76373127337181</v>
+        <v>1.7576158845078</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>3.689166856621284</v>
+        <v>1.596079457459723</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 20.14</t>
+          <t>X ≈ 20.11</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>39</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1.389384130075385</v>
+        <v>1.489336139139198</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1292330781416595</v>
+        <v>2.604328546095026</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.9893865975897995</v>
+        <v>3.905553512774318</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.928836532568695</v>
+        <v>10.96420075315237</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.497031105157802</v>
+        <v>3.045020727815022</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1334769357683143</v>
+        <v>-1.898078402129414</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.634189370069933</v>
+        <v>-0.1385663425138048</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.9116758129229865</v>
+        <v>-2.994093323280246</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.682400997404947</v>
+        <v>-0.3150557785842025</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.021315921075782</v>
+        <v>3.999026674842746</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>8.850563668334608</v>
+        <v>6.825121021847224</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.13061860056152</v>
+        <v>9.106118390930462</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>12.57021457774915</v>
+        <v>10.55294031011889</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.796687477202468</v>
+        <v>7.752539752069445</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>9.143333501625456</v>
+        <v>7.074821676858967</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>4.621958996306404</v>
+        <v>2.521017150382256</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>7.049191527851647</v>
+        <v>4.976729319049902</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>6.946684827649676</v>
+        <v>4.845536581582081</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>4.603567926912838</v>
+        <v>2.500999984415856</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>4.791897762824917</v>
+        <v>2.716278768617009</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>4.251344971139751</v>
+        <v>2.150366349061386</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>9.300654611223983</v>
+        <v>7.201097873609434</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>9.578052823627132</v>
+        <v>7.446926214951723</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>6.94119937694763</v>
+        <v>4.723033803927983</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 22.75</t>
+          <t>X ≈ 22.69</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-7.422176648181157</v>
+        <v>-4.466724130556265</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-13.20476963589475</v>
+        <v>-8.26644023531108</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-17.32518815640186</v>
+        <v>-14.86099842351285</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-22.47223413903992</v>
+        <v>-19.7995996530938</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-15.58505117774772</v>
+        <v>-12.97844451709514</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-10.76450467294467</v>
+        <v>-7.498432604014816</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-11.53542739767101</v>
+        <v>-10.06796006042659</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-15.43571063433785</v>
+        <v>-12.15160153125836</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-13.589157600149</v>
+        <v>-12.02801377415594</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-10.74128194002208</v>
+        <v>-9.268128428927504</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-8.6606419557883</v>
+        <v>-7.221693555407484</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-7.12955441674378</v>
+        <v>-5.720727742430142</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-13.68939603785039</v>
+        <v>-12.1729043483799</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-10.28763364764842</v>
+        <v>-8.863382671669619</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-10.94709466050674</v>
+        <v>-9.546102128377221</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-12.17154196141619</v>
+        <v>-10.77042683342456</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-10.49415035900801</v>
+        <v>-9.095658930315786</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-10.60205056653935</v>
+        <v>-9.231152041296696</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-10.3895751127959</v>
+        <v>-9.019753157280306</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-12.02235516333586</v>
+        <v>-10.5915224428289</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-12.56808928115377</v>
+        <v>-11.16150734178899</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-10.82682931721643</v>
+        <v>-11.23999456853176</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-5.102774434678778</v>
+        <v>-5.644326719574288</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-6.99819456244731</v>
+        <v>-5.808101727209113</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 25.36</t>
+          <t>X ≈ 25.27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.067847558691106</v>
+        <v>-4.816003210649022</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-9.875334426137492</v>
+        <v>-11.13298155069154</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-8.758122813076589</v>
+        <v>-11.74184707524201</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.8502474322992555</v>
+        <v>-0.2164579617621101</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.239398231520873</v>
+        <v>-1.026383927153503</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>6.595964878474724</v>
+        <v>3.979549658423508</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.233854802896502</v>
+        <v>-0.4486183462214512</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.9243909330047373</v>
+        <v>-3.17891883937218</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.468697620975021</v>
+        <v>-6.693863982495053</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.925270684252034</v>
+        <v>-2.632134256113225</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.384468633927376</v>
+        <v>-4.79146065156845</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3701386001049443</v>
+        <v>-3.854133561515035</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4.970726097406661</v>
+        <v>1.10995329381727</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.158427695109857</v>
+        <v>-1.568329737656406</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>2.78935258641765</v>
+        <v>-1.032727917222509</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.7989657487864861</v>
+        <v>-2.906004038182495</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-5.818307030385796</v>
+        <v>-7.878025307720449</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-5.925090028688984</v>
+        <v>-8.013246426687488</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-3.11287041608206</v>
+        <v>-5.366439890273284</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-1.627663347929953</v>
+        <v>-3.935666323055308</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>3.015227614180745</v>
+        <v>0.369753474317136</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>2.938592405135402</v>
+        <v>1.513520083585718</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>7.880149950116063</v>
+        <v>4.195823761394493</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>5.209597645345603</v>
+        <v>1.596079457460277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 27.96</t>
+          <t>X ≈ 27.84</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.7004334475372</v>
+        <v>-1.01149415731431</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-3.0468889267812</v>
+        <v>-5.268274357633935</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-5.501233067516601</v>
+        <v>-5.511298119622467</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.240369720476806</v>
+        <v>-3.089821885932466</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-2.57956647495179</v>
+        <v>-3.36420599340827</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.392819995082519</v>
+        <v>-1.201818585386228</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.366114106236672</v>
+        <v>2.026064377808368</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.086886547178366</v>
+        <v>1.723665532770568</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.8544277118130168</v>
+        <v>-1.163596496217686</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.6354451549313325</v>
+        <v>-0.951521559127265</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.349094745373364</v>
+        <v>-3.698625113285701</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.629490346238029</v>
+        <v>-3.976002109980627</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.765934508874508</v>
+        <v>-3.075751576041498</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.987563295842264</v>
+        <v>-4.330621491471497</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.6602956243575875</v>
+        <v>0.02368693568725888</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.06137190161368267</v>
+        <v>1.591115999424552</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.1970164715789195</v>
+        <v>0.4802388405847253</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-2.30002412746061</v>
+        <v>0.3476160401010944</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-3.081012882876045</v>
+        <v>-0.4467115382700371</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-1.893995495768245</v>
+        <v>0.7763400755401051</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-4.441684419955216</v>
+        <v>-1.808471141606383</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-1.5181691549191</v>
+        <v>1.144150125515317</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-3.2389036407764</v>
+        <v>0.3783174041788655</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-1.725467289719631</v>
+        <v>2.236631317524328</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 30.57</t>
+          <t>X ≈ 30.41</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-7.005214789508571</v>
+        <v>-5.798958596231437</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-8.302490555917508</v>
+        <v>-6.950749080499307</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-6.834872321940509</v>
+        <v>-6.374198771367773</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.680941150924262</v>
+        <v>-3.318562910053295</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-15.61066274407376</v>
+        <v>-13.61978570202543</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-6.728991034761592</v>
+        <v>-5.263189457141316</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-6.530778004362389</v>
+        <v>-4.230765093634346</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.876362080785526</v>
+        <v>-4.535103815832656</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-3.869441999776456</v>
+        <v>-3.495732321800347</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.706847738714025</v>
+        <v>-2.463734989259642</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.402349428791375</v>
+        <v>-2.193620047269732</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.189588600521958</v>
+        <v>1.184259051325476</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.803882674424173</v>
+        <v>-3.582808016716065</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.151480803949354</v>
+        <v>-0.1736488831013503</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-1.808728577718639</v>
+        <v>-1.768637753187804</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.7226295682045532</v>
+        <v>1.535365668050581</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.3801707689190437</v>
+        <v>-0.3981128979187005</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.4849202343944583</v>
+        <v>0.3845465681050939</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>4.581709568234992</v>
+        <v>3.346328825146543</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>4.770192302938398</v>
+        <v>2.645641275330725</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>7.142027474566625</v>
+        <v>5.745790589392016</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>5.124433940341994</v>
+        <v>4.755752685573789</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>4.428034866416283</v>
+        <v>4.083831538094898</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>7.264823972416302</v>
+        <v>4.840653187601255</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 33.19</t>
+          <t>X ≈ 32.99</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.176025286600073</v>
+        <v>-7.097029253536704</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.489684749050276</v>
+        <v>-1.824149999615699</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.496119699543044</v>
+        <v>-6.235173713611751</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.207719922863291</v>
+        <v>-6.039229551708402</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.317656931964841</v>
+        <v>-6.315665777376161</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-4.688629616351783</v>
+        <v>-4.927698533025563</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.792346097795857</v>
+        <v>-2.564073579792861</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.263505266164422</v>
+        <v>-0.5002884265528564</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.305433278238169</v>
+        <v>-2.740876444591521</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.2429817933972984</v>
+        <v>-3.534954181048597</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.527018452853781</v>
+        <v>-4.055394482794028</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.700244210335526</v>
+        <v>-7.494698838372557</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-5.264254661846344</v>
+        <v>-7.02682950601838</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.928046344724777</v>
+        <v>-4.904124029488777</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-3.806631355407561</v>
+        <v>-4.003661779648546</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-7.11394883204823</v>
+        <v>-6.611338691733252</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-3.349216980380788</v>
+        <v>-2.758556019209443</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-4.23551111078617</v>
+        <v>-3.684331339159939</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-4.021343446163982</v>
+        <v>-2.679575275883195</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-2.273856219818072</v>
+        <v>-0.08852195599679646</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.598263787569302</v>
+        <v>-2.240947245131366</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.2321402510217752</v>
+        <v>1.64860498794431</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.837135036496349</v>
+        <v>-1.280633564056863</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.3504672897196244</v>
+        <v>0.9379300188230317</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 35.79</t>
+          <t>X ≈ 35.56</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-4.0516988662214</v>
+        <v>-5.56815526712591</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-9.57384231841656</v>
+        <v>-7.45104904175291</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.678664237248391</v>
+        <v>-2.949424971677693</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-7.390142528597217</v>
+        <v>-6.82471657372956</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-5.992137644232379</v>
+        <v>-6.275329219409208</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-5.808307380334512</v>
+        <v>-6.944514203277855</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-6.576935676013662</v>
+        <v>-6.095244417450068</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-8.587302207497814</v>
+        <v>-6.400765001315847</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5.951904074990608</v>
+        <v>-3.809038628817206</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-6.724432297084398</v>
+        <v>-3.781160435984141</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-4.72110268513854</v>
+        <v>-4.334240558536628</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-5.867915940480806</v>
+        <v>-5.434826695705439</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-7.857128610669236</v>
+        <v>-7.370535167001222</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-8.080790076494814</v>
+        <v>-7.621012772411461</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-13.94633311352918</v>
+        <v>-12.42245977393497</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-12.4900756839355</v>
+        <v>-13.51553858773399</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-14.36501059549992</v>
+        <v>-14.44863965704629</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-11.00066760359839</v>
+        <v>-11.28835900124907</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-12.52701003075332</v>
+        <v>-12.72873749842304</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-10.60629420680836</v>
+        <v>-10.86880217367801</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-12.89174204843886</v>
+        <v>-13.91605912700611</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-12.96758800984816</v>
+        <v>-13.99647310777215</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-14.43224373214852</v>
+        <v>-15.41021695684066</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-11.02981511580658</v>
+        <v>-11.44564600111662</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 38.4</t>
+          <t>X ≈ 38.14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.58222308200645</v>
+        <v>-2.671072673586913</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>7.200776990345958</v>
+        <v>7.187784356144164</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6.587314646440177</v>
+        <v>6.783375346086501</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.7596378919570057</v>
+        <v>1.143588139530117</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.877182457177561</v>
+        <v>5.079992563971665</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.237064879056504</v>
+        <v>4.389972361448514</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-4.170085685261178</v>
+        <v>-2.292499935310154</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.792383324645542</v>
+        <v>-2.596607657819952</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.2625280432479187</v>
+        <v>2.585465249590733</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.86889641564278</v>
+        <v>-1.577886626324052</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.06659675406933729</v>
+        <v>0.3786807999701622</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.874657115697111</v>
+        <v>-1.584296116117379</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.5118248020719136</v>
+        <v>0.6803406888944892</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.734028021960917</v>
+        <v>1.276949229400572</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.2655218402222985</v>
+        <v>1.442482444779593</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>1.695756048966082</v>
+        <v>3.692070589341292</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>3.225822372663288</v>
+        <v>5.279902927566063</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1.457077820032218</v>
+        <v>3.457590367211118</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.676781916087975</v>
+        <v>3.672437070934798</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.033823038373072</v>
+        <v>3.041564345932557</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.1517362124306985</v>
+        <v>2.476113894658248</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-2.42410974897841</v>
+        <v>-0.1388228820096273</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-2.149635036496356</v>
+        <v>0.1046491932614231</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-2.225467289719631</v>
+        <v>-0.05749640033220516</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 41.01</t>
+          <t>X ≈ 40.72</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-4.928619321180875</v>
+        <v>-2.318729056624804</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.977539539163914</v>
+        <v>1.409275290845059</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-5.900973498308332</v>
+        <v>-1.424455427719856</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.330393862780383</v>
+        <v>-1.218753766689701</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-6.139984618459458</v>
+        <v>-2.285378429330805</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.30010156297309</v>
+        <v>-3.722400595075271</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-7.552354721104699</v>
+        <v>-6.895893446040446</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-7.014045133721368</v>
+        <v>-4.817366646169624</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.973030561271763</v>
+        <v>-4.693004518288568</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-6.935327757339167</v>
+        <v>-3.895621003811101</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-6.658816281426439</v>
+        <v>-2.831229378794234</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-7.283246377746721</v>
+        <v>-3.108018575029824</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.469239261179887</v>
+        <v>0.5588450905048248</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.867993813156062</v>
+        <v>0.3111345275010748</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-2.707633988194722</v>
+        <v>-0.3680570987674798</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-2.935474159772696</v>
+        <v>-1.404048669872402</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-3.071501376921475</v>
+        <v>-1.508692628647566</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.525709092792766</v>
+        <v>-0.04636480030979584</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-3.78621767537863</v>
+        <v>-1.429647895836581</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-2.280924231173522</v>
+        <v>-1.216326870772299</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-2.823470399139552</v>
+        <v>-0.9842949962068914</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-5.378655203523863</v>
+        <v>-3.458129266214584</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-5.930626772033541</v>
+        <v>-4.015701587684468</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-11.79158299219896</v>
+        <v>-8.979530298637286</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 43.62</t>
+          <t>X ≈ 43.28</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.434896461675251</v>
+        <v>0.7238470241170418</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.3646128543463902</v>
+        <v>-1.058638698678791</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.3585125912725218</v>
+        <v>-1.533184510584817</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.809166313903788</v>
+        <v>-2.890755403875993</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-5.813719254510062</v>
+        <v>-7.777922654688801</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-7.083732163432238</v>
+        <v>-8.395832065268664</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-7.868399633736175</v>
+        <v>-8.416881686497078</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-5.222057506808412</v>
+        <v>-4.87494620787286</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-4.447677101587189</v>
+        <v>-4.750996731871723</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.765308425416848</v>
+        <v>-3.233123355586827</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-6.723497283243766</v>
+        <v>-6.04834089170069</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-5.536827445065022</v>
+        <v>-5.555327402910159</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.531362119002729</v>
+        <v>-2.039636481060789</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.956002738341546</v>
+        <v>-4.604005563455161</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-2.417872288151678</v>
+        <v>-2.968389874547618</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-4.024677731748611</v>
+        <v>-3.183231542311063</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-3.426335524403477</v>
+        <v>-0.9701377643484577</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.79717147555769</v>
+        <v>-2.650362317280873</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.06626009984046277</v>
+        <v>-0.1173798094812497</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-2.688070560779742</v>
+        <v>-0.6774919862225772</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-2.495322611098551</v>
+        <v>-1.24425226216276</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-2.571168572507815</v>
+        <v>-2.09464647776619</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-2.296693860025762</v>
+        <v>-1.852108090975122</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-2.372526113249037</v>
+        <v>-2.790383011815756</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 46.22</t>
+          <t>X ≈ 45.86</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-4.572254065251578</v>
+        <v>-6.762308726145868</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.541675045633653</v>
+        <v>-4.109586875757977</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-4.029178522067447</v>
+        <v>-6.800303283364428</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-4.75862735064446</v>
+        <v>-4.491978053344361</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-6.703465432457364</v>
+        <v>-5.485197555844742</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-6.496197942809928</v>
+        <v>-6.058167978211117</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-8.888613719212749</v>
+        <v>-7.571785776367761</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-6.004935428850246</v>
+        <v>-6.431522865718868</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-4.373363513778777</v>
+        <v>-4.858871748292692</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-6.756798795683089</v>
+        <v>-4.927945135535872</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.30305463109417</v>
+        <v>-3.934295683364397</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-5.174309570858618</v>
+        <v>-5.663826382798938</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.084712924836204</v>
+        <v>-0.9683842437534622</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.8347549830718606</v>
+        <v>-2.669339345298305</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.7113863367686477</v>
+        <v>-1.895961803421642</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.9028055097783749</v>
+        <v>-2.792589881967736</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-2.146116376213115</v>
+        <v>-5.808886829498583</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.77194687398768</v>
+        <v>-3.033108392768412</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-3.937007874015741</v>
+        <v>-5.734462181297637</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-6.131114445000094</v>
+        <v>-8.437674463710849</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-5.880009819315511</v>
+        <v>-9.00790142698483</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-5.955855780724434</v>
+        <v>-6.899592528844686</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-8.855984242845558</v>
+        <v>-9.577758874647337</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-5.757213321465656</v>
+        <v>-6.824785773089673</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 48.83</t>
+          <t>X ≈ 48.44</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4.888078710403718</v>
+        <v>3.597283211683653</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>7.09473096058435</v>
+        <v>7.427221944035388</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3.728658919956693</v>
+        <v>2.778641709428392</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.37302056998179</v>
+        <v>2.86617635562358</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.389918144755512</v>
+        <v>3.271161837628256</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.502888684777098</v>
+        <v>0.03070348766019748</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.4747770314779132</v>
+        <v>0.995912903735082</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.1167664382742828</v>
+        <v>2.049037106598512</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.5650434382512799</v>
+        <v>1.494626894317463</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.1112646912513</v>
+        <v>0.7032997997439452</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.107771235845568</v>
+        <v>0.9732228489073833</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.751775562790925</v>
+        <v>0.6983453156880017</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.9672052904489234</v>
+        <v>0.9473286997128838</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.720255197615792</v>
+        <v>2.745774385083507</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-3.127188505533724</v>
+        <v>-0.6599060317506655</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-2.781798880525137</v>
+        <v>-0.7837726889601058</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-2.278773342343378</v>
+        <v>-0.8883682836053808</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-3.657499396482883</v>
+        <v>-3.0716045547519</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-2.804665340399325</v>
+        <v>-2.176624514392117</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-5.165590231068094</v>
+        <v>-5.381788767276262</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-6.345079074193507</v>
+        <v>-5.950903745754964</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-8.331753061080171</v>
+        <v>-9.450902821374349</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-6.783392998279645</v>
+        <v>-7.843145398211412</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-6.859225251503062</v>
+        <v>-8.009667284938651</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 51.44</t>
+          <t>X ≈ 51.01</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.643329994621709</v>
+        <v>4.853417319376938</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.6682397910225291</v>
+        <v>4.606628124014932</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.514223337779704</v>
+        <v>6.710263405152631</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.798227618066932</v>
+        <v>2.781590814767426</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.652858530903288</v>
+        <v>4.740801251616546</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>4.939272063640374</v>
+        <v>4.336175044488655</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>4.710746388224486</v>
+        <v>4.109270542817718</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.139625369258177</v>
+        <v>1.575824491941411</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4089029282880077</v>
+        <v>1.701059098935673</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.1856755682626599</v>
+        <v>-1.877333118085986</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.73708883194108</v>
+        <v>-2.724981519064329</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.3682202036146691</v>
+        <v>-1.326956809881608</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.491248296743088</v>
+        <v>-3.00039193977333</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.359730846999732</v>
+        <v>-2.690473754969425</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.1739740015301905</v>
+        <v>-2.251546420578322</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-2.876290376290378</v>
+        <v>-3.372481919451253</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-1.911306414366756</v>
+        <v>-2.359208480631182</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-3.664498766539701</v>
+        <v>-3.614258450739513</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-5.096959033967032</v>
+        <v>-3.963721749617342</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-4.910113223999126</v>
+        <v>-4.312278889554705</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-4.353758293063926</v>
+        <v>-3.198432352076011</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.68235150722041</v>
+        <v>-1.592424499869573</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.8584262452878093</v>
+        <v>-0.7890727897365011</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.483709047961511</v>
+        <v>-0.3907662536933287</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 54.05</t>
+          <t>X ≈ 53.58</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.105371571943856</v>
+        <v>-1.061199904796837</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.196440516471569</v>
+        <v>-1.849138259268017</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4.352954445018952</v>
+        <v>2.324511621867842</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5.362982765182856</v>
+        <v>6.067826320175669</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>7.898548092517643</v>
+        <v>5.258800709685687</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.214742993001614</v>
+        <v>3.787498747287309</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>6.740450474079573</v>
+        <v>6.792525149685623</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.870016898310347</v>
+        <v>2.160342481737572</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.485612297586954</v>
+        <v>2.285347564615215</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.862050909834252</v>
+        <v>3.124476284789139</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.3102292774646784</v>
+        <v>0.6843192802845692</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-4.035090939661558</v>
+        <v>-1.219045077264958</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-8.604300245063079</v>
+        <v>-6.676665180227715</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-5.953375080122768</v>
+        <v>-5.841759656010829</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-6.615808029570864</v>
+        <v>-4.348717694395312</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-6.596133751306162</v>
+        <v>-5.968244373723898</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-5.580625600927313</v>
+        <v>-3.900116085948909</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-6.834891592104682</v>
+        <v>-6.214183129808369</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-3.745436992789564</v>
+        <v>-4.371055133918311</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-4.133303826499557</v>
+        <v>-4.159683788793807</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-4.675849994465857</v>
+        <v>-4.729010215750172</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-4.176983312196668</v>
+        <v>-3.170817117179716</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-5.05193388707093</v>
+        <v>-4.02256170161305</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-6.277191427650529</v>
+        <v>-5.827617730331525</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 56.65</t>
+          <t>X ≈ 56.16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.875393133347217</v>
+        <v>5.475545486491228</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.117099731839915</v>
+        <v>2.915925135064924</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.083000116668508</v>
+        <v>2.834251588320008</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4.392365095592815</v>
+        <v>3.98125794397842</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>4.652473733914718</v>
+        <v>7.763440101864077</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.6114764291078387</v>
+        <v>3.867911384501085</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.1858203225789978</v>
+        <v>1.928177930724736</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1107730361426746</v>
+        <v>1.050067466927949</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.146103509753409</v>
+        <v>4.06878273771143</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.451167160200704</v>
+        <v>1.545663512278644</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.03428743811364399</v>
+        <v>1.817936932767616</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.459851329315732</v>
+        <v>-0.1958804548569333</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-5.01125022824337</v>
+        <v>-2.467326747854834</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-5.23232910468996</v>
+        <v>-1.555734305611239</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-3.094386921942991</v>
+        <v>-0.4911808314462789</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.893939393939192</v>
+        <v>1.230644350421173</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.8157353187955181</v>
+        <v>1.706721678718097</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.3145154165563042</v>
+        <v>0.9920848774420818</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-4.94710888411668</v>
+        <v>-2.29358764842263</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-4.154202468088251</v>
+        <v>-1.498348655072121</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-4.696748636054018</v>
+        <v>-3.817247856374095</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-5.378655203523863</v>
+        <v>-4.481044333546826</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-3.892059278920584</v>
+        <v>-3.073258048587576</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-3.967891532143859</v>
+        <v>-3.823974743081529</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 59.26</t>
+          <t>X ≈ 58.73</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.136222950262301</v>
+        <v>3.361405099099017</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.71227417739027</v>
+        <v>8.164690953674636</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.637312453200046</v>
+        <v>4.044675045135442</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.986469591720486</v>
+        <v>3.455498698687364</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.322260064267823</v>
+        <v>-1.139413423270682</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.323304847944208</v>
+        <v>0.4594554115872072</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>6.009954890168572</v>
+        <v>4.006308347735398</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.820915419937791</v>
+        <v>0.8243626088378022</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.596196124262157</v>
+        <v>-2.666791267803227</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.09522644998024532</v>
+        <v>-1.284484385972959</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.089661217659383</v>
+        <v>-0.2911958843108664</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.0999162112662475</v>
+        <v>-2.010743026287628</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.6877497473553404</v>
+        <v>-0.9480190455762383</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>4.925269597023402</v>
+        <v>1.699910505990367</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>2.99324094912437</v>
+        <v>1.747347737067386</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.676799845589585</v>
+        <v>-1.322437256405877</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.004887992024763</v>
+        <v>-2.883540545356212</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>2.711927355109545</v>
+        <v>2.068582397425011</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>1.016990710556023</v>
+        <v>-2.809256387666949</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.5668938453648806</v>
+        <v>-4.05401151596427</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.02434767739885046</v>
+        <v>-3.89523944611966</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.5854443911489824</v>
+        <v>-0.331707135559391</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.8599191036310359</v>
+        <v>-0.8202436939997995</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.421029525567</v>
+        <v>-0.2554427073964902</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 61.87</t>
+          <t>X ≈ 61.31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-4.845666390540401</v>
+        <v>-7.550858846467285</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-8.192491381661299</v>
+        <v>-8.953071764593666</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-4.208823683704338</v>
+        <v>-3.845403849705463</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.307319871821775</v>
+        <v>-3.858581581919843</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.4382910672605576</v>
+        <v>-1.818313281026526</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.3510847573910496</v>
+        <v>-0.5082878687540884</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.1815457120548487</v>
+        <v>2.166619791663116</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.5057439058559794</v>
+        <v>1.868725270545184</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.862407466446179</v>
+        <v>-1.474487888399182</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.786363604505283</v>
+        <v>2.93964110774354</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.5540345846580905</v>
+        <v>0.3173151721240117</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.179264204664996</v>
+        <v>2.359779043126281</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.260921414917306</v>
+        <v>2.986495964518113</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.642252177024943</v>
+        <v>4.479079269977738</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>3.188928156552812</v>
+        <v>4.380056749655374</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>3.783315078495804</v>
+        <v>3.779994752810289</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.444578664409903</v>
+        <v>0.7674086563893709</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.339737960588721</v>
+        <v>0.6329598939228021</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.350810064404605</v>
+        <v>1.428142424179171</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.9352462358184184</v>
+        <v>1.640764907179204</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.597519344960887</v>
+        <v>2.817626268041053</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>3.32890229921437</v>
+        <v>2.159680253292017</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.01108081962888008</v>
+        <v>0.06393838949966124</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.117906204256279</v>
+        <v>0.8543878300176857</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 64.47</t>
+          <t>X ≈ 63.89</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.5845049992440963</v>
+        <v>1.862737581959685</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.066629609345057</v>
+        <v>-1.737839733340586</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.9243852082013149</v>
+        <v>0.370651597783592</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.90124486757945</v>
+        <v>-2.231998402756709</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.284091420436653</v>
+        <v>2.193361247480468</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-6.27542126670533</v>
+        <v>-1.005592048034913</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.526243190032382</v>
+        <v>-1.125117561063682</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-5.21290533901081</v>
+        <v>-1.696246083360748</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.9460660444199647</v>
+        <v>2.455482899631036</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.3936943358814915</v>
+        <v>3.012150598714719</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.371979330156016</v>
+        <v>5.307175540552102</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.91013133515888</v>
+        <v>7.733138512799684</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.378518564077403</v>
+        <v>4.609140217218354</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.9552363687072898</v>
+        <v>2.334378370985874</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1.203521742162941</v>
+        <v>2.333412350648132</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>1.09368331199309</v>
+        <v>2.895525764229276</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.663991527128459</v>
+        <v>3.468609658213708</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.1507001190817618</v>
+        <v>2.658439777756115</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.07081685211876</v>
+        <v>2.195495750959964</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.1507880421384868</v>
+        <v>1.053036938498899</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>1.419341846233436</v>
+        <v>2.522507776640559</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.343495884824414</v>
+        <v>1.765412274992897</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.026421301531826</v>
+        <v>4.047914818101162</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.246363696195864</v>
+        <v>3.20550371496816</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 67.08</t>
+          <t>X ≈ 66.45</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.193685260668751</v>
+        <v>1.842220404872442</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.7006350810239326</v>
+        <v>3.114612999646972</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.176232888870324</v>
+        <v>-1.151071768579214</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.7309135270181031</v>
+        <v>-0.2206554437403199</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.066703999565377</v>
+        <v>-2.005474827980741</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>5.595082330416808</v>
+        <v>-0.3332545202833899</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.945435804799928</v>
+        <v>0.3959883555204229</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.983771122636696</v>
+        <v>3.139717688184881</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>7.464107225414708</v>
+        <v>5.532122497130231</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>8.13004047024161</v>
+        <v>5.506690234306362</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>11.2817979541303</v>
+        <v>8.062473898996686</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>9.564199629818773</v>
+        <v>7.036798931635772</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>9.879886483825878</v>
+        <v>8.223247211334602</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.500534226084397</v>
+        <v>5.692345570037567</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>9.000664309798729</v>
+        <v>9.596460665234041</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>8.156202310878655</v>
+        <v>9.40322881772687</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>8.741709634332665</v>
+        <v>7.777993582191762</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>5.759171088785038</v>
+        <v>6.119826213158845</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.816789088414396</v>
+        <v>4.041112321971418</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.284210437950684</v>
+        <v>3.491094680818009</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>4.899937651279622</v>
+        <v>5.228334919187134</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>7.701789531597136</v>
+        <v>7.458397972512948</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>7.256839783647536</v>
+        <v>6.93645484949824</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.583885228265906</v>
+        <v>5.235854316747329</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 69.69</t>
+          <t>X ≈ 69.03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4.151360678775831</v>
+        <v>3.737170106978795</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.07952001567791456</v>
+        <v>1.699664631594707</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2188377660075744</v>
+        <v>-0.1217109730634363</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.665610811952284</v>
+        <v>1.087889346374467</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.6182316086469442</v>
+        <v>-0.3730511920879778</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-3.678018669302809</v>
+        <v>-1.413984638731989</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.501915405141247</v>
+        <v>-1.00287649546982</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-3.429477499244825</v>
+        <v>-3.678561735604426</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-5.985392914732834</v>
+        <v>-5.37325578040749</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-5.459607292068021</v>
+        <v>-4.370220946192731</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.938794403152968</v>
+        <v>-1.707260318100978</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.2694918585488963</v>
+        <v>-0.1767213911282184</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.5553980226470046</v>
+        <v>1.729285220349851</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.581072392953658</v>
+        <v>4.49296755472124</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>2.9229290953731</v>
+        <v>3.213881592766811</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>6.114718614718626</v>
+        <v>5.592606512216307</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>7.279502776442442</v>
+        <v>7.915137830360187</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>5.226610124569305</v>
+        <v>5.973345823727229</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>6.741202804194934</v>
+        <v>7.408694937026226</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>8.226749912864264</v>
+        <v>7.63109664891762</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>7.034853095547582</v>
+        <v>7.071028697811215</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>5.010955186086498</v>
+        <v>5.171072280286289</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>2.688027301166024</v>
+        <v>3.587486744432731</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>3.261545697293435</v>
+        <v>2.205835555021253</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 72.29</t>
+          <t>X ≈ 71.6</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.788995261580119</v>
+        <v>-0.06128801276341278</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>6.024376088218219</v>
+        <v>3.584461817835823</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.623394076224265</v>
+        <v>-1.574010603267467</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.132662279003739</v>
+        <v>1.727062112163644</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.019094028678694</v>
+        <v>2.226077592923261</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.428282436998302</v>
+        <v>1.603588916899021</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.915593012367253</v>
+        <v>0.02787245735301269</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.896640826873345</v>
+        <v>5.166180252547058</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.71590578656587</v>
+        <v>1.09339127701562</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.202249369788632</v>
+        <v>1.074294726264263</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-4.449616913975319</v>
+        <v>-0.2188944251877558</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.2839218729789224</v>
+        <v>1.847132301910328</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.07439754164644086</v>
+        <v>-0.0548959552238415</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-3.109644297763104</v>
+        <v>-1.088270387212923</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-3.767787595343663</v>
+        <v>-1.777051558294893</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.271043771043772</v>
+        <v>2.717246222363443</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>2.618608115547779</v>
+        <v>1.039667889995592</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>3.254508152467338</v>
+        <v>-0.6800216772221148</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.211140274132411</v>
+        <v>0.3157622769919257</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>5.879467565581919</v>
+        <v>2.101258263081561</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>6.077662138356622</v>
+        <v>3.098954758044201</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>2.298112473243869</v>
+        <v>0.3584370020954708</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>2.57258718572583</v>
+        <v>-2.074534161490725</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.756014191761857</v>
+        <v>-2.236673155780146</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 74.91</t>
+          <t>X ≈ 74.18</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-11.29850477108963</v>
+        <v>-8.496318490677275</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.8224707586286257</v>
+        <v>0.4601534700619183</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.045816498646637</v>
+        <v>6.777583327538395</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.6301597765012446</v>
+        <v>4.503797899940295</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.2943693039539212</v>
+        <v>5.913555941839725</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.283137291853095</v>
+        <v>10.25821580697727</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.412089508863652</v>
+        <v>7.797482378790008</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.133878064110675</v>
+        <v>5.832809949240023</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.175365246025379</v>
+        <v>5.958772382319708</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.402449569988889</v>
+        <v>5.67498814956803</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.1252925896510391</v>
+        <v>0.07308325535346682</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.205843794900844</v>
+        <v>-0.210296115195753</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.2745977418466978</v>
+        <v>4.576108907525992</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.9544197663010081</v>
+        <v>3.479124618126612</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>3.899880072324052</v>
+        <v>5.341399716898401</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.8906633906633985</v>
+        <v>5.055301301876156</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>2.558548055487677</v>
+        <v>9.19985275075171</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>5.156410054369189</v>
+        <v>11.63754783646853</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>5.372301435293515</v>
+        <v>11.8719304576273</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>2.856444542558947</v>
+        <v>12.10521598629873</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>5.917501978196476</v>
+        <v>13.26370938190173</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>3.138953314084659</v>
+        <v>11.47914515054479</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>7.017031630170308</v>
+        <v>14.28688219992569</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>5.139397575145288</v>
+        <v>12.41534149623451</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 77.51</t>
+          <t>X ≈ 76.75</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>8.623303829964257</v>
+        <v>4.86235946646466</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.145435232536499</v>
+        <v>0.6792357321990892</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.907111756168412</v>
+        <v>9.219914557238063</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.420572831065243</v>
+        <v>5.693137753192701</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.914971037763301</v>
+        <v>5.428172795198734</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.215144771030495</v>
+        <v>2.648083500433486</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.386592313555241</v>
+        <v>0.8925319232971916</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.995173321632237</v>
+        <v>4.516883491871297</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.980056729962072</v>
+        <v>4.642164106029092</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.980725959585925</v>
+        <v>5.801479582458981</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.254785601747905</v>
+        <v>6.67879798290528</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>7.976036198299909</v>
+        <v>5.428903625243713</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>8.739666584273898</v>
+        <v>3.336424823564414</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>5.688399028582083</v>
+        <v>3.08001923632888</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>4.086859504586393</v>
+        <v>3.389448217048539</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>5.624642652944544</v>
+        <v>3.946946114988094</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>7.377517968797306</v>
+        <v>3.843280936179504</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>10.10286594422141</v>
+        <v>5.711443563293955</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>6.545172419485333</v>
+        <v>5.941962621145862</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>10.50560313511366</v>
+        <v>7.168310307564568</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>9.019660740732583</v>
+        <v>5.61413673232903</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>10.83060723215367</v>
+        <v>3.538974210373766</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>10.16168571822062</v>
+        <v>5.782608695652236</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>8.199061012167114</v>
+        <v>4.620469701362659</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 80.12</t>
+          <t>X ≈ 79.33</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6.141761582220241</v>
+        <v>9.867049379763152</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>7.980897827348649</v>
+        <v>6.853127205234841</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.065816873856257</v>
+        <v>-1.88366072649417</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-3.952683936777255</v>
+        <v>-2.480379479286903</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.027604844107131</v>
+        <v>0.02934393537622526</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.333274385468506</v>
+        <v>2.054642721841411</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-3.786500385378361</v>
+        <v>-1.573202938983677</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.2831142568250797</v>
+        <v>-2.833888742548446</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.411557960478888</v>
+        <v>1.03508708205441</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.812555327920691</v>
+        <v>3.045899911520216</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.260528013560872</v>
+        <v>3.305185264170902</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8.24264817533026</v>
+        <v>6.3930369553849</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.3803556736916</v>
+        <v>9.036231542984389</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.985363753766649</v>
+        <v>3.182186513496085</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>9.501133499664384</v>
+        <v>3.45244519513691</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>7.921607378129082</v>
+        <v>4.047690863440813</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>1.26595111071687</v>
+        <v>1.13702120827606</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.07415388515654797</v>
+        <v>2.493829964210228</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>4.637871353037433</v>
+        <v>3.661200181651395</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>5.911673684744557</v>
+        <v>5.37987891026836</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>6.456084038517623</v>
+        <v>7.280803398995744</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>7.467194598847648</v>
+        <v>8.158021829421394</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>9.915582354807995</v>
+        <v>11.25879917184266</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>13.10061966680211</v>
+        <v>10.14427922517229</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 82.72</t>
+          <t>X ≈ 81.91</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.786119178702826</v>
+        <v>3.583023477252546</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-5.661017170208765</v>
+        <v>-3.750497175669821</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-3.728249702385803</v>
+        <v>-2.616239180054819</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.176773806261338</v>
+        <v>-0.8482165724648922</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-4.776994194375817</v>
+        <v>-7.013742782017353</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-3.466432502660467</v>
+        <v>-4.505893466657284</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.626787352775068</v>
+        <v>2.981114387081817</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.595766919257905</v>
+        <v>6.231094798824543</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.513658595554659</v>
+        <v>2.807292552369255</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.3699564026642435</v>
+        <v>-0.3586928462843346</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.767611550444144</v>
+        <v>3.4589339264353</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.983244169467994</v>
+        <v>6.708725536006909</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.736486596993892</v>
+        <v>4.425763269587513</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>2.391812214929359</v>
+        <v>6.578092094563452</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>0.6100734117308306</v>
+        <v>7.120167937817847</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-2.16632618318009</v>
+        <v>2.930455947381745</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>1.070543196696349</v>
+        <v>2.853678061761649</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.9657024928751667</v>
+        <v>0.3111554023831715</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>1.181593873799493</v>
+        <v>2.412777921180954</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>1.368439683767519</v>
+        <v>2.627364366239931</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>1.949489021419481</v>
+        <v>5.674377696184507</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>1.87364306001038</v>
+        <v>4.394395897120781</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>1.02452226687442</v>
+        <v>2.228391828182296</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>4.319476530505092</v>
+        <v>5.680710665218164</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 85.34</t>
+          <t>X ≈ 84.48</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-5.91357438615924</v>
+        <v>-2.629546057154386</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-3.975623911781717</v>
+        <v>-4.402213037165879</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-3.140915688085499</v>
+        <v>-4.012990004382686</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-12.94477879843736</v>
+        <v>-6.158187234246853</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-11.00784199825733</v>
+        <v>-4.815863126419622</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-13.09360308488723</v>
+        <v>-7.790554469281645</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-7.047369950595822</v>
+        <v>-0.847696212983152</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-7.325581395348834</v>
+        <v>0.4262132614124283</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-5.011366940706957</v>
+        <v>-1.011670303333425</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-5.784282616743447</v>
+        <v>-3.373534272982859</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.9647684291269414</v>
+        <v>-0.02174408301497266</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-5.788972378029356</v>
+        <v>1.16334688995078</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-6.912134444885538</v>
+        <v>3.128857041977284</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-7.133213321332128</v>
+        <v>-0.1988067622339926</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-12.33681116436723</v>
+        <v>-5.584992558012303</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-14.01515151515152</v>
+        <v>-5.034219011360378</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-16.42179592485623</v>
+        <v>-1.971726190476218</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-14.25390935595017</v>
+        <v>-0.517308708336202</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-16.31074524775308</v>
+        <v>-3.477449655793606</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-9.305717619603271</v>
+        <v>-0.08826003613142319</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-9.848263787569266</v>
+        <v>-3.830307712115356</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-5.378655203523827</v>
+        <v>0.8564345278341179</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-5.104180491041774</v>
+        <v>-0.4872325741890862</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-7.452740016992323</v>
+        <v>0.9379300188230104</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 87.94</t>
+          <t>X ≈ 87.06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.5796226236360482</v>
+        <v>-8.578554871823194</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.208049557605939</v>
+        <v>-6.414162306329402</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.810846835105615</v>
+        <v>4.42719149597059</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.057076489132271</v>
+        <v>-3.485210702837627</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.762102343115579</v>
+        <v>-1.395020339942953</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.8674358761517311</v>
+        <v>-1.20838613514249</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.09548719226138047</v>
+        <v>0.4662324514272242</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.898908400569532</v>
+        <v>2.571611409216196</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-2.182053397107573</v>
+        <v>0.2743906183014815</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.9141527466134463</v>
+        <v>1.933189422483373</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>1.400723222079058</v>
+        <v>2.235125035890114</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.162790145161694</v>
+        <v>-2.817504822772783</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.042004574755673</v>
+        <v>-9.863305244097809</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2222671246716175</v>
+        <v>-6.311670740361052</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.8804104222521758</v>
+        <v>-7.013981763402043</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-2.32683982683983</v>
+        <v>-8.963319012186425</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-2.460756963817325</v>
+        <v>-9.1145833333333</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-6.647230320699705</v>
+        <v>-11.74746743849494</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-12.55378791936722</v>
+        <v>-16.53300521134916</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-10.32612578286858</v>
+        <v>-11.31841876629018</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-8.827855624303993</v>
+        <v>-9.385863267670914</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-6.862885259182484</v>
+        <v>-4.461025789626191</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-2.506777893639232</v>
+        <v>-4.217391304347814</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>1.499022506198713</v>
+        <v>-1.87953029863732</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 90.55</t>
+          <t>X ≈ 89.62</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>10.35915288656803</v>
+        <v>11.85419866871479</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.024376088218233</v>
+        <v>9.817815642534711</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.586357039187206</v>
+        <v>3.18322736074898</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.873403019744487</v>
+        <v>0.8172801883957845</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>3.537612547197213</v>
+        <v>4.173468080042468</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>3.724578733294592</v>
+        <v>0.7155868712257671</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.952630049404242</v>
+        <v>-3.702775564287386</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.674418604651166</v>
+        <v>-0.4013468013468042</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>6.71590578656587</v>
+        <v>-0.2734178916626959</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.942990110529379</v>
+        <v>-1.08640060381326</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.2170497526912953</v>
+        <v>-0.8310968061401312</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-8.061699650756708</v>
+        <v>-4.747890400823096</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-9.184861717612812</v>
+        <v>-7.678655534146849</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-11.40594059405944</v>
+        <v>-9.71736578605617</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-10.06408389163997</v>
+        <v>-8.686771541401093</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-3.469696969696962</v>
+        <v>-6.375954351900383</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-9.603614106674442</v>
+        <v>-9.11458333333335</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-11.70845481049562</v>
+        <v>-12.95117114219864</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-13.49256342957133</v>
+        <v>-14.58856076690472</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-15.30571761960329</v>
+        <v>-12.52212246999388</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-19.8482637875693</v>
+        <v>-13.08956697137461</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-19.92410974897839</v>
+        <v>-15.01658134518176</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-23.64963503649631</v>
+        <v>-16.62479871175522</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-17.72546728971962</v>
+        <v>-11.23138215048913</v>
       </c>
     </row>
   </sheetData>
@@ -3180,2461 +3180,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 16.23</t>
+          <t>X &gt; 16.26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3342</v>
+        <v>3365</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1193017939668835</v>
+        <v>-0.1482937883231159</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.02199727682339869</v>
+        <v>0.09395831690594036</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1950880990821773</v>
+        <v>-0.1111544229417234</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2669896036939434</v>
+        <v>-0.1260286828303734</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3183826923148345</v>
+        <v>-0.1783274845190448</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2932784095625465</v>
+        <v>-0.2118364264015113</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.3042916534835243</v>
+        <v>-0.2808562216111028</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2975885424602112</v>
+        <v>-0.2733636274009044</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.3284790808752973</v>
+        <v>-0.2470380037443505</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.3096916534753831</v>
+        <v>-0.2273217304106225</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.3760948076663766</v>
+        <v>-0.2637619503505704</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.3693919584490075</v>
+        <v>-0.2273482333753662</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.3718584369686155</v>
+        <v>-0.1996753691477409</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.4262269902407851</v>
+        <v>-0.2231858918762697</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.410249215423903</v>
+        <v>-0.176630532603447</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.4547715965626367</v>
+        <v>-0.2203086138704151</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.451628439311051</v>
+        <v>-0.2770981613285883</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.4790641294920448</v>
+        <v>-0.303533887619821</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.5143740062070989</v>
+        <v>-0.3089696030405662</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.5489931725022572</v>
+        <v>-0.3440940408523616</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.5059618443704963</v>
+        <v>-0.2409701560319633</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.444444677208061</v>
+        <v>-0.2391665677669792</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.4213969270138449</v>
+        <v>-0.2453176263917953</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.4196623824784496</v>
+        <v>-0.300778441282155</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 18.84</t>
+          <t>X &gt; 18.83</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3301</v>
+        <v>3324</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2252587896281781</v>
+        <v>-0.2411627305007968</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.09242102195636903</v>
+        <v>0.00704324431463732</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1893129397347906</v>
+        <v>-0.09554455658796712</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1627415585687686</v>
+        <v>-0.0136202951362776</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2105043554843178</v>
+        <v>-0.09306057416191749</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1271391690562282</v>
+        <v>-0.06903596653891952</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.0380241562032424</v>
+        <v>-0.0393094728057406</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1181025051196443</v>
+        <v>-0.1177299081490801</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1498559027252355</v>
+        <v>-0.09260527311423061</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.06063089128112154</v>
+        <v>-0.002906701625526864</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1614591516250243</v>
+        <v>-0.07303924089048053</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.271844578292928</v>
+        <v>-0.152625660234591</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.4110773624331117</v>
+        <v>-0.2608089019074242</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.4029194460231551</v>
+        <v>-0.2215862118122729</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.3783782403858069</v>
+        <v>-0.1660663463685879</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.4612326407973342</v>
+        <v>-0.2471975194474609</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.4865896131758021</v>
+        <v>-0.3034155158611043</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.5735485794006507</v>
+        <v>-0.3886085796360845</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.6423365006756896</v>
+        <v>-0.4268171668913681</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.5890105978115017</v>
+        <v>-0.374909150905566</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.56882085690021</v>
+        <v>-0.2935879445569967</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.4932892827355957</v>
+        <v>-0.2607852604620362</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.4733782224442606</v>
+        <v>-0.2700228832951979</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.4706960082897496</v>
+        <v>-0.3241753046541263</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 21.45</t>
+          <t>X &gt; 21.4</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3262</v>
+        <v>3285</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2445632267429687</v>
+        <v>-0.2617074659394447</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.09198090233919487</v>
+        <v>-0.02379210630010675</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2034053008493402</v>
+        <v>-0.1430461775027752</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.259483295403335</v>
+        <v>-0.1439505906867424</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2428752576808293</v>
+        <v>-0.1303163339114235</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1302550574952761</v>
+        <v>-0.04732130748624996</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.03089649116927973</v>
+        <v>-0.03813108074527349</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1086146574788316</v>
+        <v>-0.0835813013940907</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1717621011020185</v>
+        <v>-0.08996430820911172</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.1333457673332106</v>
+        <v>-0.05041823942834611</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.2692055924522521</v>
+        <v>-0.1549352074800581</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.4081707781627415</v>
+        <v>-0.2625468224858665</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.566279810522353</v>
+        <v>-0.3891913126438098</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.5248644705497654</v>
+        <v>-0.3162562004245686</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.492218448214885</v>
+        <v>-0.2520312270096525</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.5220065444904805</v>
+        <v>-0.2800621684956681</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.5766863220967196</v>
+        <v>-0.3661021668691831</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.6634594018638538</v>
+        <v>-0.4507491157966683</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.7050557749479012</v>
+        <v>-0.4615766399205867</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.6533439595726378</v>
+        <v>-0.411608185566557</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.6264500620791082</v>
+        <v>-0.3226029270383037</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.6103842587823252</v>
+        <v>-0.3493738273505613</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.5935516776241485</v>
+        <v>-0.3616396305803207</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.5593115570402887</v>
+        <v>-0.3840965086829513</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 24.06</t>
+          <t>X &gt; 23.98</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3207</v>
+        <v>3229</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1214672684707239</v>
+        <v>-0.1887805742644488</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1329032200011682</v>
+        <v>0.119158743877847</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.09023300817947444</v>
+        <v>0.112204775044944</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1214650352483631</v>
+        <v>0.1969340012905931</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.02024282015005952</v>
+        <v>0.09250657666717643</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.05212215761221017</v>
+        <v>0.08190205349411883</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.166406034511283</v>
+        <v>0.1358145441733285</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.1542447995611553</v>
+        <v>0.1257123291021571</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.05834602251743348</v>
+        <v>0.1170752613458674</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.04858017264118075</v>
+        <v>0.109442946886908</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1252925896510391</v>
+        <v>-0.03237761457701538</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.2928991535534635</v>
+        <v>-0.1678865154196245</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.341218571824804</v>
+        <v>-0.1848283736530334</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.3574331313728294</v>
+        <v>-0.1680248339365775</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.3129174841749531</v>
+        <v>-0.09084572980414407</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.3222171937168881</v>
+        <v>-0.09812955120362687</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.4066019684858304</v>
+        <v>-0.2147069427276449</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.4930127183411983</v>
+        <v>-0.2984720752800953</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.5389664192941268</v>
+        <v>-0.3131536343547339</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.4583655946811547</v>
+        <v>-0.2350596571036618</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.4216511356528159</v>
+        <v>-0.1346256439085352</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.4351723853137059</v>
+        <v>-0.1604996367323608</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.5162185776434782</v>
+        <v>-0.2700228832951979</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.4488848138855062</v>
+        <v>-0.2900289050169675</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 26.66</t>
+          <t>X &gt; 26.55</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3130</v>
+        <v>3147</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.04898443066019098</v>
+        <v>-0.06821106165450175</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.3791122611362141</v>
+        <v>0.4123508329006285</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.3079082152838524</v>
+        <v>0.421080609720363</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1035365226052676</v>
+        <v>0.2077055745255265</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.009749181982698474</v>
+        <v>0.1216610162328919</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1088605546901533</v>
+        <v>-0.01965724221741993</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.09094483477785076</v>
+        <v>0.1510428559027019</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.180779927806384</v>
+        <v>0.211819655385888</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1451135498493556</v>
+        <v>0.2945449207023856</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.02701302586992682</v>
+        <v>0.1808790227197719</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.09431605437651314</v>
+        <v>0.09162772671097485</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.290999013814023</v>
+        <v>-0.07183559143493312</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.4718958049017559</v>
+        <v>-0.2185659321953253</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.4193249152831129</v>
+        <v>-0.1315377026671101</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.3892353101927242</v>
+        <v>-0.06630351837475246</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.3497990105132942</v>
+        <v>-0.02496599609327177</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.2734705660045904</v>
+        <v>-0.01502721411964103</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.3593801455307286</v>
+        <v>-0.09745158058183989</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.4756467363060537</v>
+        <v>-0.1814823687095739</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.429600122796117</v>
+        <v>-0.1386345707966896</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.5062005489873798</v>
+        <v>-0.1477680295756798</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.5181691549190006</v>
+        <v>-0.2041188350374341</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.7227746085180726</v>
+        <v>-0.3863874924037276</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.5880870980263353</v>
+        <v>-0.3391744041345817</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 29.27</t>
+          <t>X &gt; 29.13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3030</v>
+        <v>3048</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.03852213755357781</v>
+        <v>-0.0375729296104268</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.4921816072721015</v>
+        <v>0.5968593282624752</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4996290496997133</v>
+        <v>0.6137661393151461</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.1808931642911347</v>
+        <v>0.3148103050325162</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.07506326993046741</v>
+        <v>0.2348830746169099</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.06648565566730724</v>
+        <v>0.01873973054298972</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.01714656031980155</v>
+        <v>0.09014156631325676</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.08486881825615455</v>
+        <v>0.1627144251165049</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.178101710300254</v>
+        <v>0.3419058131810857</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.04887633216699783</v>
+        <v>0.2176597502797577</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.01310238427024757</v>
+        <v>0.2147363327344891</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.180817781720819</v>
+        <v>0.05497296674617047</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.3961849565858202</v>
+        <v>-0.1257636425822</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.3015612723603596</v>
+        <v>0.004849861339337735</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.3802894252367963</v>
+        <v>-0.06922643666613482</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.3593180570116346</v>
+        <v>-0.07745684830990029</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.2759938034443863</v>
+        <v>-0.03111361156574333</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.295332489361428</v>
+        <v>-0.1119075170803967</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.3896610549011115</v>
+        <v>-0.1728676417454977</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.3812702425000083</v>
+        <v>-0.1683532354906987</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.3763165928498253</v>
+        <v>-0.09382786944082255</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.4851658545889634</v>
+        <v>-0.2479110355278351</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.6397340463973435</v>
+        <v>-0.4112253482966608</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.5505497979704472</v>
+        <v>-0.4228373852514622</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 31.88</t>
+          <t>X &gt; 31.7</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2927</v>
+        <v>2939</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2863885207060832</v>
+        <v>0.1761021427480927</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.801662725416449</v>
+        <v>0.8767808378082549</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.7577273214041611</v>
+        <v>0.8729319015691317</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.316789622940675</v>
+        <v>0.4495628332544896</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.627037912719139</v>
+        <v>0.748717336833316</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1679653364907807</v>
+        <v>0.2146329872485282</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.2120656155382079</v>
+        <v>0.2503929531571742</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2594526182566028</v>
+        <v>0.3369444993810404</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.3205332108598427</v>
+        <v>0.4842340053256891</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1458491983442229</v>
+        <v>0.3171058294256568</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.133290814999782</v>
+        <v>0.3040561168176623</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1938522393125552</v>
+        <v>0.01309063152359613</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2410797755344447</v>
+        <v>0.00244929950034134</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.271652932164379</v>
+        <v>0.01146992365442401</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.3300232029253323</v>
+        <v>-0.006199613426637995</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.3973913762454018</v>
+        <v>-0.137272314210982</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.2723278562479692</v>
+        <v>-0.01750254582485411</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.3227892814853917</v>
+        <v>-0.1303197305153105</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.5646016678778807</v>
+        <v>-0.3033856461317654</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.5625482206961721</v>
+        <v>-0.2727171013224563</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.6408842180441923</v>
+        <v>-0.3104043961549365</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.6825655057259254</v>
+        <v>-0.4334841371270457</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.8180668779722637</v>
+        <v>-0.577935522034899</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.8255697837408107</v>
+        <v>-0.6180468008489228</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 34.49</t>
+          <t>X &gt; 34.28</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2799</v>
+        <v>2813</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.5361880803113692</v>
+        <v>0.5018805131469151</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.7701990530244771</v>
+        <v>0.9977610317348109</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.8607971387250828</v>
+        <v>1.191318431079537</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.4322370048138069</v>
+        <v>0.7402090616602237</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.8074312460951916</v>
+        <v>1.065145446463745</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.3900604254382074</v>
+        <v>0.4449684908228377</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2579979839936399</v>
+        <v>0.376458642155292</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.213536670085027</v>
+        <v>0.3744458675529714</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.27549312203368</v>
+        <v>0.6286932718345994</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1636306799244025</v>
+        <v>0.4896474438301226</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2092177840191738</v>
+        <v>0.4993247892496129</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.05795846890143252</v>
+        <v>0.3493798150312131</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.01136688327009949</v>
+        <v>0.3173050156380484</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1044438014720868</v>
+        <v>0.2316493897390401</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.1710357632977164</v>
+        <v>0.1728548597137589</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.09023905243591201</v>
+        <v>0.1527143063250307</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1316198148442638</v>
+        <v>0.1052748226950371</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.1438580938646439</v>
+        <v>0.02887168885518321</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.4065227298212122</v>
+        <v>-0.1969512723853555</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.484289048174702</v>
+        <v>-0.2809675770818032</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.5056414224388988</v>
+        <v>-0.2239314494890934</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.7243955653413963</v>
+        <v>-0.5267451501945857</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.7714642612194638</v>
+        <v>-0.5464602453570606</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.8472965144427391</v>
+        <v>-0.6877421720820038</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 37.09</t>
+          <t>X &gt; 36.85</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2684</v>
+        <v>2692</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.7327629681099097</v>
+        <v>0.7747164453211326</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.213404998522144</v>
+        <v>1.377518096702133</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.183836653716504</v>
+        <v>1.377436540936017</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.7673985720054191</v>
+        <v>1.080237294157314</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.098768959354366</v>
+        <v>1.395085058117019</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.6556387777719834</v>
+        <v>0.7771109150376176</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.5508509537778536</v>
+        <v>0.6673487128136273</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.590621793379384</v>
+        <v>0.6789780054181804</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.5423152821148278</v>
+        <v>0.8281604189292793</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.4587600548707584</v>
+        <v>0.6816116910283085</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4204647489793487</v>
+        <v>0.7165838557734361</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3118614335359169</v>
+        <v>0.6093682948971662</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.324796529043951</v>
+        <v>0.6628580104743449</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.2373147013698045</v>
+        <v>0.5846108019307934</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.4191874838247287</v>
+        <v>0.7389889870062945</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.4410505200761818</v>
+        <v>0.7670748561694438</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.4782311314207917</v>
+        <v>0.7594440842287256</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.3213181705241013</v>
+        <v>0.5375585066496171</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.1127977022231903</v>
+        <v>0.3663273804194631</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.05059657677273321</v>
+        <v>0.1949343494368279</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.02505961034425752</v>
+        <v>0.3915022239802894</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.1998176476371185</v>
+        <v>0.07869210198479237</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.1861477041565536</v>
+        <v>0.1216358029674325</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.4110112539521111</v>
+        <v>-0.2041959747145512</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 39.7</t>
+          <t>X &gt; 39.43</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2564</v>
+        <v>2574</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.8411086490825923</v>
+        <v>0.9326819138647053</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.9331847804960631</v>
+        <v>1.111157794210229</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9309437679415922</v>
+        <v>1.129611840466794</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.8388667372454606</v>
+        <v>1.07733309844869</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.9687340062581313</v>
+        <v>1.226157674398735</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.5348232036089087</v>
+        <v>0.6114863421252252</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.7717996264317932</v>
+        <v>0.8030371900780437</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.7489527661418549</v>
+        <v>0.829140829140826</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.5799834564687814</v>
+        <v>0.7476002130170514</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.5676987352380038</v>
+        <v>0.7851939759729802</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.4370264336085228</v>
+        <v>0.7320743610511258</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.4141945949664745</v>
+        <v>0.7099325530555589</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.3639519735579455</v>
+        <v>0.6620565512460743</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.2827753592479922</v>
+        <v>0.5528718996613975</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.4263793236189031</v>
+        <v>0.7067387041713147</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.38232795242142</v>
+        <v>0.6329841426829219</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.3496387176340932</v>
+        <v>0.5522124822420196</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.2681624927000072</v>
+        <v>0.4036953522027389</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.03960031311876122</v>
+        <v>0.214765242315039</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.1013494448762842</v>
+        <v>0.06443616000927932</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.01913090821853558</v>
+        <v>0.2959372755964438</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.09571661325296787</v>
+        <v>0.08866365136758958</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.09425282120773915</v>
+        <v>0.1224145208948997</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.3260913146806175</v>
+        <v>-0.2109211300281189</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 42.31</t>
+          <t>X &gt; 42</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2443</v>
+        <v>2449</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.126879047937223</v>
+        <v>1.098637965849683</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.077350823344545</v>
+        <v>1.095941507121886</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.2693236243543</v>
+        <v>1.259974604257465</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.045367159923785</v>
+        <v>1.194528222230758</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.320823631141799</v>
+        <v>1.405390836083598</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.7742934847208289</v>
+        <v>0.8326933111534274</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.184088892110026</v>
+        <v>1.196000166605124</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.13344836412935</v>
+        <v>1.117345579820217</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.9540787066311225</v>
+        <v>1.025295432050619</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.9393181399051471</v>
+        <v>1.024108582944407</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.7884783241198789</v>
+        <v>0.9139498071436876</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.7954432063861603</v>
+        <v>0.9048055179435437</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.5538071268134885</v>
+        <v>0.6673245923210729</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.4388306477706649</v>
+        <v>0.5652104752106268</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.5816047066436525</v>
+        <v>0.7615976161220459</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.5466562600659088</v>
+        <v>0.7369568260514114</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.519085279828623</v>
+        <v>0.6574036373507042</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.3570116379495474</v>
+        <v>0.4266669810570036</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.2290902748904315</v>
+        <v>0.2986981301341274</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.00660329730217768</v>
+        <v>0.12980789494096</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.1599228681818232</v>
+        <v>0.3612819199310451</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.1659434642839841</v>
+        <v>0.2696963645965695</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.1948185042322663</v>
+        <v>0.3336291038154471</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.2417860872758766</v>
+        <v>0.2366395666138388</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 44.92</t>
+          <t>X &gt; 44.57</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2307</v>
+        <v>2320</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.108721107638843</v>
+        <v>1.11947763459257</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.119367452639636</v>
+        <v>1.21574359615132</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.365286227442837</v>
+        <v>1.41528388262585</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.213644815944832</v>
+        <v>1.421684079027216</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.741412201774075</v>
+        <v>1.916014732768772</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.237532101170245</v>
+        <v>1.345831144583798</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.717742311925832</v>
+        <v>1.73050954550606</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.508111909186802</v>
+        <v>1.450537666291083</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.272517713964319</v>
+        <v>1.346477194613549</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.216660668246632</v>
+        <v>1.260825358836875</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.231316938164717</v>
+        <v>1.301077177898399</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.168737011586586</v>
+        <v>1.264011184663417</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.6767299778889111</v>
+        <v>0.817840962349635</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.6979105526303471</v>
+        <v>0.8526367118433313</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.7584269308708613</v>
+        <v>0.9689977826291098</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.8161410554221291</v>
+        <v>0.9549328172232876</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.7516718551973085</v>
+        <v>0.7479005514969188</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.5429539454644967</v>
+        <v>0.5977604204904452</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.2386892795747784</v>
+        <v>0.3218334983282531</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.1654570661357866</v>
+        <v>0.1746965521263419</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.316452293921806</v>
+        <v>0.4505551567802328</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.3272990069817183</v>
+        <v>0.4011619795383083</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.3416956960567461</v>
+        <v>0.4551636288706149</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.3959024545369871</v>
+        <v>0.4049524599834129</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 47.52</t>
+          <t>X &gt; 47.15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.436920498644888</v>
+        <v>1.614120205101578</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.330871971109346</v>
+        <v>1.549948944136467</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.676933434429678</v>
+        <v>1.93087501489368</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.558672919104048</v>
+        <v>1.792811752932344</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.229286838139579</v>
+        <v>2.38049759284209</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.684322557631276</v>
+        <v>1.810488899885165</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.330489152789418</v>
+        <v>2.314299952788119</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.942153158426905</v>
+        <v>1.945197443151059</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.598689669349753</v>
+        <v>1.735910453971378</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.677300692297592</v>
+        <v>1.649218193344005</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.493275130611593</v>
+        <v>1.629636995577279</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.535185369857139</v>
+        <v>1.698786148814747</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.7784914660793589</v>
+        <v>0.9299402996085036</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.7864551915567262</v>
+        <v>1.073667733294734</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.8433404896615926</v>
+        <v>1.148795979280038</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.9154474594639623</v>
+        <v>1.190118621066247</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.9190819043296869</v>
+        <v>1.15938926940639</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.6766896186653071</v>
+        <v>0.8256252979143781</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.4799262540600608</v>
+        <v>0.701912521740411</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.5292204821848969</v>
+        <v>0.715188915465653</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.6744322234348274</v>
+        <v>1.044145881459926</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.6902873165878489</v>
+        <v>0.8593403430969175</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.87306097450778</v>
+        <v>1.084806497849975</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.7513781940034363</v>
+        <v>0.8586740073636321</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 50.13</t>
+          <t>X &gt; 49.72</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2024</v>
+        <v>2037</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.169217020756484</v>
+        <v>1.471978919406446</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.8837742135265501</v>
+        <v>1.128701100255633</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.517782791530593</v>
+        <v>1.870112159026185</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.49550464776619</v>
+        <v>1.715879385729153</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.29439597097619</v>
+        <v>2.316660096652214</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.086690228114527</v>
+        <v>1.938053293692164</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.548091322221218</v>
+        <v>2.408794066269579</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.101861842558371</v>
+        <v>1.937754835952582</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.678868749528831</v>
+        <v>1.753204219169938</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.893607394479993</v>
+        <v>1.717015977077736</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.772605308246852</v>
+        <v>1.676684843104923</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.790152201095161</v>
+        <v>1.770491775538609</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.9139037144859543</v>
+        <v>0.9286940028901753</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.7915902701381299</v>
+        <v>0.9538211102406464</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.151331128122884</v>
+        <v>1.278432942269959</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.202239789196319</v>
+        <v>1.331595366900231</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>1.167136881467854</v>
+        <v>1.306160306588389</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.012889063022165</v>
+        <v>1.104955468994049</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.7347092977014285</v>
+        <v>0.9082288728819776</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.9709622222939558</v>
+        <v>1.152183879471707</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.218929888320027</v>
+        <v>1.545509281348686</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.39011950003345</v>
+        <v>1.598317025479247</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.46696575401748</v>
+        <v>1.724708793787613</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.341726386169704</v>
+        <v>1.494303771073071</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 52.74</t>
+          <t>X &gt; 52.3</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1842</v>
+        <v>1859</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.348306899583214</v>
+        <v>1.148204828392593</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.9050702313852526</v>
+        <v>0.7956881845863819</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.419328839621066</v>
+        <v>1.406665724485848</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.46559390911542</v>
+        <v>1.613837086445223</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.160172200125629</v>
+        <v>2.084547603062298</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.80483903698223</v>
+        <v>1.708432168548654</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.334408791269752</v>
+        <v>2.245972757595261</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.196936238943081</v>
+        <v>1.972409812409808</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.804348542941341</v>
+        <v>1.758197135469942</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.062360701956401</v>
+        <v>2.061176353053611</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.119382905160101</v>
+        <v>2.09814617310284</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.003411580930766</v>
+        <v>2.067073727235659</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.151546312772432</v>
+        <v>1.304905567061297</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.201764235023617</v>
+        <v>1.302763813848713</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.282278757654289</v>
+        <v>1.616429890407126</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.605221597078284</v>
+        <v>1.782012664894083</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.471304460100811</v>
+        <v>1.657120846730976</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.475041389287227</v>
+        <v>1.556822105740984</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.310911054684951</v>
+        <v>1.374720110539251</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.552045681156777</v>
+        <v>1.67540839420365</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.769542944243952</v>
+        <v>1.999743606657766</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.693696982834851</v>
+        <v>1.903831813812815</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.696727612797901</v>
+        <v>1.965404394576908</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>1.620895359574625</v>
+        <v>1.674799986462226</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 55.35</t>
+          <t>X &gt; 54.87</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1668</v>
+        <v>1676</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.269332527286593</v>
+        <v>1.389446514653727</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.8746754894158215</v>
+        <v>1.084472933527522</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.113303146971653</v>
+        <v>1.306447467194133</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.059031762259458</v>
+        <v>1.127512486342198</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.561564643005596</v>
+        <v>1.737955527577768</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.449129631498188</v>
+        <v>1.481421915619563</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.874785738027001</v>
+        <v>1.749541320988733</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.231039335627791</v>
+        <v>1.951889717847166</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.733281460622187</v>
+        <v>1.700638347562077</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.978939780990729</v>
+        <v>1.945076181509691</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.372831658023841</v>
+        <v>2.252519873213664</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.63332731149616</v>
+        <v>2.425880255412039</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.169242536431526</v>
+        <v>2.176401657009912</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.948163659984935</v>
+        <v>2.082863930187791</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>2.106179897328865</v>
+        <v>2.267755670847968</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>2.460758665794643</v>
+        <v>2.62825194775035</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>2.206937452078563</v>
+        <v>2.263907456922155</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>2.341904901734594</v>
+        <v>2.405326854013978</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.838371822227259</v>
+        <v>2.002092944510451</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>2.145121708933893</v>
+        <v>2.312533614662208</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>2.441904078138137</v>
+        <v>2.734446440488703</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>2.306106078359726</v>
+        <v>2.457925342674159</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>2.400724675733869</v>
+        <v>2.619221695055877</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>2.4447964992492</v>
+        <v>2.49397805458468</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 57.95</t>
+          <t>X &gt; 57.45</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.9832380495753554</v>
+        <v>0.9251787909432849</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.8480620496287372</v>
+        <v>0.8763810222564885</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.006849387823294</v>
+        <v>1.132856434162548</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.693096965186939</v>
+        <v>0.8032663247104352</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.222243285720168</v>
+        <v>1.053332363323314</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.675343869688469</v>
+        <v>1.210265969321398</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.100999976217281</v>
+        <v>1.729244403869231</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.488124526141519</v>
+        <v>2.054355900509741</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.797742113911177</v>
+        <v>1.431566792269358</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.355498427229307</v>
+        <v>1.99045795322963</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.62955806939123</v>
+        <v>2.301897735550064</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.082678260088279</v>
+        <v>2.723768017176809</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.957520185248136</v>
+        <v>2.704027940884906</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.736441308801545</v>
+        <v>2.49628605531845</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>2.677100406430569</v>
+        <v>2.581229519281393</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>2.938819331034892</v>
+        <v>2.787049887380434</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>2.538767796186505</v>
+        <v>2.327215608465607</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>2.633527890768519</v>
+        <v>2.56590119155139</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.58328487382191</v>
+        <v>2.490173596597856</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>2.836664283257676</v>
+        <v>2.745530869230031</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>3.22558850783988</v>
+        <v>3.478858217740232</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>3.14974254643078</v>
+        <v>3.246339837447451</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>3.09154926157418</v>
+        <v>3.266008430047933</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>3.148784207286361</v>
+        <v>3.211831827608556</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 60.56</t>
+          <t>X &gt; 60.02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1346</v>
+        <v>1368</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.9653935997923995</v>
+        <v>0.6811999866908494</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.630616801442585</v>
+        <v>0.1464844867270472</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.049952878711743</v>
+        <v>0.8412488685899788</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.005646704737053</v>
+        <v>0.5376553340416876</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.635680897865868</v>
+        <v>1.2729275188521</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.59976446880723</v>
+        <v>1.285456792720218</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.645052040488942</v>
+        <v>1.501205105397247</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.33266526141194</v>
+        <v>2.177535053257593</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.076975623118621</v>
+        <v>1.842001773431591</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.641355638018233</v>
+        <v>2.318430979889534</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.692532665024139</v>
+        <v>2.561586204790522</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.453902132304229</v>
+        <v>3.197911301500369</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.22227052607218</v>
+        <v>3.06976656452904</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.48113221426155</v>
+        <v>2.576040039425138</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.640225172253054</v>
+        <v>2.664739610044052</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>3.086023684092034</v>
+        <v>3.19859940397307</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.95210654711456</v>
+        <v>2.849053030303033</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.624383228137361</v>
+        <v>2.615705778390065</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.765980404009682</v>
+        <v>3.020891365489874</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>3.10141462408172</v>
+        <v>3.426479192893495</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>3.598987326843769</v>
+        <v>4.217346068579999</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>3.448847160382662</v>
+        <v>3.604667641030737</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>3.351850847604688</v>
+        <v>3.675231047733988</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>3.350312799433418</v>
+        <v>3.559066192590784</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 63.17</t>
+          <t>X &gt; 62.6</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1180</v>
+        <v>1197</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.782881700127355</v>
+        <v>1.857208391427733</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.871833715336862</v>
+        <v>1.446421094058572</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.789746869695705</v>
+        <v>1.510770685489327</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.331030138388556</v>
+        <v>1.165689179179047</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.927443055671787</v>
+        <v>1.714533347406181</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.775426190921713</v>
+        <v>1.541706030073676</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.850935134149999</v>
+        <v>1.406145864502129</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.589672841939304</v>
+        <v>2.22165073650222</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.631160023854008</v>
+        <v>2.315786010836</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.620956212224293</v>
+        <v>2.229686675910393</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.149253142521808</v>
+        <v>2.88219635231431</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.6332156034806</v>
+        <v>3.317644481268104</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.357511163743119</v>
+        <v>3.081662364530601</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.458466185601615</v>
+        <v>2.304177292203335</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2.563034752427832</v>
+        <v>2.419694304385288</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.9879301489471</v>
+        <v>3.115542925567752</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.02350453739335</v>
+        <v>3.146430798004985</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.664426545436584</v>
+        <v>2.89895519045681</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.965063689072771</v>
+        <v>3.248426928534265</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.40614678717639</v>
+        <v>3.681581233709821</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.880549771752726</v>
+        <v>4.417306040085556</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.465720759496172</v>
+        <v>3.811094410707696</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.824941234690094</v>
+        <v>4.191129998910327</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.66436321875495</v>
+        <v>3.94544881581551</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 65.78</t>
+          <t>X &gt; 65.17</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1038</v>
+        <v>1050</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.946821480016972</v>
+        <v>1.85643430475325</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.708383795347309</v>
+        <v>1.892217609894452</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.908129678878943</v>
+        <v>1.670387357768128</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.773210341517128</v>
+        <v>1.641365440650056</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.01545455105078</v>
+        <v>1.647497441395785</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.87679453290923</v>
+        <v>1.898327761008886</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.586541417419653</v>
+        <v>1.760522744081335</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.657077564188739</v>
+        <v>2.770156291283044</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.12053006402251</v>
+        <v>2.29622844640469</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.925649070066953</v>
+        <v>2.12014172671779</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.392386939589187</v>
+        <v>2.542699265961019</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.59533310454195</v>
+        <v>2.699475316853672</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.628240401847684</v>
+        <v>2.867815465154322</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.925465957000327</v>
+        <v>2.299949141173784</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.749018227820535</v>
+        <v>2.431773777908496</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>3.247066036083382</v>
+        <v>3.146345328155149</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.209488012786053</v>
+        <v>3.101325757575758</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>3.008308195284727</v>
+        <v>2.932627348234917</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.224199576209053</v>
+        <v>3.395837293394671</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.892740954577846</v>
+        <v>4.049577435039353</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>4.217246809733204</v>
+        <v>4.682577796967863</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.756044393603489</v>
+        <v>4.097489909707775</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>3.93417999240539</v>
+        <v>4.211180124223603</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.858347739182115</v>
+        <v>4.049041129934139</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 68.38</t>
+          <t>X &gt; 67.74</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.754036090127542</v>
+        <v>1.858442790605977</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.864198112689849</v>
+        <v>1.719487826559863</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.539638462991455</v>
+        <v>2.069071799534598</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.160388559232807</v>
+        <v>1.904477087357392</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.492006318053718</v>
+        <v>2.163678305546817</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.456503093695034</v>
+        <v>2.213660039887152</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.685666756856968</v>
+        <v>1.953337385943207</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.297332953928148</v>
+        <v>2.717935659112122</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.448942494018596</v>
+        <v>1.838982547932602</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.120965638894226</v>
+        <v>1.641607698471574</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.172555870600085</v>
+        <v>1.762731111292936</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.67244940374831</v>
+        <v>2.086592632156204</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.661634389172512</v>
+        <v>2.111069674933191</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.218086102269858</v>
+        <v>1.820588776225641</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1.782412215145364</v>
+        <v>1.419372369916836</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>2.488033842316376</v>
+        <v>2.262220487237407</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>2.354116705338903</v>
+        <v>2.440492260619145</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.582980117201821</v>
+        <v>2.482262291234797</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.132575613810239</v>
+        <v>3.304657126313174</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.986829655146451</v>
+        <v>4.128493476396713</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>4.111691718548606</v>
+        <v>4.605459942741227</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>3.145968115315256</v>
+        <v>3.622578987789652</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>3.420442827797309</v>
+        <v>3.826086956521749</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>3.900784100714198</v>
+        <v>3.881339266580106</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 70.99</t>
+          <t>X &gt; 70.32</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>745</v>
+        <v>756</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.258481745628437</v>
+        <v>1.45088818758331</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.265986826473252</v>
+        <v>1.723788096367116</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.109846972073136</v>
+        <v>2.544320972426242</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.262664764710934</v>
+        <v>2.081620459739938</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.134927983438828</v>
+        <v>2.713974122494051</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.724578733294592</v>
+        <v>3.000609414614054</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.757999176921025</v>
+        <v>2.594632460747093</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.687841423443103</v>
+        <v>4.105535623045348</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.192415853679968</v>
+        <v>3.403542185297383</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.687956553482401</v>
+        <v>2.945761002340554</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.022418880208086</v>
+        <v>2.515480574812244</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.280582228437936</v>
+        <v>2.577576097524783</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.097017477018063</v>
+        <v>2.193890641271381</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.936341285135228</v>
+        <v>1.240866395705432</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>1.5466543633936</v>
+        <v>1.030087300409711</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.738356721578199</v>
+        <v>1.539755793988007</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>1.335983208761803</v>
+        <v>1.252870734908129</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>2.036511632457398</v>
+        <v>1.724937292122675</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2.386631201301185</v>
+        <v>2.414363209703467</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>3.110389762947065</v>
+        <v>3.368669507754618</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>3.50744091041728</v>
+        <v>4.070601112276314</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>2.760454009410864</v>
+        <v>3.286662453438524</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>3.571841473570757</v>
+        <v>3.877846790890274</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>4.032921972025342</v>
+        <v>4.244808325701342</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 73.6</t>
+          <t>X &gt; 72.89</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.932923378371306</v>
+        <v>1.753323427652646</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.434212153791989</v>
+        <v>1.351653352073377</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.438816055580673</v>
+        <v>3.367987287564979</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.070124331219894</v>
+        <v>2.152532129255199</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.717940416049672</v>
+        <v>2.811553428408203</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.904906602147051</v>
+        <v>3.280013514157062</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.280498901863261</v>
+        <v>3.1079844614259</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.641631719405261</v>
+        <v>3.893406697145004</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.519184475090455</v>
+        <v>3.865572366953728</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.238072077742494</v>
+        <v>3.32005425755581</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.676066146133927</v>
+        <v>3.062355574812244</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.069447890226918</v>
+        <v>2.72366485664768</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.765957954518342</v>
+        <v>2.643647960570426</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.053075799383222</v>
+        <v>1.706693752289091</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>2.722801354261676</v>
+        <v>1.591515072150628</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>1.841778440139102</v>
+        <v>1.304257708312925</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>1.05212359824359</v>
+        <v>1.295511303890642</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>1.766955025569949</v>
+        <v>2.205929085991635</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>1.982846406494275</v>
+        <v>2.834083396245774</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>2.497561068921314</v>
+        <v>3.62215175668922</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>2.938621458332335</v>
+        <v>4.264930383122731</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2.862775496923234</v>
+        <v>3.87230754370713</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>3.792987914323319</v>
+        <v>5.068322981366471</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>4.536827792247585</v>
+        <v>5.54110462199764</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 76.21</t>
+          <t>X &gt; 75.47</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.876186954704309</v>
+        <v>4.090961058148949</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.936199735512808</v>
+        <v>1.554977886567208</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.303791908926712</v>
+        <v>2.590360120553498</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.390437087880763</v>
+        <v>1.61627853243229</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.257051424952728</v>
+        <v>2.104079170958912</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.043216007843697</v>
+        <v>1.688493692987535</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.473672133572585</v>
+        <v>2.038449848693745</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.199468704851562</v>
+        <v>3.451086657193521</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.040555085163057</v>
+        <v>3.388175872221147</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>4.868841813936186</v>
+        <v>2.782964071658292</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.744103860907735</v>
+        <v>3.744119437144946</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.465354457459739</v>
+        <v>3.392813850226005</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.542593192206823</v>
+        <v>2.202911253370026</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.519911109347404</v>
+        <v>1.302455133764752</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>2.460966208560436</v>
+        <v>0.7362782233485063</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.053349122487397</v>
+        <v>0.448756537851132</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.7170271758906921</v>
+        <v>-0.5072332366215377</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>1.012988075275928</v>
+        <v>0.05485814290041446</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1.228879456200254</v>
+        <v>0.7728200313692852</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>2.417729274184296</v>
+        <v>1.687417809585305</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>2.275984709424684</v>
+        <v>2.212577278138049</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>2.801341152825202</v>
+        <v>2.137414756182764</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>3.075815865307256</v>
+        <v>2.965844563098578</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>4.402789223306421</v>
+        <v>3.973296212083966</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 78.81</t>
+          <t>X &gt; 78.04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.865514209723251</v>
+        <v>3.904181782527708</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.76737863274748</v>
+        <v>1.767021991741089</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.601624214759745</v>
+        <v>0.9851411286201923</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.652028973942961</v>
+        <v>0.6291455491973181</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.079597280021638</v>
+        <v>1.29921388663935</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.266563466119017</v>
+        <v>1.456147492637434</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.76687941327193</v>
+        <v>2.315911816102108</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.52429137818806</v>
+        <v>3.193024469620205</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.056872707685457</v>
+        <v>3.084546759918972</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.029504105440324</v>
+        <v>2.052088645314292</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.066922526228197</v>
+        <v>3.033543518074652</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.788173122780201</v>
+        <v>2.899813904701134</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.41055812971544</v>
+        <v>1.928452761797537</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.935026327060186</v>
+        <v>0.8720522033618252</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>2.022430103270985</v>
+        <v>0.09386418129038532</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>1.090099467962062</v>
+        <v>-0.3982627302207646</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-1.079441078684617</v>
+        <v>-1.560626498800964</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-1.438734708714449</v>
+        <v>-1.314775130802623</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.2050316229555165</v>
+        <v>-0.4787883438792875</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.2362671132211531</v>
+        <v>0.3603251950624724</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.4570797238810798</v>
+        <v>1.388955134266133</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>0.6356866886806287</v>
+        <v>1.798054113521495</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>1.164614327371339</v>
+        <v>2.283819349405206</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>3.37885841002592</v>
+        <v>3.816595609353037</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 81.42</t>
+          <t>X &gt; 80.62</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.169784115803907</v>
+        <v>1.871386010742903</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.173877749347781</v>
+        <v>0.03312248714094324</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.722569663771942</v>
+        <v>1.963141761045542</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.670745212435513</v>
+        <v>1.689210899816935</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.334954739888239</v>
+        <v>1.732124097297216</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.857469098743103</v>
+        <v>1.252115028136068</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.075553637444109</v>
+        <v>3.641746391699527</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.126245847176079</v>
+        <v>5.247653973768614</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.171055288227002</v>
+        <v>3.783226195554633</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.401461871326717</v>
+        <v>1.713289350016822</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.007747427109905</v>
+        <v>2.940938377360013</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.732320282798128</v>
+        <v>1.708942410149859</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>1.28025456145695</v>
+        <v>-0.4946536408797897</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.391401598631624</v>
+        <v>0.08450641581604401</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.263419439812715</v>
+        <v>-1.051106618884575</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.9979361723547697</v>
+        <v>-1.913928728059943</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-1.796305136574773</v>
+        <v>-2.480279126213588</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-1.901145840395955</v>
+        <v>-2.613163231375189</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-1.685254459471629</v>
+        <v>-1.890148068492024</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-1.498408649503602</v>
+        <v>-1.350886298757715</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-1.376502990227102</v>
+        <v>-0.6196295014371458</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-1.452348951636203</v>
+        <v>-0.370116698717105</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-1.510100152775415</v>
+        <v>-0.7758328627893789</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.4074230757288859</v>
+        <v>1.659430740323749</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 84.03</t>
+          <t>X &gt; 83.19</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.491228358266149</v>
+        <v>1.239981967541574</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.043244012746527</v>
+        <v>1.42885774053336</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.850507982583451</v>
+        <v>3.652424508206998</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6.137553963140711</v>
+        <v>2.625239700703119</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.160254056631175</v>
+        <v>4.958377212777705</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.932125903105913</v>
+        <v>3.376180383993173</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.103573445630651</v>
+        <v>3.885446197847408</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>7.768758227292679</v>
+        <v>4.884873580525749</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.866849182792279</v>
+        <v>4.14323727281856</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.093933506755789</v>
+        <v>2.47762056020791</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.367993148917712</v>
+        <v>2.749855574812244</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.787356953016896</v>
+        <v>-0.1354220318329666</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.2491005465381306</v>
+        <v>-2.309740767852183</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.9714178965066367</v>
+        <v>-2.310905190121886</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.630121627489018</v>
+        <v>-4.065399010912571</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.5074328187535713</v>
+        <v>-3.700968408333992</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-2.999840521768782</v>
+        <v>-4.447916666666671</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-3.104681225589964</v>
+        <v>-3.69191188293938</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-2.888789844665638</v>
+        <v>-3.477449655793606</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-2.701944034697611</v>
+        <v>-2.818418766290172</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-2.77279208945609</v>
+        <v>-2.941418823226471</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-2.848638050865191</v>
+        <v>-2.127692456292863</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-2.574163338383137</v>
+        <v>-1.884057971014485</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-1.234901251983779</v>
+        <v>0.1760252569182654</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 86.64</t>
+          <t>X &gt; 85.77</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.692486219901369</v>
+        <v>2.744798421589998</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>6.143423707265832</v>
+        <v>3.696496376305291</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>9.467309420139607</v>
+        <v>6.633419040880774</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>11.13530778164926</v>
+        <v>6.041016842072551</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>13.18046969005435</v>
+        <v>8.759470678021117</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>12.17695968567554</v>
+        <v>7.718799493600045</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.8097729065471</v>
+        <v>5.72611269094817</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11.72203765227022</v>
+        <v>6.618797037958707</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>9.977810548470643</v>
+        <v>6.147923552433234</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>9.204894872434153</v>
+        <v>4.753069662004322</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>8.288478324119872</v>
+        <v>3.827699886189492</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>5.033538444481401</v>
+        <v>-0.6404988347488683</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.124662091910999</v>
+        <v>-4.424751027230307</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>3.094059405940598</v>
+        <v>-3.132276800967169</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>2.43591610836004</v>
+        <v>-3.47444596481823</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>3.030303030303031</v>
+        <v>-3.182482062712623</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.5154335123731713</v>
+        <v>-5.410879629629626</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.1846452866860986</v>
+        <v>-4.926479784173949</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>0.6264841894763151</v>
+        <v>-3.477449655793606</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.9723842862699357</v>
+        <v>-3.880147161351907</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.9196923589978709</v>
+        <v>-2.595739810880794</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-2.186014510883169</v>
+        <v>-3.288186283453356</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-1.911539798401115</v>
+        <v>-2.427267847557701</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.3935803293279889</v>
+        <v>-0.1202710393780322</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 89.25</t>
+          <t>X &gt; 88.34</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>6.8633545672403</v>
+        <v>6.457373271889402</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>6.528577768890486</v>
+        <v>7.011466436185529</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>10.97291166103596</v>
+        <v>7.35677233429395</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>14.46163831386214</v>
+        <v>9.164370135485726</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>16.6468562446762</v>
+        <v>12.08881199538639</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>16.83382243077358</v>
+        <v>10.64574560138448</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>15.22153761242945</v>
+        <v>7.450663589151759</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>14.94332616767637</v>
+        <v>7.945743145743137</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14.98481334959108</v>
+        <v>8.073672055427245</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.37156153910081</v>
+        <v>5.677620560207913</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>11.12461277790138</v>
+        <v>4.349855574812246</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5.803846567730695</v>
+        <v>0.07327362034094165</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.840348366420798</v>
+        <v>-2.641618497109818</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>4.459605624427986</v>
+        <v>-2.089852558542937</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>3.801462326847428</v>
+        <v>-2.313942424298951</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>5.236185383244205</v>
+        <v>-1.287125685835967</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>1.740923708451611</v>
+        <v>-4.196550546448087</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>2.476419139084207</v>
+        <v>-2.690090389314612</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>6.053655057823654</v>
+        <v>0.8030603624213271</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>2.87915632997656</v>
+        <v>-1.441369585962313</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>2.33661016201053</v>
+        <v>-0.3694698250479647</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.2602442027599139</v>
+        <v>-2.903648740445874</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-1.666441759185417</v>
+        <v>-1.840342124019955</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.06160174350113579</v>
+        <v>0.4565352751332057</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 91.85</t>
+          <t>X &gt; 90.91</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>4.330167379321658</v>
+        <v>2.171658986175117</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>9.792492030247196</v>
+        <v>4.782895007614108</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>15.60084979281041</v>
+        <v>10.67105804857966</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>22.13427258496188</v>
+        <v>15.79294156405716</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>26.14630819937112</v>
+        <v>18.37452628110069</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>26.3332743854685</v>
+        <v>18.53145988709877</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>24.11205033925932</v>
+        <v>16.30780644629461</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>22.3845635321874</v>
+        <v>14.57431457431457</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>20.97677535178326</v>
+        <v>14.70224348399868</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>18.75458431342793</v>
+        <v>11.04904913163648</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>19.02864395558985</v>
+        <v>8.464141289097952</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>15.85134382750417</v>
+        <v>3.901845048912378</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>13.27890639832922</v>
+        <v>1.358381502890175</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>15.95637824652032</v>
+        <v>3.96729029859992</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>13.8489595866209</v>
+        <v>2.746833639282151</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>11.54479578392622</v>
+        <v>2.754002960744614</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>9.961603284629902</v>
+        <v>-0.2910539215686256</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>12.75531330544641</v>
+        <v>5.458414914446237</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>20.21758149796494</v>
+        <v>13.0258183180626</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>16.05660122097645</v>
+        <v>7.358051821945111</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>18.41260577764809</v>
+        <v>9.731783791152608</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>13.98893372928246</v>
+        <v>6.715444798609091</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>14.26340844176451</v>
+        <v>9.900255754475701</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>12.73830082622241</v>
+        <v>9.738116760186237</v>
       </c>
     </row>
   </sheetData>
@@ -5824,2461 +5824,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 16.23</t>
+          <t>X &lt; 16.26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2.241505827744504</v>
+        <v>3.600230414746541</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-5.446212147075897</v>
+        <v>-5.217104992385899</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.939298215657814</v>
+        <v>3.528200905722528</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4.167520666803306</v>
+        <v>4.364370135485728</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.772906664844271</v>
+        <v>5.517383423957824</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>5.489284615647534</v>
+        <v>4.245745601384478</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>6.1879241670513</v>
+        <v>4.87923501772319</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.909712722298224</v>
+        <v>4.57431457431457</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>7.421788139507044</v>
+        <v>6.130814912570102</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.648872463470553</v>
+        <v>5.334763417350764</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>9.864108576220723</v>
+        <v>8.464141289097952</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>9.585359172772726</v>
+        <v>8.187559334626656</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>9.93278534121071</v>
+        <v>8.501238645747314</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>12.65288293535237</v>
+        <v>11.11014744145707</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>11.99473963777181</v>
+        <v>10.42799305957201</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>14.05971479500892</v>
+        <v>12.4178685069631</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>13.92579765803144</v>
+        <v>13.74255952380951</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>15.29154518950438</v>
+        <v>15.03824684721936</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>16.97802480572282</v>
+        <v>16.68128050293654</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>18.63545885098496</v>
+        <v>18.32443837656697</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>16.62232444772481</v>
+        <v>16.32842244661479</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>13.60530201572748</v>
+        <v>13.39611706751665</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>12.40918849291542</v>
+        <v>13.63975155279503</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>12.33335623969214</v>
+        <v>13.47761255850556</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 18.84</t>
+          <t>X &lt; 18.83</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.540971068386213</v>
+        <v>5.015931830447961</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.248351184509062</v>
+        <v>-0.6353804106613126</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.949993402823587</v>
+        <v>1.713529091050709</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.6720515257100601</v>
+        <v>-0.6806749095593148</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.8103398199244864</v>
+        <v>0.8455687521431514</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.729966721250868</v>
+        <v>-1.700200344561466</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.320097223323039</v>
+        <v>-4.297084158595993</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.871035940803381</v>
+        <v>-1.899301899301904</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.9204578497977707</v>
+        <v>-0.8704720887169017</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.511555344016081</v>
+        <v>-3.468325385738034</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.5102229745814242</v>
+        <v>-0.4933876684309979</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.84739125833422</v>
+        <v>2.833633980701315</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>7.178774646023562</v>
+        <v>7.124147268655953</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.957695769576972</v>
+        <v>6.875913207222844</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>6.299552471996414</v>
+        <v>6.193758825337788</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>8.712121212121204</v>
+        <v>8.556864645959237</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>9.487294984234651</v>
+        <v>9.353885135135137</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>12.10972700768619</v>
+        <v>11.92370373267623</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>14.14380020679233</v>
+        <v>13.93996776162381</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>12.51246419857854</v>
+        <v>12.35275240488099</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>11.96991803061251</v>
+        <v>11.78530790350025</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>9.80066089322343</v>
+        <v>9.007442678842274</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>9.157704413044939</v>
+        <v>9.251077164120652</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>9.081872159821664</v>
+        <v>9.088938169831188</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 21.45</t>
+          <t>X &lt; 21.4</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.692486219901369</v>
+        <v>4.073267311624498</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.9554896835938607</v>
+        <v>0.2114664361855318</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.9621959653617225</v>
+        <v>2.290105667627287</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.591523825113619</v>
+        <v>2.364370135485721</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.255733352566345</v>
+        <v>1.422145328719729</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.241864219725542</v>
+        <v>-1.754254398615522</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.356094782810523</v>
+        <v>-3.216003077514905</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.620883408771654</v>
+        <v>-2.187590187590196</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.2371143476623203</v>
+        <v>-0.7263279445727449</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.01003002369881</v>
+        <v>-1.522379439792083</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.948593376852379</v>
+        <v>1.416522241478908</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>5.025548671390958</v>
+        <v>4.473273620340947</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8.600373181716044</v>
+        <v>8.025048169556833</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>7.708153365672146</v>
+        <v>7.110147441457066</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>7.050010068091588</v>
+        <v>6.42799305957201</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>7.644396990034579</v>
+        <v>6.989297078391672</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>8.852761732251736</v>
+        <v>8.218749999999993</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>10.76134384722249</v>
+        <v>10.08586589483841</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>11.64837616774414</v>
+        <v>10.96699478865084</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>10.49294009851754</v>
+        <v>9.848247900376492</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>9.950393930551506</v>
+        <v>9.280803398995758</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>9.670484845616194</v>
+        <v>8.538974210373802</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>9.26928388242257</v>
+        <v>8.782608695652179</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>8.517775953523618</v>
+        <v>7.953803034696044</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 24.06</t>
+          <t>X &lt; 23.98</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.6860759634911062</v>
+        <v>1.745834810350942</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.217169805501591</v>
+        <v>-2.097712307775822</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.957332281201126</v>
+        <v>-2.386222834788171</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.907084785133563</v>
+        <v>-3.693882291698742</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-3.291655745485713</v>
+        <v>-2.513129752186423</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-3.824440874548543</v>
+        <v>-3.327069932596103</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.576781715301642</v>
+        <v>-5.093025731236594</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-5.364797081623337</v>
+        <v>-4.912509281441331</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.852721664414524</v>
+        <v>-3.813706585349451</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.645245183588273</v>
+        <v>-3.638884294161024</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.9202051492694849</v>
+        <v>-0.9394648135372705</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.742221917870758</v>
+        <v>1.696574591214727</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.57984416474013</v>
+        <v>2.523430046579492</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.848961366724915</v>
+        <v>2.760632878350265</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>2.190818069144356</v>
+        <v>2.078478496465209</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>2.295008912655973</v>
+        <v>2.154345622080989</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>3.631680010972616</v>
+        <v>3.506775889967642</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>4.99742754244555</v>
+        <v>4.830202464417695</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>5.703515001801257</v>
+        <v>5.530101584767351</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>4.419772576475154</v>
+        <v>4.288377350214681</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>3.877226408509124</v>
+        <v>3.720932848833947</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>4.115299118016672</v>
+        <v>3.160333433674779</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>5.374995505375566</v>
+        <v>4.860278598564811</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>4.31394157727545</v>
+        <v>4.212702711071458</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 26.66</t>
+          <t>X &lt; 26.55</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.330742583815244</v>
+        <v>-0.1179691938640204</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-5.723875660033528</v>
+        <v>-4.647640093024094</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-5.238204364321547</v>
+        <v>-5.043227665706048</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.309695571804809</v>
+        <v>-2.694453393926032</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-2.045426322060742</v>
+        <v>-2.091743560169164</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.9562723305351923</v>
+        <v>-1.240365509726637</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.146660730737601</v>
+        <v>-3.771558633070462</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-4.134092033646709</v>
+        <v>-4.423701298701303</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.737994922653982</v>
+        <v>-4.642994611239416</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.383251024222396</v>
+        <v>-3.355712773125425</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.045361594826424</v>
+        <v>-2.04181109185442</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.158158505271679</v>
+        <v>0.1121625092298331</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.226485800117686</v>
+        <v>2.122270391779061</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.650796994593072</v>
+        <v>1.52681410812373</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>2.347263626090538</v>
+        <v>1.191881948460896</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1.877820760799487</v>
+        <v>0.7115193006138938</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>1.034683765665989</v>
+        <v>0.2604166666666643</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>1.993672849078841</v>
+        <v>1.169199228171728</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>3.273394017237209</v>
+        <v>2.425328121984172</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>2.751019969049203</v>
+        <v>1.945470122598707</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>3.626913517395238</v>
+        <v>2.766914510106865</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>3.776957866679957</v>
+        <v>2.69175198815158</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>6.064650677789359</v>
+        <v>4.671497584541065</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>4.560246995994667</v>
+        <v>3.467691923584937</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 29.27</t>
+          <t>X &lt; 29.13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.9416183216581899</v>
+        <v>-0.3456957818190318</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-5.006551746833331</v>
+        <v>-4.814174589455497</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.284443994404498</v>
+        <v>-5.17176237007623</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.017788690100076</v>
+        <v>-2.800578318122518</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.176673167088502</v>
+        <v>-2.422815911590355</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.067087933372072</v>
+        <v>-1.232290574326115</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.433792927097066</v>
+        <v>-2.285770519375376</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.234197583338393</v>
+        <v>-2.849088895600531</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.976000218656054</v>
+        <v>-3.754751717182572</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.921239654483671</v>
+        <v>-2.742017682686146</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.647180012321748</v>
+        <v>-2.469782668081812</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.09825317556087043</v>
+        <v>-0.9375790928373462</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.650647420768394</v>
+        <v>0.7899060506937943</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.9073753328335528</v>
+        <v>0.02487612362761382</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>1.55471506397361</v>
+        <v>0.8931093386417714</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>1.365812168684236</v>
+        <v>0.9376174918283695</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.7097018202185126</v>
+        <v>0.3169412144702832</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.8659577221414523</v>
+        <v>0.959250907758296</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1.604042314554036</v>
+        <v>1.690509000537148</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.529791518777934</v>
+        <v>1.646697512779582</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>1.509438562300147</v>
+        <v>1.596048877031933</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>2.379555172487571</v>
+        <v>2.296080153526262</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>3.604958139356661</v>
+        <v>3.573306370070782</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>2.906111657648793</v>
+        <v>3.152769442964789</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 31.88</t>
+          <t>X &lt; 31.7</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.218082885789684</v>
+        <v>-1.542626728110598</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.706784807912129</v>
+        <v>-5.29153957583852</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-5.617724593465837</v>
+        <v>-5.444834091408858</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.16136180643138</v>
+        <v>-2.919332077793946</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-5.027961223294582</v>
+        <v>-4.903123488484567</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.271314490524716</v>
+        <v>-2.12522214055101</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.520620979402338</v>
+        <v>-2.718691249557914</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.798832424155414</v>
+        <v>-3.225224596192348</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.168867875985569</v>
+        <v>-3.702134396185649</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.089931700170212</v>
+        <v>-2.683669762372737</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.021633374880714</v>
+        <v>-2.411434747768403</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.03700829273199702</v>
+        <v>-0.4702747667558285</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.2801588585188739</v>
+        <v>-0.1738765616259528</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.4706026158171426</v>
+        <v>-0.01888481660744645</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.841265902598721</v>
+        <v>0.3070253176365227</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>1.229891507669279</v>
+        <v>1.069942239682</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.4786904200745354</v>
+        <v>0.1596102150537675</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.7853723499982053</v>
+        <v>0.8331777227953907</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.235831632157094</v>
+        <v>2.055704466070189</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>2.216916125252702</v>
+        <v>1.867065104677557</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>2.703176541648808</v>
+        <v>2.509298022651663</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>2.962488189165924</v>
+        <v>2.837361307147987</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>3.780117029619362</v>
+        <v>3.685834502103795</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>3.835609314835246</v>
+        <v>3.523695507814331</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 34.49</t>
+          <t>X &lt; 34.28</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.834395500528743</v>
+        <v>-2.665433745654454</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.217950244576613</v>
+        <v>-4.587255608542904</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.766393769874256</v>
+        <v>-5.603227665706051</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.966143171503482</v>
+        <v>-3.552296531180936</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.676673167088495</v>
+        <v>-5.188876608144909</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.779486307355818</v>
+        <v>-2.699592019194299</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.161376465253738</v>
+        <v>-2.690815510526704</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.950988561472613</v>
+        <v>-2.674192545575188</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.235234278580705</v>
+        <v>-3.510893860971464</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.70521835852599</v>
+        <v>-2.860000018570226</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.919758064898268</v>
+        <v>-2.748536708145956</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.221308771277862</v>
+        <v>-1.899716733356804</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.8786727925313755</v>
+        <v>-1.567663513187</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.4482858709323594</v>
+        <v>-1.012039053719782</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.1292304714445152</v>
+        <v>-0.5687915063443896</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.5120422465699264</v>
+        <v>-0.4898026000649125</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.3202264845246034</v>
+        <v>-0.4329113076098636</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.2622007388343803</v>
+        <v>-0.08348030023127251</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.9308893391583482</v>
+        <v>1.095612151994885</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>1.280601598637773</v>
+        <v>1.470970301233933</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>1.389521228717349</v>
+        <v>1.546612616573462</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>2.392366596861727</v>
+        <v>2.596852023878625</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>2.605266924287967</v>
+        <v>2.679714804976939</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>2.958657096532427</v>
+        <v>2.999890923227667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 37.09</t>
+          <t>X &lt; 36.85</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>726</v>
+        <v>743</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.028602215472787</v>
+        <v>-3.141557209394016</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.065542167912568</v>
+        <v>-5.060287245206702</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.072578840758204</v>
+        <v>-5.177275923078703</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.667580586812889</v>
+        <v>-4.092005703440442</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.8892000383021</v>
+        <v>-5.373553596011455</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-3.261722636568422</v>
+        <v>-3.39893811328578</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.863556507523057</v>
+        <v>-3.251893611386592</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.004593741027847</v>
+        <v>-3.287635050757537</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.825932347864857</v>
+        <v>-3.563474647129951</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.501454333915063</v>
+        <v>-3.013631122160859</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.364568903001434</v>
+        <v>-3.010575111594214</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.957447250207998</v>
+        <v>-2.479620053952459</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.98321562707784</v>
+        <v>-2.517796155252491</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.655597658531278</v>
+        <v>-2.093082706591389</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-2.313740956111836</v>
+        <v>-2.506058084438756</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-2.405225090410276</v>
+        <v>-2.617701575713305</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-2.53914222738775</v>
+        <v>-2.721581987438313</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.9581118749675</v>
+        <v>-1.912339578468021</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.193523649050029</v>
+        <v>-1.15951934324687</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.5951552053371501</v>
+        <v>-0.541164392131364</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.8633529508066076</v>
+        <v>-0.9740193914932505</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.03399985886851198</v>
+        <v>-0.1070553993166499</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.08980009839456216</v>
+        <v>-0.2671894200947946</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.7428522695090223</v>
+        <v>0.6473876017664821</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 39.7</t>
+          <t>X &lt; 39.43</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>846</v>
+        <v>861</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.82309010408617</v>
+        <v>-3.080732963676411</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.332349057980615</v>
+        <v>-3.38390928635782</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.423010642311603</v>
+        <v>-3.538598036076422</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.254381270994088</v>
+        <v>-3.376070188963865</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-3.645486044352083</v>
+        <v>-3.939030231991801</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.338876025812347</v>
+        <v>-2.328005850415749</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.047369950595758</v>
+        <v>-3.123087862648468</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.97264021887824</v>
+        <v>-3.195720268891002</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.460564801669427</v>
+        <v>-2.719359303457772</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.409951065941208</v>
+        <v>-2.818546687178852</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.018244364955756</v>
+        <v>-2.546311672574518</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.944052591933165</v>
+        <v>-2.358317552713636</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.773097011730464</v>
+        <v>-2.079481447167893</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.523587652882931</v>
+        <v>-1.630851397102752</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.946436832816431</v>
+        <v>-1.964573723238672</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.822638146167563</v>
+        <v>-1.751701760168146</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.721261165497971</v>
+        <v>-1.623294134727061</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.473160692848559</v>
+        <v>-1.175458146973448</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.7866810766301242</v>
+        <v>-0.4964198454955095</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.3645411490150394</v>
+        <v>-0.04954536327043968</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.7198774507023984</v>
+        <v>-0.500845846068124</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.3722229565255688</v>
+        <v>-0.1114322936912373</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.3816303139461752</v>
+        <v>-0.2162298641619884</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.3218140341574411</v>
+        <v>0.550783290212884</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 42.31</t>
+          <t>X &lt; 42</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>967</v>
+        <v>986</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-3.079049360622975</v>
+        <v>-2.987631773519276</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.157628001761331</v>
+        <v>-2.778432553713465</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.72479956265515</v>
+        <v>-3.27376356054932</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.257744521239125</v>
+        <v>-3.10526549204463</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-3.949566939982276</v>
+        <v>-3.73286986884866</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.579322704077072</v>
+        <v>-2.508818293138852</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.604410032815693</v>
+        <v>-3.608159940260002</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.471521785893536</v>
+        <v>-3.405980992187899</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.0189349123036</v>
+        <v>-2.973792447615352</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.969651204989631</v>
+        <v>-2.958484916465515</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.592816639908904</v>
+        <v>-2.584830023565033</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.609024753637357</v>
+        <v>-2.455732464851756</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.98321562707784</v>
+        <v>-1.745066772971889</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.689891211343351</v>
+        <v>-1.384781564628128</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-2.039392533615263</v>
+        <v>-1.762676311624745</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.959408903853351</v>
+        <v>-1.708471684285804</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-1.887564723958391</v>
+        <v>-1.609512339418529</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.478002135598508</v>
+        <v>-1.032457296507104</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.159230096237962</v>
+        <v>-0.6151553127690406</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.60334892753324</v>
+        <v>-0.1977291111177735</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.9822844061259985</v>
+        <v>-0.5623338559062034</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.9973811628070948</v>
+        <v>-0.5360764995653398</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.075254871207093</v>
+        <v>-0.6981215274715495</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.193926441736167</v>
+        <v>-0.6574207651687232</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 44.92</t>
+          <t>X &lt; 44.57</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1103</v>
+        <v>1115</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.521778178785596</v>
+        <v>-2.560483870967744</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.721143625043432</v>
+        <v>-2.582099247460583</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.306019642427117</v>
+        <v>-3.075428023487802</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.074532348298604</v>
+        <v>-3.084152693520537</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.171282331508984</v>
+        <v>-4.208679044040124</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-3.127939252316914</v>
+        <v>-3.198200586956325</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.122077421342837</v>
+        <v>-4.17265479649847</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.680216858895193</v>
+        <v>-3.58071425336</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.188684672480029</v>
+        <v>-3.18372704771177</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.061510339515621</v>
+        <v>-2.993231457729316</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.098265562624015</v>
+        <v>-2.990054739089103</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.967019758962287</v>
+        <v>-2.818206200286852</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.926070013374755</v>
+        <v>-1.78063195002462</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.966806238784379</v>
+        <v>-1.759807715493601</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-2.083921583254032</v>
+        <v>-1.903845505450406</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-2.210905265458912</v>
+        <v>-1.880658078558994</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-2.074308425880936</v>
+        <v>-1.536107997010468</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.638121176591213</v>
+        <v>-1.220561608898528</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-1.008808916935919</v>
+        <v>-0.5576688884792134</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.8594664904253122</v>
+        <v>-0.2533963447655196</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-1.168336120299863</v>
+        <v>-0.6414686488368275</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-1.191078074770253</v>
+        <v>-0.7166311707921125</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-1.225721993018091</v>
+        <v>-0.8317410801325735</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.339247888087712</v>
+        <v>-0.9041939757673347</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 47.52</t>
+          <t>X &lt; 47.15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1229</v>
+        <v>1252</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.718633801483293</v>
+        <v>-3.025522511722365</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.691514762504092</v>
+        <v>-2.753501716680709</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.365450189728442</v>
+        <v>-3.489442805148279</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.232706305014354</v>
+        <v>-3.243285366906612</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-4.410899118128611</v>
+        <v>-4.35492304052741</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.457385839974329</v>
+        <v>-3.517832673375914</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-4.589674543665865</v>
+        <v>-4.552531299027152</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.900923861102257</v>
+        <v>-3.898985288761651</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.295375438252819</v>
+        <v>-3.371695356713325</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.423649696078201</v>
+        <v>-3.209280398258549</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.105530892469993</v>
+        <v>-3.0967897925999</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.178729513549271</v>
+        <v>-3.133755133652656</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.834296289502952</v>
+        <v>-1.692736707972443</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.847331054851644</v>
+        <v>-1.861098564932711</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.939589146288299</v>
+        <v>-1.904275311035022</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-2.072768917958896</v>
+        <v>-1.981948927998104</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-2.079342262014251</v>
+        <v>-2.00595713525027</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.651774648552305</v>
+        <v>-1.419991400156285</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.307798437675025</v>
+        <v>-1.125656968537669</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.398175040527846</v>
+        <v>-1.150687136897211</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.650211839517361</v>
+        <v>-1.558387229332261</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.678780748166048</v>
+        <v>-1.393933137869006</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-2.007358613732123</v>
+        <v>-1.789276288373372</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.792188201029632</v>
+        <v>-1.552054260298632</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 50.13</t>
+          <t>X &lt; 49.72</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1386</v>
+        <v>1398</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.862753230074922</v>
+        <v>-2.331800517284385</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.591282274771103</v>
+        <v>-1.685896357827303</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.564640111809929</v>
+        <v>-2.832100704222462</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.598443024446539</v>
+        <v>-2.602082398418631</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.751973758080965</v>
+        <v>-3.554045147470745</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.456006562922397</v>
+        <v>-3.145247965448974</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-4.118798522024335</v>
+        <v>-3.974229114710909</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.468438538205973</v>
+        <v>-3.277718942955005</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.855522784862707</v>
+        <v>-2.863667000366746</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.160655350514226</v>
+        <v>-2.80134939687364</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.990389446164201</v>
+        <v>-2.672175898721378</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.015171375881962</v>
+        <v>-2.734165578514556</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.735004984088462</v>
+        <v>-1.41701191628006</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.556478228468002</v>
+        <v>-1.379122944809033</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-2.071252350421325</v>
+        <v>-1.775154293789939</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-2.152623798965266</v>
+        <v>-1.85762709900461</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-2.1018194189501</v>
+        <v>-1.889976752503571</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.877995040380682</v>
+        <v>-1.593676308308957</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.476747469830109</v>
+        <v>-1.236152564711112</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.82370323111406</v>
+        <v>-1.593812185460415</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-2.180877178498029</v>
+        <v>-2.018195170389085</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-2.431314359929409</v>
+        <v>-2.236419208796434</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-2.547976781269242</v>
+        <v>-2.421969272874293</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-2.366159930412273</v>
+        <v>-2.226454476033567</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 52.74</t>
+          <t>X &lt; 52.3</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1568</v>
+        <v>1576</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.721400920858017</v>
+        <v>-1.519870723053707</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.330787639741473</v>
+        <v>-0.973859307014969</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.979490471839867</v>
+        <v>-1.752088425199723</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.091288026913773</v>
+        <v>-1.994084582690327</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.897718683086701</v>
+        <v>-2.615877484968486</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.487542478826626</v>
+        <v>-2.298325419541328</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.099170329622922</v>
+        <v>-3.059488695112201</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.935183416827037</v>
+        <v>-2.729891372023353</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.480048701424018</v>
+        <v>-2.348155355740268</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.775542463790664</v>
+        <v>-2.70004441441138</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.846241386549202</v>
+        <v>-2.68161650640603</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.710211367032827</v>
+        <v>-2.577487800978851</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.707041692264262</v>
+        <v>-1.598471288988002</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.764849915555907</v>
+        <v>-1.52944646717237</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.852289345032474</v>
+        <v>-1.83089018915895</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-2.236194431625904</v>
+        <v>-2.031007490136247</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-2.079804582864924</v>
+        <v>-1.944532571912013</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-2.084566627522307</v>
+        <v>-1.823609570474638</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-1.895614923531888</v>
+        <v>-1.545695566679115</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-2.181035685761032</v>
+        <v>-1.902175111467841</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-2.432604971528562</v>
+        <v>-2.152360729599849</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-2.3444919145835</v>
+        <v>-2.164071474905384</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-2.351993226426238</v>
+        <v>-2.23769587287574</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-2.263732595842072</v>
+        <v>-2.019124207266721</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 55.35</t>
+          <t>X &lt; 54.87</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1742</v>
+        <v>1759</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.343626466806889</v>
+        <v>-1.474638059555353</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.081185773302778</v>
+        <v>-1.067445128440312</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.353449888694662</v>
+        <v>-1.327969582892656</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.35386970752824</v>
+        <v>-1.152088434321314</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.829073069630525</v>
+        <v>-1.794209015402934</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.724795555670134</v>
+        <v>-1.663345307706436</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.12420546567828</v>
+        <v>-2.029722994134197</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.459332106788793</v>
+        <v>-2.220942471084598</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.987966650791762</v>
+        <v>-1.865611628484068</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.216554049014782</v>
+        <v>-2.09315829141233</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.594808856202661</v>
+        <v>-2.332577625869959</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.842076148189669</v>
+        <v>-2.43860813065394</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.392624274690434</v>
+        <v>-2.132238167377018</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.181497418731013</v>
+        <v>-1.982518846206382</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-2.325648711742765</v>
+        <v>-2.096168395800355</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-2.669696969696972</v>
+        <v>-2.444472108646416</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.428085233032363</v>
+        <v>-2.150399137767678</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-2.55742506221187</v>
+        <v>-2.283283242929279</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-2.079855931002328</v>
+        <v>-1.841419082867063</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-2.375591617312324</v>
+        <v>-2.138486986870056</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.6562867102054</v>
+        <v>-2.421679072105256</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.527320758152719</v>
+        <v>-2.269439661144098</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-2.621522586697154</v>
+        <v>-2.42375855846948</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-2.664617691556593</v>
+        <v>-2.415346103071627</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 57.95</t>
+          <t>X &lt; 57.45</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1907</v>
+        <v>1930</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.8947331237946585</v>
+        <v>-0.8566763148874585</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.8911241709834385</v>
+        <v>-0.713598163297668</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.056796487783728</v>
+        <v>-0.9584293203079071</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.8593421800479391</v>
+        <v>-0.6951228805515157</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.270279456956466</v>
+        <v>-0.9422439052347258</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.626070617354763</v>
+        <v>-1.17113684294489</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.953814857040669</v>
+        <v>-1.678870089604715</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.255378587236514</v>
+        <v>-1.93197706151075</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.71697662758605</v>
+        <v>-1.337726908303324</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.148628837934957</v>
+        <v>-1.771084103004526</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.366283580642026</v>
+        <v>-1.965170331923503</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.720376044711884</v>
+        <v>-2.241752286394799</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.61551865191938</v>
+        <v>-2.164934559285989</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.441934334278493</v>
+        <v>-1.94684737719578</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2.391850071180663</v>
+        <v>-1.955426629547162</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-2.602856238626465</v>
+        <v>-2.119511211763772</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-2.289089550770576</v>
+        <v>-1.808883851468053</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-2.363969708561484</v>
+        <v>-1.993581428132238</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-2.327291463044098</v>
+        <v>-1.882746143991653</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-2.529160843046498</v>
+        <v>-2.082667470953389</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-2.832556981286587</v>
+        <v>-2.546485029328949</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-2.773769256573999</v>
+        <v>-2.466207136776454</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.731396042785661</v>
+        <v>-2.481640009011031</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-2.777381290768389</v>
+        <v>-2.54015206029532</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 60.56</t>
+          <t>X &lt; 60.02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2064</v>
+        <v>2067</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7419491738057147</v>
+        <v>-0.5759118221771686</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.6199192137952068</v>
+        <v>-0.1205798958608</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.9292304907887896</v>
+        <v>-0.6250721852618213</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.9442553295837257</v>
+        <v>-0.4182385601664436</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.349569401914643</v>
+        <v>-0.9571039060152486</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.328255080346132</v>
+        <v>-1.063732154901786</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.352992247568373</v>
+        <v>-1.300183048487327</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.796735241502681</v>
+        <v>-1.75024137288289</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.63233856167848</v>
+        <v>-1.42879528854953</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.993487271568789</v>
+        <v>-1.741053847145743</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.029459635849861</v>
+        <v>-1.855853181839905</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.522200614147827</v>
+        <v>-2.229193723635831</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.365584609179081</v>
+        <v>-2.086224205866479</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.884243390587848</v>
+        <v>-1.705527449689527</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.984006708813141</v>
+        <v>-1.710371720302206</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-2.278577278577274</v>
+        <v>-2.068274281066472</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-2.191735787022097</v>
+        <v>-1.881878930817614</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.978986211461809</v>
+        <v>-1.724487274005334</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-2.073520413621566</v>
+        <v>-1.945438689820378</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.294112203742536</v>
+        <v>-2.214645181384519</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.615559385053579</v>
+        <v>-2.636951801778324</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-2.518495034554398</v>
+        <v>-2.325079974435099</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-2.458351743518136</v>
+        <v>-2.371721251130595</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-2.458025429254505</v>
+        <v>-2.388722364433129</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 63.17</t>
+          <t>X &lt; 62.6</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2230</v>
+        <v>2238</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.044309164031169</v>
+        <v>-1.115009801607258</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.178110590289776</v>
+        <v>-0.8027938133688295</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.171084098085096</v>
+        <v>-0.8747033678906249</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.9710414246999548</v>
+        <v>-0.6846932008211439</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.282307417231422</v>
+        <v>-1.024976491896062</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.204246889481212</v>
+        <v>-1.022111541472661</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.239626292384806</v>
+        <v>-1.033481118306923</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.626560914493979</v>
+        <v>-1.472389949388614</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.649350338155742</v>
+        <v>-1.433786631486555</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.639897590005376</v>
+        <v>-1.38124500477646</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.920266341824977</v>
+        <v>-1.689626336755424</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.174099293932429</v>
+        <v>-1.876882699444671</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.022880459246011</v>
+        <v>-1.696553736055783</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.548797736916541</v>
+        <v>-1.230183063232531</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.600484070291138</v>
+        <v>-1.242395506752246</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.82894629945568</v>
+        <v>-1.619010201644059</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.847690995364651</v>
+        <v>-1.678227817478039</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.658365365057342</v>
+        <v>-1.543135147293505</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.819185353508658</v>
+        <v>-1.685975287275916</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-2.054150923094767</v>
+        <v>-1.918016801127166</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-2.302361414080721</v>
+        <v>-2.217484527161758</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-2.083607956863709</v>
+        <v>-1.980007477879887</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-2.276259868410285</v>
+        <v>-2.183000951511737</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-2.191835002724105</v>
+        <v>-2.140924400513953</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 65.78</t>
+          <t>X &lt; 65.17</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2372</v>
+        <v>2385</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.9477364662503405</v>
+        <v>-0.9308423570282685</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9263340203866264</v>
+        <v>-0.8621121591321881</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.04673949236313</v>
+        <v>-0.7981419275211863</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.026262532094975</v>
+        <v>-0.782073379158625</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.129890589565655</v>
+        <v>-0.8253780422862675</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.505546789717961</v>
+        <v>-1.022261098783027</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.37554073335005</v>
+        <v>-1.04032928893789</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.839819251295239</v>
+        <v>-1.489629863477319</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.607512730401034</v>
+        <v>-1.194056360331338</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.518870744458042</v>
+        <v>-1.109973739875912</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.724250037665087</v>
+        <v>-1.256850208926231</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.811699650756694</v>
+        <v>-1.281965273204733</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.820195330705552</v>
+        <v>-1.307167533153418</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.513413306066127</v>
+        <v>-1.010556665835473</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.433256508187625</v>
+        <v>-1.022132673873088</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.654570919276793</v>
+        <v>-1.340962770728197</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.638082370650906</v>
+        <v>-1.361020885722276</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.550338746576358</v>
+        <v>-1.284349249056547</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.64653902906646</v>
+        <v>-1.447087357199962</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.94039775428341</v>
+        <v>-1.73543469252656</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-2.079842734937721</v>
+        <v>-1.925678858618106</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.878616909888265</v>
+        <v>-1.749374490380596</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.958948142269634</v>
+        <v>-1.799118043660471</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.926141825975947</v>
+        <v>-1.811396126729527</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 68.38</t>
+          <t>X &lt; 67.74</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.7205629776782203</v>
+        <v>-0.7879695739290682</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.8370530471943383</v>
+        <v>-0.6560989880809203</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.108745646436788</v>
+        <v>-0.8187135839924409</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.010042258801541</v>
+        <v>-0.7546774835618848</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.126419073356146</v>
+        <v>-0.8893539434782411</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.11527891795096</v>
+        <v>-0.9885673453986854</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.192939570848928</v>
+        <v>-0.9672942972209029</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.409475340738616</v>
+        <v>-1.25012330894684</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.108322241937692</v>
+        <v>-0.843975003396281</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.9877029587775539</v>
+        <v>-0.7656226830353319</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.007989866960045</v>
+        <v>-0.7716070642974557</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.184965603986974</v>
+        <v>-0.8494608788641358</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.175345460673867</v>
+        <v>-0.8117297848681773</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.016412628966187</v>
+        <v>-0.662507566492053</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.857734685290751</v>
+        <v>-0.4702581327968289</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.113206298795816</v>
+        <v>-0.7833579295574467</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.065091469660942</v>
+        <v>-0.8872383412824547</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.146674913793198</v>
+        <v>-0.9008855625012941</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.344709693482272</v>
+        <v>-1.163370871126588</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.65164207288359</v>
+        <v>-1.465477589819592</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.693928067601128</v>
+        <v>-1.555974555429266</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.348701869949352</v>
+        <v>-1.273426425556245</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.448998093821196</v>
+        <v>-1.347756964125246</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.621126389679794</v>
+        <v>-1.44712473203689</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 70.99</t>
+          <t>X &lt; 70.32</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2665</v>
+        <v>2679</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.4414423515272006</v>
+        <v>-0.5095042867261554</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.7936365652987192</v>
+        <v>-0.5122863560706108</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.057723377789692</v>
+        <v>-0.778795635910889</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.8565783582815882</v>
+        <v>-0.6430814293428853</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.097260776200706</v>
+        <v>-0.8608711950720505</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.262376167935379</v>
+        <v>-1.01898221367891</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.26810074850777</v>
+        <v>-0.9730589024558469</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.525506796318624</v>
+        <v>-1.406495660227009</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.388571825374427</v>
+        <v>-1.129313019199621</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.244766515077188</v>
+        <v>-0.9925286935234254</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.061516341408776</v>
+        <v>-0.8322339774265544</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.13230107025614</v>
+        <v>-0.810308469211293</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.075743630916243</v>
+        <v>-0.6565438702441497</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.7517349865827612</v>
+        <v>-0.3450764391399517</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.6400001220064553</v>
+        <v>-0.2436487314727671</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.6967826412270881</v>
+        <v>-0.3912999365336987</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.58415302883013</v>
+        <v>-0.3459266169154276</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.7792148254712856</v>
+        <v>-0.4788107220770286</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.8783312198334698</v>
+        <v>-0.63748282328946</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.081663666811963</v>
+        <v>-0.9079710050961509</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.190092873026572</v>
+        <v>-1.027654312447034</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.981477577999776</v>
+        <v>-0.8789362373873928</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.210025134020732</v>
+        <v>-1.045749513303036</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.338975732496358</v>
+        <v>-1.223501929842961</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 73.6</t>
+          <t>X &lt; 72.89</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2800</v>
+        <v>2805</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.5058843079059372</v>
+        <v>-0.4886494553833245</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4674736637307575</v>
+        <v>-0.3249456419672256</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.9294175088453898</v>
+        <v>-0.8143719443130166</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.6656040724540944</v>
+        <v>-0.5343145427936946</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.8043526887020391</v>
+        <v>-0.7191538652110481</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.846038725896328</v>
+        <v>-0.8983312395973826</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.9238342743444221</v>
+        <v>-0.926560610136498</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.217626849894295</v>
+        <v>-1.104879851764863</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.191731868851541</v>
+        <v>-1.028322246567058</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.127372362818164</v>
+        <v>-0.8984478158604645</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.224116262239377</v>
+        <v>-0.8042754793188038</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.091571627997091</v>
+        <v>-0.689119542052218</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.020507395307575</v>
+        <v>-0.6287979842893066</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.8650153271554899</v>
+        <v>-0.378456547146925</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.790320986691583</v>
+        <v>-0.3127476811687373</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.6021756021755991</v>
+        <v>-0.2500191609245661</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.43011927233173</v>
+        <v>-0.282674501424502</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.5851476116360388</v>
+        <v>-0.4867836778111752</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.6333833939206741</v>
+        <v>-0.5928342711782193</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.7465164783764493</v>
+        <v>-0.7699857178571321</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.8400582934558471</v>
+        <v>-0.8388547206623613</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.823467350691466</v>
+        <v>-0.8219092951481031</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-1.027714293904424</v>
+        <v>-1.091945830363507</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.189753004005333</v>
+        <v>-1.26901336459094</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 76.21</t>
+          <t>X &lt; 75.47</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2911</v>
+        <v>2922</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.9141940800304624</v>
+        <v>-0.8159736947090934</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.4809086032239875</v>
+        <v>-0.2938182552566744</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7410645160651654</v>
+        <v>-0.5070748689802613</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.616532155963462</v>
+        <v>-0.3302733309079926</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.7627287497311102</v>
+        <v>-0.4504371513712826</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.7274526767429563</v>
+        <v>-0.4452752248360738</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.7973699505957583</v>
+        <v>-0.5725604545640905</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.090528440104556</v>
+        <v>-0.8241919413767747</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.063998519654227</v>
+        <v>-0.7454667005536066</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.031368863829591</v>
+        <v>-0.6334905509032041</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.182403051686265</v>
+        <v>-0.7715119465552789</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.133885760917487</v>
+        <v>-0.6720255249581939</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.9713093562165085</v>
+        <v>-0.4193962748876032</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7958755478423498</v>
+        <v>-0.2231858918762697</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.6120290971194109</v>
+        <v>-0.08482745324850072</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.5454078295804905</v>
+        <v>-0.03634394724934964</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.3164311046182462</v>
+        <v>0.09909188034187366</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.3666653007253089</v>
+        <v>0.0003958093683138486</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.4047719343723912</v>
+        <v>-0.0928342711782193</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.6093196779223149</v>
+        <v>-0.2543162021876171</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.5826495116598949</v>
+        <v>-0.2747521565597992</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.6724791276258415</v>
+        <v>-0.3296988402417966</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.7210636079249184</v>
+        <v>-0.4763718038346525</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.9484147304616357</v>
+        <v>-0.7210771843320103</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 78.81</t>
+          <t>X &lt; 78.04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3017</v>
+        <v>3022</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.5816365871161722</v>
+        <v>-0.6266464974680943</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.5040872220812176</v>
+        <v>-0.2618361346780205</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5091004986666263</v>
+        <v>-0.1800558885876811</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5454313562844817</v>
+        <v>-0.1277142972319538</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.5994098506947552</v>
+        <v>-0.2529893902948999</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.6246799157993124</v>
+        <v>-0.3417131444901074</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.686130662527205</v>
+        <v>-0.5242456218089515</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.9127887807758057</v>
+        <v>-0.6455382281009889</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.8526957965475859</v>
+        <v>-0.5651122194323506</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.7161982761416823</v>
+        <v>-0.417290213090169</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.8522571780017714</v>
+        <v>-0.5228716979150292</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.8150836058573816</v>
+        <v>-0.4688751399896347</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.6313610571108299</v>
+        <v>-0.2945110590932956</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.5688081196623074</v>
+        <v>-0.1129930544107083</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.4474282406155083</v>
+        <v>0.0312988446959821</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.3292011019283763</v>
+        <v>0.09673509492059651</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.04673579979613862</v>
+        <v>0.2242596418732745</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.0004436347574312549</v>
+        <v>0.1905490904306788</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.1609949318876502</v>
+        <v>0.1074906564194293</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.2193223862368328</v>
+        <v>-0.008501410918277941</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.2456147809467808</v>
+        <v>-0.0800781437039646</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.2685946777627635</v>
+        <v>-0.201766530366946</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.3388331809628795</v>
+        <v>-0.2693264680924443</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.6270251286324537</v>
+        <v>-0.5443218274261667</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 81.42</t>
+          <t>X &lt; 80.62</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3109</v>
+        <v>3127</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.3841421325890479</v>
+        <v>-0.2665453031742118</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2547679552183837</v>
+        <v>-0.01825039486760716</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.525464047074756</v>
+        <v>-0.2373715231217091</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.6456126402107643</v>
+        <v>-0.207422287309555</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6120038210892318</v>
+        <v>-0.2423981956964099</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.5670746085666138</v>
+        <v>-0.2588737041268274</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.7773763485484153</v>
+        <v>-0.5582592916640436</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.8775813953488338</v>
+        <v>-0.7178207688249216</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.786014828030801</v>
+        <v>-0.5082156996747997</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.6122452400950209</v>
+        <v>-0.2974990570169638</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.672123853971101</v>
+        <v>-0.3899019235923546</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.5480822204458988</v>
+        <v>-0.2333973020976146</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.3066565894076803</v>
+        <v>0.02419701517872141</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.3164888467044733</v>
+        <v>-0.0006090219964889343</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1538850462262289</v>
+        <v>0.1471121147906516</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.0856738705631841</v>
+        <v>0.2296417959148158</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.00797867663593621</v>
+        <v>0.2534345409086072</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.002620630916894129</v>
+        <v>0.2672196623990573</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.01921725102280902</v>
+        <v>0.2262540479100892</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.03813008346449465</v>
+        <v>0.1723190171655773</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.04749257934307849</v>
+        <v>0.1668523872811676</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.03982816749334717</v>
+        <v>0.07876328036421398</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.03548712652850838</v>
+        <v>0.1176470588235361</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.2208034106588315</v>
+        <v>-0.1854145327274708</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 84.03</t>
+          <t>X &lt; 83.19</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3198</v>
+        <v>3210</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.241281761056932</v>
+        <v>-0.1659228867227469</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.4041953403532119</v>
+        <v>-0.1163922560983224</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.6140157473924504</v>
+        <v>-0.3005122286322717</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.5952110262468082</v>
+        <v>-0.224777151335978</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.7272304742513427</v>
+        <v>-0.4211135629262657</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.6473118139690897</v>
+        <v>-0.3710710290840282</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.6554570423531416</v>
+        <v>-0.4661582606309764</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.6983256392816273</v>
+        <v>-0.5363431628566673</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.6392140391421961</v>
+        <v>-0.4219801184857985</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.5850298147508255</v>
+        <v>-0.2996394584314217</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.6045011660256066</v>
+        <v>-0.289299179693657</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.3669956009124604</v>
+        <v>-0.05081714745513466</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.1945220479337877</v>
+        <v>0.1398549253334522</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.2413520653810934</v>
+        <v>0.1713846189516275</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.132683829276381</v>
+        <v>0.3285215022204397</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.1434337133027057</v>
+        <v>0.2992131492651566</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.0219709167264952</v>
+        <v>0.3196721842296171</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.02937290486018185</v>
+        <v>0.2674579346393955</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>0.01414902750020275</v>
+        <v>0.2827024091796062</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.0009657033198990916</v>
+        <v>0.2357193793227665</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>0.008031120272001147</v>
+        <v>0.3091258390829026</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>0.01339025102159752</v>
+        <v>0.1902818068868797</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.005996399422265597</v>
+        <v>0.1722069516471905</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.09444790260268121</v>
+        <v>-0.03373590611391819</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 86.64</t>
+          <t>X &lt; 85.77</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3242</v>
+        <v>3273</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.3177230705529439</v>
+        <v>-0.2153705749656538</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4523395980562839</v>
+        <v>-0.2019074239968432</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.6480897888851018</v>
+        <v>-0.3761556073296362</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.7617901133027232</v>
+        <v>-0.3436590615945647</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.8659446438484792</v>
+        <v>-0.5111271588576045</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.815298567318905</v>
+        <v>-0.519926948828541</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.741754731203315</v>
+        <v>-0.4762770501176448</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.7878281725127394</v>
+        <v>-0.5205175119913292</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.698279046102229</v>
+        <v>-0.4363492665343713</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.655289987750713</v>
+        <v>-0.3621113106025717</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.6093711382457201</v>
+        <v>-0.2858042849866038</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.4403105911377594</v>
+        <v>-0.02672637965905977</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.2853843121409412</v>
+        <v>0.1998449175243167</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.334599880652263</v>
+        <v>0.1650254902375536</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.2978581149558579</v>
+        <v>0.2145784254256711</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.3312354312354273</v>
+        <v>0.1966141515624003</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.2007209087673942</v>
+        <v>0.275660569105689</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.164119835126165</v>
+        <v>0.2523800759911907</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.2070691271382827</v>
+        <v>0.2104359112865879</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.1251877366704264</v>
+        <v>0.2294909071916678</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.1256135564444918</v>
+        <v>0.2295213477136997</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.0597447674740863</v>
+        <v>0.2030963477783843</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.0751669513899671</v>
+        <v>0.1595176754933476</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.194313680836224</v>
+        <v>-0.0150328956430883</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 89.25</t>
+          <t>X &lt; 88.34</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3291</v>
+        <v>3313</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.3215954538061325</v>
+        <v>-0.3173041958573677</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.3686211952107001</v>
+        <v>-0.2771290019897421</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.5525318497016585</v>
+        <v>-0.3149178488342343</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.7052741170721788</v>
+        <v>-0.3803746092590217</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.7826291446456821</v>
+        <v>-0.519178392117368</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.7903804688812954</v>
+        <v>-0.5258890140001355</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.7293530219379605</v>
+        <v>-0.4627719383504925</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.7183845401931066</v>
+        <v>-0.4802340039862614</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.720270861951974</v>
+        <v>-0.4255760648735034</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.6591278924963433</v>
+        <v>-0.332247069154306</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.57956041680022</v>
+        <v>-0.253454686999369</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.3868585971690521</v>
+        <v>-0.06134407983966383</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3114516631003923</v>
+        <v>0.07563534209523937</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3329324147198065</v>
+        <v>0.08605105591490059</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.3065081340642095</v>
+        <v>0.126788240294907</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.3608761148924771</v>
+        <v>0.08568262056034825</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.2342993704706799</v>
+        <v>0.1625251004016022</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.2604717956336273</v>
+        <v>0.1077600396611302</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.390621681998482</v>
+        <v>0.008586108723164898</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.276886056629067</v>
+        <v>0.09023363045386645</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.2550640304351148</v>
+        <v>0.1135335960202752</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.1609758285411047</v>
+        <v>0.1468173476287049</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.1113604313930665</v>
+        <v>0.1066883576920077</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.169101443472286</v>
+        <v>-0.03754418333393517</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 91.85</t>
+          <t>X &lt; 90.91</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3341</v>
+        <v>3367</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.162844735310685</v>
+        <v>-0.1187778497162668</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.3330428829384857</v>
+        <v>-0.1127142546913475</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.476105780562925</v>
+        <v>-0.2588212864975432</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.6371593128946031</v>
+        <v>-0.3623654627417423</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.7183398337551665</v>
+        <v>-0.4442849313275516</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.7231735739397109</v>
+        <v>-0.5074320515862567</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.6745289738238682</v>
+        <v>-0.5174026438464665</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.6380627775353105</v>
+        <v>-0.4804029648750188</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.6094815793459389</v>
+        <v>-0.4245527966437592</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.5607356718849275</v>
+        <v>-0.345699948818428</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.5676848925084599</v>
+        <v>-0.2637619503505704</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.5013059734527801</v>
+        <v>-0.1385119881873251</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.4438115982810729</v>
+        <v>-0.05157110374489804</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.4981518742742637</v>
+        <v>-0.07503774372811733</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.4521435931324973</v>
+        <v>-0.01645138487243969</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.4072902811332142</v>
+        <v>-0.01811032901573384</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.3742234256708628</v>
+        <v>0.01404737206085827</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.4314903647232953</v>
+        <v>-0.1013067506799388</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.586406824669929</v>
+        <v>-0.2251760298545022</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.501532268332717</v>
+        <v>-0.1118035185891983</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.5480245531195393</v>
+        <v>-0.09802943977773282</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.4565656269323384</v>
+        <v>-0.0962291140548146</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.4635189383515268</v>
+        <v>-0.1615718269131392</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.4318426264451531</v>
+        <v>-0.2170711361781272</v>
       </c>
     </row>
   </sheetData>
